--- a/data/VLT.MI.xlsx
+++ b/data/VLT.MI.xlsx
@@ -20957,6 +20957,52 @@
         <v>7</v>
       </c>
     </row>
+    <row r="896">
+      <c r="A896" s="1" t="n">
+        <v>46279.2916666667</v>
+      </c>
+      <c r="B896" t="n">
+        <v>0</v>
+      </c>
+      <c r="C896" t="n">
+        <v>11.8000001907349</v>
+      </c>
+      <c r="D896" t="n">
+        <v>11.8000001907349</v>
+      </c>
+      <c r="E896" t="n">
+        <v>11.8000001907349</v>
+      </c>
+      <c r="F896" t="n">
+        <v>11.8000001907349</v>
+      </c>
+      <c r="G896" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="897">
+      <c r="A897" s="1" t="n">
+        <v>46280.2916666667</v>
+      </c>
+      <c r="B897" t="n">
+        <v>3600</v>
+      </c>
+      <c r="C897" t="n">
+        <v>11.8000001907349</v>
+      </c>
+      <c r="D897" t="n">
+        <v>11.8000001907349</v>
+      </c>
+      <c r="E897" t="n">
+        <v>11.8000001907349</v>
+      </c>
+      <c r="F897" t="n">
+        <v>11.8000001907349</v>
+      </c>
+      <c r="G897" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/VLT.MI.xlsx
+++ b/data/VLT.MI.xlsx
@@ -21003,6 +21003,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="898">
+      <c r="A898" s="1" t="n">
+        <v>46281.2916666667</v>
+      </c>
+      <c r="B898" t="n">
+        <v>0</v>
+      </c>
+      <c r="C898" t="n">
+        <v>11.8000001907349</v>
+      </c>
+      <c r="D898" t="n">
+        <v>11.8000001907349</v>
+      </c>
+      <c r="E898" t="n">
+        <v>11.8000001907349</v>
+      </c>
+      <c r="F898" t="n">
+        <v>11.8000001907349</v>
+      </c>
+      <c r="G898" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/VLT.MI.xlsx
+++ b/data/VLT.MI.xlsx
@@ -20867,10 +20867,10 @@
     </row>
     <row r="892">
       <c r="A892" s="1" t="n">
-        <v>46273.2916666667</v>
+        <v>46272.2916666667</v>
       </c>
       <c r="B892" t="n">
-        <v>300</v>
+        <v>4500</v>
       </c>
       <c r="C892" t="n">
         <v>11.8000001907349</v>
@@ -20890,10 +20890,10 @@
     </row>
     <row r="893">
       <c r="A893" s="1" t="n">
-        <v>46274.2916666667</v>
+        <v>46273.2916666667</v>
       </c>
       <c r="B893" t="n">
-        <v>4200</v>
+        <v>300</v>
       </c>
       <c r="C893" t="n">
         <v>11.8000001907349</v>
@@ -20913,22 +20913,22 @@
     </row>
     <row r="894">
       <c r="A894" s="1" t="n">
-        <v>46275.2916666667</v>
+        <v>46274.2916666667</v>
       </c>
       <c r="B894" t="n">
-        <v>7200</v>
+        <v>4200</v>
       </c>
       <c r="C894" t="n">
-        <v>12</v>
+        <v>11.8000001907349</v>
       </c>
       <c r="D894" t="n">
-        <v>11.6999998092651</v>
+        <v>11.8000001907349</v>
       </c>
       <c r="E894" t="n">
-        <v>11.8999996185303</v>
+        <v>11.8000001907349</v>
       </c>
       <c r="F894" t="n">
-        <v>11.8999996185303</v>
+        <v>11.8000001907349</v>
       </c>
       <c r="G894" t="s">
         <v>7</v>
@@ -20936,22 +20936,22 @@
     </row>
     <row r="895">
       <c r="A895" s="1" t="n">
-        <v>46276.2916666667</v>
+        <v>46275.2916666667</v>
       </c>
       <c r="B895" t="n">
-        <v>600</v>
+        <v>7200</v>
       </c>
       <c r="C895" t="n">
-        <v>11.8000001907349</v>
+        <v>12</v>
       </c>
       <c r="D895" t="n">
-        <v>11.8000001907349</v>
+        <v>11.6999998092651</v>
       </c>
       <c r="E895" t="n">
-        <v>11.8000001907349</v>
+        <v>11.8999996185303</v>
       </c>
       <c r="F895" t="n">
-        <v>11.8000001907349</v>
+        <v>11.8999996185303</v>
       </c>
       <c r="G895" t="s">
         <v>7</v>
@@ -20959,10 +20959,10 @@
     </row>
     <row r="896">
       <c r="A896" s="1" t="n">
-        <v>46279.2916666667</v>
+        <v>46276.2916666667</v>
       </c>
       <c r="B896" t="n">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="C896" t="n">
         <v>11.8000001907349</v>
@@ -20982,10 +20982,10 @@
     </row>
     <row r="897">
       <c r="A897" s="1" t="n">
-        <v>46280.2916666667</v>
+        <v>46279.2916666667</v>
       </c>
       <c r="B897" t="n">
-        <v>3600</v>
+        <v>0</v>
       </c>
       <c r="C897" t="n">
         <v>11.8000001907349</v>
@@ -21005,10 +21005,10 @@
     </row>
     <row r="898">
       <c r="A898" s="1" t="n">
-        <v>46281.2916666667</v>
+        <v>46280.2916666667</v>
       </c>
       <c r="B898" t="n">
-        <v>0</v>
+        <v>3600</v>
       </c>
       <c r="C898" t="n">
         <v>11.8000001907349</v>
@@ -21023,6 +21023,52 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G898" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="899">
+      <c r="A899" s="1" t="n">
+        <v>46281.2916666667</v>
+      </c>
+      <c r="B899" t="n">
+        <v>0</v>
+      </c>
+      <c r="C899" t="n">
+        <v>11.8000001907349</v>
+      </c>
+      <c r="D899" t="n">
+        <v>11.8000001907349</v>
+      </c>
+      <c r="E899" t="n">
+        <v>11.8000001907349</v>
+      </c>
+      <c r="F899" t="n">
+        <v>11.8000001907349</v>
+      </c>
+      <c r="G899" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="900">
+      <c r="A900" s="1" t="n">
+        <v>46283.2916666667</v>
+      </c>
+      <c r="B900" t="n">
+        <v>300</v>
+      </c>
+      <c r="C900" t="n">
+        <v>11.8000001907349</v>
+      </c>
+      <c r="D900" t="n">
+        <v>11.8000001907349</v>
+      </c>
+      <c r="E900" t="n">
+        <v>11.8000001907349</v>
+      </c>
+      <c r="F900" t="n">
+        <v>11.8000001907349</v>
+      </c>
+      <c r="G900" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/VLT.MI.xlsx
+++ b/data/VLT.MI.xlsx
@@ -21051,10 +21051,10 @@
     </row>
     <row r="900">
       <c r="A900" s="1" t="n">
-        <v>46283.2916666667</v>
+        <v>46282.2916666667</v>
       </c>
       <c r="B900" t="n">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="C900" t="n">
         <v>11.8000001907349</v>
@@ -21069,6 +21069,29 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G900" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="901">
+      <c r="A901" s="1" t="n">
+        <v>46283.2916666667</v>
+      </c>
+      <c r="B901" t="n">
+        <v>300</v>
+      </c>
+      <c r="C901" t="n">
+        <v>11.8000001907349</v>
+      </c>
+      <c r="D901" t="n">
+        <v>11.8000001907349</v>
+      </c>
+      <c r="E901" t="n">
+        <v>11.8000001907349</v>
+      </c>
+      <c r="F901" t="n">
+        <v>11.8000001907349</v>
+      </c>
+      <c r="G901" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/VLT.MI.xlsx
+++ b/data/VLT.MI.xlsx
@@ -21095,6 +21095,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="902">
+      <c r="A902" s="1" t="n">
+        <v>46286.2916666667</v>
+      </c>
+      <c r="B902" t="n">
+        <v>0</v>
+      </c>
+      <c r="C902" t="n">
+        <v>11.8000001907349</v>
+      </c>
+      <c r="D902" t="n">
+        <v>11.8000001907349</v>
+      </c>
+      <c r="E902" t="n">
+        <v>11.8000001907349</v>
+      </c>
+      <c r="F902" t="n">
+        <v>11.8000001907349</v>
+      </c>
+      <c r="G902" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/VLT.MI.xlsx
+++ b/data/VLT.MI.xlsx
@@ -21226,7 +21226,9 @@
       <c r="E907" t="n">
         <v>11.8000001907349</v>
       </c>
-      <c r="F907"/>
+      <c r="F907" t="n">
+        <v>11.8000001907349</v>
+      </c>
       <c r="G907" t="s">
         <v>7</v>
       </c>

--- a/data/VLT.MI.xlsx
+++ b/data/VLT.MI.xlsx
@@ -21233,6 +21233,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="908">
+      <c r="A908" s="1" t="n">
+        <v>46294.2916666667</v>
+      </c>
+      <c r="B908" t="n">
+        <v>0</v>
+      </c>
+      <c r="C908" t="n">
+        <v>11.8000001907349</v>
+      </c>
+      <c r="D908" t="n">
+        <v>11.8000001907349</v>
+      </c>
+      <c r="E908" t="n">
+        <v>11.8000001907349</v>
+      </c>
+      <c r="F908" t="n">
+        <v>11.8000001907349</v>
+      </c>
+      <c r="G908" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/VLT.MI.xlsx
+++ b/data/VLT.MI.xlsx
@@ -21256,6 +21256,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="909">
+      <c r="A909" s="1" t="n">
+        <v>46295.2916666667</v>
+      </c>
+      <c r="B909" t="n">
+        <v>0</v>
+      </c>
+      <c r="C909" t="n">
+        <v>11.8000001907349</v>
+      </c>
+      <c r="D909" t="n">
+        <v>11.8000001907349</v>
+      </c>
+      <c r="E909" t="n">
+        <v>11.8000001907349</v>
+      </c>
+      <c r="F909" t="n">
+        <v>11.8000001907349</v>
+      </c>
+      <c r="G909" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/VLT.MI.xlsx
+++ b/data/VLT.MI.xlsx
@@ -21279,6 +21279,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="910">
+      <c r="A910" s="1" t="n">
+        <v>46296.2916666667</v>
+      </c>
+      <c r="B910" t="n">
+        <v>0</v>
+      </c>
+      <c r="C910" t="n">
+        <v>11.8000001907349</v>
+      </c>
+      <c r="D910" t="n">
+        <v>11.8000001907349</v>
+      </c>
+      <c r="E910" t="n">
+        <v>11.8000001907349</v>
+      </c>
+      <c r="F910" t="n">
+        <v>11.8000001907349</v>
+      </c>
+      <c r="G910" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/VLT.MI.xlsx
+++ b/data/VLT.MI.xlsx
@@ -21302,6 +21302,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="911">
+      <c r="A911" s="1" t="n">
+        <v>46297.2916666667</v>
+      </c>
+      <c r="B911" t="n">
+        <v>0</v>
+      </c>
+      <c r="C911" t="n">
+        <v>11.8000001907349</v>
+      </c>
+      <c r="D911" t="n">
+        <v>11.8000001907349</v>
+      </c>
+      <c r="E911" t="n">
+        <v>11.8000001907349</v>
+      </c>
+      <c r="F911" t="n">
+        <v>11.8000001907349</v>
+      </c>
+      <c r="G911" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/VLT.MI.xlsx
+++ b/data/VLT.MI.xlsx
@@ -21325,6 +21325,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="912">
+      <c r="A912" s="1" t="n">
+        <v>46300.2916666667</v>
+      </c>
+      <c r="B912" t="n">
+        <v>0</v>
+      </c>
+      <c r="C912" t="n">
+        <v>11.8000001907349</v>
+      </c>
+      <c r="D912" t="n">
+        <v>11.8000001907349</v>
+      </c>
+      <c r="E912" t="n">
+        <v>11.8000001907349</v>
+      </c>
+      <c r="F912" t="n">
+        <v>11.8000001907349</v>
+      </c>
+      <c r="G912" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/VLT.MI.xlsx
+++ b/data/VLT.MI.xlsx
@@ -21348,6 +21348,50 @@
         <v>7</v>
       </c>
     </row>
+    <row r="913">
+      <c r="A913" s="1" t="n">
+        <v>46301.2916666667</v>
+      </c>
+      <c r="B913" t="n">
+        <v>0</v>
+      </c>
+      <c r="C913" t="n">
+        <v>11.8000001907349</v>
+      </c>
+      <c r="D913" t="n">
+        <v>11.8000001907349</v>
+      </c>
+      <c r="E913" t="n">
+        <v>11.8000001907349</v>
+      </c>
+      <c r="F913" t="n">
+        <v>11.8000001907349</v>
+      </c>
+      <c r="G913" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="914">
+      <c r="A914" s="1" t="n">
+        <v>46302.2916666667</v>
+      </c>
+      <c r="B914" t="n">
+        <v>600</v>
+      </c>
+      <c r="C914" t="n">
+        <v>11.8999996185303</v>
+      </c>
+      <c r="D914" t="n">
+        <v>11.8999996185303</v>
+      </c>
+      <c r="E914" t="n">
+        <v>11.8999996185303</v>
+      </c>
+      <c r="F914"/>
+      <c r="G914" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/VLT.MI.xlsx
+++ b/data/VLT.MI.xlsx
@@ -21387,8 +21387,31 @@
       <c r="E914" t="n">
         <v>11.8999996185303</v>
       </c>
-      <c r="F914"/>
+      <c r="F914" t="n">
+        <v>11.8999996185303</v>
+      </c>
       <c r="G914" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="915">
+      <c r="A915" s="1" t="n">
+        <v>46303.2916666667</v>
+      </c>
+      <c r="B915" t="n">
+        <v>900</v>
+      </c>
+      <c r="C915" t="n">
+        <v>12</v>
+      </c>
+      <c r="D915" t="n">
+        <v>12</v>
+      </c>
+      <c r="E915" t="n">
+        <v>12</v>
+      </c>
+      <c r="F915"/>
+      <c r="G915" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/VLT.MI.xlsx
+++ b/data/VLT.MI.xlsx
@@ -21410,7 +21410,9 @@
       <c r="E915" t="n">
         <v>12</v>
       </c>
-      <c r="F915"/>
+      <c r="F915" t="n">
+        <v>12</v>
+      </c>
       <c r="G915" t="s">
         <v>7</v>
       </c>

--- a/data/VLT.MI.xlsx
+++ b/data/VLT.MI.xlsx
@@ -21440,6 +21440,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="917">
+      <c r="A917" s="1" t="n">
+        <v>46307.2916666667</v>
+      </c>
+      <c r="B917" t="n">
+        <v>600</v>
+      </c>
+      <c r="C917" t="n">
+        <v>11.8999996185303</v>
+      </c>
+      <c r="D917" t="n">
+        <v>11.8999996185303</v>
+      </c>
+      <c r="E917" t="n">
+        <v>11.8999996185303</v>
+      </c>
+      <c r="F917" t="n">
+        <v>11.8999996185303</v>
+      </c>
+      <c r="G917" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/VLT.MI.xlsx
+++ b/data/VLT.MI.xlsx
@@ -21463,6 +21463,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="918">
+      <c r="A918" s="1" t="n">
+        <v>46308.2916666667</v>
+      </c>
+      <c r="B918" t="n">
+        <v>3900</v>
+      </c>
+      <c r="C918" t="n">
+        <v>12</v>
+      </c>
+      <c r="D918" t="n">
+        <v>12</v>
+      </c>
+      <c r="E918" t="n">
+        <v>12</v>
+      </c>
+      <c r="F918" t="n">
+        <v>12</v>
+      </c>
+      <c r="G918" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/VLT.MI.xlsx
+++ b/data/VLT.MI.xlsx
@@ -21486,6 +21486,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="919">
+      <c r="A919" s="1" t="n">
+        <v>46309.2916666667</v>
+      </c>
+      <c r="B919" t="n">
+        <v>0</v>
+      </c>
+      <c r="C919" t="n">
+        <v>12</v>
+      </c>
+      <c r="D919" t="n">
+        <v>12</v>
+      </c>
+      <c r="E919" t="n">
+        <v>12</v>
+      </c>
+      <c r="F919" t="n">
+        <v>12</v>
+      </c>
+      <c r="G919" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/VLT.MI.xlsx
+++ b/data/VLT.MI.xlsx
@@ -21509,6 +21509,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="920">
+      <c r="A920" s="1" t="n">
+        <v>46310.2916666667</v>
+      </c>
+      <c r="B920" t="n">
+        <v>0</v>
+      </c>
+      <c r="C920" t="n">
+        <v>12</v>
+      </c>
+      <c r="D920" t="n">
+        <v>12</v>
+      </c>
+      <c r="E920" t="n">
+        <v>12</v>
+      </c>
+      <c r="F920" t="n">
+        <v>12</v>
+      </c>
+      <c r="G920" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/VLT.MI.xlsx
+++ b/data/VLT.MI.xlsx
@@ -543,7 +543,7 @@
         <v>5.69799995422363</v>
       </c>
       <c r="G6" t="n">
-        <v>5.54366254806519</v>
+        <v>5.54366302490234</v>
       </c>
       <c r="H6" t="n">
         <v>18900</v>
@@ -717,7 +717,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G12" t="n">
-        <v>5.02023506164551</v>
+        <v>5.02023553848267</v>
       </c>
       <c r="H12" t="n">
         <v>3300</v>
@@ -804,7 +804,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G15" t="n">
-        <v>5.15644359588623</v>
+        <v>5.15644311904907</v>
       </c>
       <c r="H15" t="n">
         <v>1500</v>
@@ -1094,7 +1094,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G25" t="n">
-        <v>5.19535970687866</v>
+        <v>5.19536018371582</v>
       </c>
       <c r="H25" t="n">
         <v>1800</v>
@@ -1123,7 +1123,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G26" t="n">
-        <v>5.19535970687866</v>
+        <v>5.19536018371582</v>
       </c>
       <c r="H26" t="n">
         <v>0</v>
@@ -1152,7 +1152,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G27" t="n">
-        <v>5.19535970687866</v>
+        <v>5.19536018371582</v>
       </c>
       <c r="H27" t="n">
         <v>0</v>
@@ -1384,7 +1384,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G35" t="n">
-        <v>5.38994216918945</v>
+        <v>5.38994264602661</v>
       </c>
       <c r="H35" t="n">
         <v>300</v>
@@ -1848,7 +1848,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G51" t="n">
-        <v>4.65052795410156</v>
+        <v>4.65052843093872</v>
       </c>
       <c r="H51" t="n">
         <v>1500</v>
@@ -1993,7 +1993,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G56" t="n">
-        <v>4.70890283584595</v>
+        <v>4.70890331268311</v>
       </c>
       <c r="H56" t="n">
         <v>300</v>
@@ -2399,7 +2399,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G70" t="n">
-        <v>4.70890283584595</v>
+        <v>4.70890331268311</v>
       </c>
       <c r="H70" t="n">
         <v>300</v>
@@ -2747,7 +2747,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G82" t="n">
-        <v>4.70890283584595</v>
+        <v>4.70890331268311</v>
       </c>
       <c r="H82" t="n">
         <v>900</v>
@@ -2776,7 +2776,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G83" t="n">
-        <v>4.70890283584595</v>
+        <v>4.70890331268311</v>
       </c>
       <c r="H83" t="n">
         <v>0</v>
@@ -2805,7 +2805,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G84" t="n">
-        <v>4.66025733947754</v>
+        <v>4.66025686264038</v>
       </c>
       <c r="H84" t="n">
         <v>1200</v>
@@ -3298,7 +3298,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G101" t="n">
-        <v>4.70890283584595</v>
+        <v>4.70890331268311</v>
       </c>
       <c r="H101" t="n">
         <v>1200</v>
@@ -3356,7 +3356,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G103" t="n">
-        <v>4.66025733947754</v>
+        <v>4.66025686264038</v>
       </c>
       <c r="H103" t="n">
         <v>300</v>
@@ -3385,7 +3385,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G104" t="n">
-        <v>4.66025733947754</v>
+        <v>4.66025686264038</v>
       </c>
       <c r="H104" t="n">
         <v>0</v>
@@ -3414,7 +3414,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G105" t="n">
-        <v>4.66025733947754</v>
+        <v>4.66025686264038</v>
       </c>
       <c r="H105" t="n">
         <v>0</v>
@@ -3443,7 +3443,7 @@
         <v>4.5</v>
       </c>
       <c r="G106" t="n">
-        <v>4.37811231613159</v>
+        <v>4.37811183929443</v>
       </c>
       <c r="H106" t="n">
         <v>4800</v>
@@ -3472,7 +3472,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G107" t="n">
-        <v>4.47540378570557</v>
+        <v>4.47540330886841</v>
       </c>
       <c r="H107" t="n">
         <v>3600</v>
@@ -3501,7 +3501,7 @@
         <v>4.5</v>
       </c>
       <c r="G108" t="n">
-        <v>4.37811231613159</v>
+        <v>4.37811183929443</v>
       </c>
       <c r="H108" t="n">
         <v>600</v>
@@ -3646,7 +3646,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G113" t="n">
-        <v>4.47540378570557</v>
+        <v>4.47540330886841</v>
       </c>
       <c r="H113" t="n">
         <v>300</v>
@@ -3675,7 +3675,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G114" t="n">
-        <v>4.47540378570557</v>
+        <v>4.47540330886841</v>
       </c>
       <c r="H114" t="n">
         <v>300</v>
@@ -3733,7 +3733,7 @@
         <v>4.53000020980835</v>
       </c>
       <c r="G116" t="n">
-        <v>4.40729999542236</v>
+        <v>4.40729951858521</v>
       </c>
       <c r="H116" t="n">
         <v>2700</v>
@@ -3762,7 +3762,7 @@
         <v>4.53000020980835</v>
       </c>
       <c r="G117" t="n">
-        <v>4.40729999542236</v>
+        <v>4.40729951858521</v>
       </c>
       <c r="H117" t="n">
         <v>0</v>
@@ -4255,7 +4255,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G134" t="n">
-        <v>4.35865354537964</v>
+        <v>4.3586540222168</v>
       </c>
       <c r="H134" t="n">
         <v>600</v>
@@ -4284,7 +4284,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G135" t="n">
-        <v>4.35865354537964</v>
+        <v>4.3586540222168</v>
       </c>
       <c r="H135" t="n">
         <v>0</v>
@@ -4313,7 +4313,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G136" t="n">
-        <v>4.35865354537964</v>
+        <v>4.3586540222168</v>
       </c>
       <c r="H136" t="n">
         <v>0</v>
@@ -4342,7 +4342,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G137" t="n">
-        <v>4.35865354537964</v>
+        <v>4.3586540222168</v>
       </c>
       <c r="H137" t="n">
         <v>0</v>
@@ -4371,7 +4371,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G138" t="n">
-        <v>4.35865354537964</v>
+        <v>4.3586540222168</v>
       </c>
       <c r="H138" t="n">
         <v>0</v>
@@ -4400,7 +4400,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G139" t="n">
-        <v>4.35865354537964</v>
+        <v>4.3586540222168</v>
       </c>
       <c r="H139" t="n">
         <v>0</v>
@@ -4429,7 +4429,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G140" t="n">
-        <v>4.35865354537964</v>
+        <v>4.3586540222168</v>
       </c>
       <c r="H140" t="n">
         <v>3000</v>
@@ -4458,7 +4458,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G141" t="n">
-        <v>4.35865354537964</v>
+        <v>4.3586540222168</v>
       </c>
       <c r="H141" t="n">
         <v>0</v>
@@ -4632,7 +4632,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G147" t="n">
-        <v>4.96186065673828</v>
+        <v>4.96186017990112</v>
       </c>
       <c r="H147" t="n">
         <v>1500</v>
@@ -4661,7 +4661,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G148" t="n">
-        <v>4.73809003829956</v>
+        <v>4.73809051513672</v>
       </c>
       <c r="H148" t="n">
         <v>4500</v>
@@ -4690,7 +4690,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G149" t="n">
-        <v>4.66025733947754</v>
+        <v>4.66025686264038</v>
       </c>
       <c r="H149" t="n">
         <v>2100</v>
@@ -4777,7 +4777,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G152" t="n">
-        <v>4.70890283584595</v>
+        <v>4.70890331268311</v>
       </c>
       <c r="H152" t="n">
         <v>600</v>
@@ -4980,7 +4980,7 @@
         <v>4.5</v>
       </c>
       <c r="G159" t="n">
-        <v>4.37811231613159</v>
+        <v>4.37811183929443</v>
       </c>
       <c r="H159" t="n">
         <v>3900</v>
@@ -5009,7 +5009,7 @@
         <v>4.5</v>
       </c>
       <c r="G160" t="n">
-        <v>4.37811231613159</v>
+        <v>4.37811183929443</v>
       </c>
       <c r="H160" t="n">
         <v>0</v>
@@ -5038,7 +5038,7 @@
         <v>4.5</v>
       </c>
       <c r="G161" t="n">
-        <v>4.37811231613159</v>
+        <v>4.37811183929443</v>
       </c>
       <c r="H161" t="n">
         <v>1800</v>
@@ -5067,7 +5067,7 @@
         <v>4.5</v>
       </c>
       <c r="G162" t="n">
-        <v>4.37811231613159</v>
+        <v>4.37811183929443</v>
       </c>
       <c r="H162" t="n">
         <v>1200</v>
@@ -5212,7 +5212,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G167" t="n">
-        <v>4.47540378570557</v>
+        <v>4.47540330886841</v>
       </c>
       <c r="H167" t="n">
         <v>900</v>
@@ -5241,7 +5241,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G168" t="n">
-        <v>4.47540378570557</v>
+        <v>4.47540330886841</v>
       </c>
       <c r="H168" t="n">
         <v>0</v>
@@ -5270,7 +5270,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G169" t="n">
-        <v>4.47540378570557</v>
+        <v>4.47540330886841</v>
       </c>
       <c r="H169" t="n">
         <v>0</v>
@@ -5299,7 +5299,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G170" t="n">
-        <v>4.47540378570557</v>
+        <v>4.47540330886841</v>
       </c>
       <c r="H170" t="n">
         <v>0</v>
@@ -5328,7 +5328,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G171" t="n">
-        <v>4.47540378570557</v>
+        <v>4.47540330886841</v>
       </c>
       <c r="H171" t="n">
         <v>0</v>
@@ -5357,7 +5357,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G172" t="n">
-        <v>4.47540378570557</v>
+        <v>4.47540330886841</v>
       </c>
       <c r="H172" t="n">
         <v>0</v>
@@ -5386,7 +5386,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G173" t="n">
-        <v>4.47540378570557</v>
+        <v>4.47540330886841</v>
       </c>
       <c r="H173" t="n">
         <v>0</v>
@@ -5415,7 +5415,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G174" t="n">
-        <v>4.47540378570557</v>
+        <v>4.47540330886841</v>
       </c>
       <c r="H174" t="n">
         <v>0</v>
@@ -5560,7 +5560,7 @@
         <v>4.76999998092651</v>
       </c>
       <c r="G179" t="n">
-        <v>4.64079856872559</v>
+        <v>4.64079904556274</v>
       </c>
       <c r="H179" t="n">
         <v>1200</v>
@@ -5618,7 +5618,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G181" t="n">
-        <v>4.68944501876831</v>
+        <v>4.68944454193115</v>
       </c>
       <c r="H181" t="n">
         <v>600</v>
@@ -5647,7 +5647,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G182" t="n">
-        <v>4.68944501876831</v>
+        <v>4.68944454193115</v>
       </c>
       <c r="H182" t="n">
         <v>300</v>
@@ -5676,7 +5676,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G183" t="n">
-        <v>4.68944501876831</v>
+        <v>4.68944454193115</v>
       </c>
       <c r="H183" t="n">
         <v>2400</v>
@@ -5705,7 +5705,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G184" t="n">
-        <v>4.68944501876831</v>
+        <v>4.68944454193115</v>
       </c>
       <c r="H184" t="n">
         <v>0</v>
@@ -5821,7 +5821,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G188" t="n">
-        <v>5.15644359588623</v>
+        <v>5.15644311904907</v>
       </c>
       <c r="H188" t="n">
         <v>600</v>
@@ -6198,7 +6198,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G201" t="n">
-        <v>4.96186065673828</v>
+        <v>4.96186017990112</v>
       </c>
       <c r="H201" t="n">
         <v>600</v>
@@ -6227,7 +6227,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G202" t="n">
-        <v>4.96186065673828</v>
+        <v>4.96186017990112</v>
       </c>
       <c r="H202" t="n">
         <v>300</v>
@@ -6256,7 +6256,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G203" t="n">
-        <v>4.96186065673828</v>
+        <v>4.96186017990112</v>
       </c>
       <c r="H203" t="n">
         <v>300</v>
@@ -6575,7 +6575,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G214" t="n">
-        <v>5.4288592338562</v>
+        <v>5.42885875701904</v>
       </c>
       <c r="H214" t="n">
         <v>3600</v>
@@ -6720,7 +6720,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G219" t="n">
-        <v>5.40940046310425</v>
+        <v>5.40940093994141</v>
       </c>
       <c r="H219" t="n">
         <v>1800</v>
@@ -7445,7 +7445,7 @@
         <v>6.03999996185303</v>
       </c>
       <c r="G244" t="n">
-        <v>5.87639904022217</v>
+        <v>5.87639951705933</v>
       </c>
       <c r="H244" t="n">
         <v>9300</v>
@@ -7909,7 +7909,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G260" t="n">
-        <v>5.64290046691895</v>
+        <v>5.64289999008179</v>
       </c>
       <c r="H260" t="n">
         <v>300</v>
@@ -7938,7 +7938,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G261" t="n">
-        <v>5.64290046691895</v>
+        <v>5.64289999008179</v>
       </c>
       <c r="H261" t="n">
         <v>0</v>
@@ -7967,7 +7967,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G262" t="n">
-        <v>5.64290046691895</v>
+        <v>5.64289999008179</v>
       </c>
       <c r="H262" t="n">
         <v>0</v>
@@ -7996,7 +7996,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G263" t="n">
-        <v>5.64290046691895</v>
+        <v>5.64289999008179</v>
       </c>
       <c r="H263" t="n">
         <v>0</v>
@@ -8025,7 +8025,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G264" t="n">
-        <v>5.64290046691895</v>
+        <v>5.64289999008179</v>
       </c>
       <c r="H264" t="n">
         <v>300</v>
@@ -8054,7 +8054,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G265" t="n">
-        <v>5.64290046691895</v>
+        <v>5.64289999008179</v>
       </c>
       <c r="H265" t="n">
         <v>0</v>
@@ -8112,7 +8112,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G267" t="n">
-        <v>5.64290046691895</v>
+        <v>5.64289999008179</v>
       </c>
       <c r="H267" t="n">
         <v>300</v>
@@ -8141,7 +8141,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G268" t="n">
-        <v>5.64290046691895</v>
+        <v>5.64289999008179</v>
       </c>
       <c r="H268" t="n">
         <v>0</v>
@@ -8315,7 +8315,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G274" t="n">
-        <v>5.72073364257812</v>
+        <v>5.72073316574097</v>
       </c>
       <c r="H274" t="n">
         <v>900</v>
@@ -8489,7 +8489,7 @@
         <v>6.05000019073486</v>
       </c>
       <c r="G280" t="n">
-        <v>5.88612842559814</v>
+        <v>5.8861289024353</v>
       </c>
       <c r="H280" t="n">
         <v>3900</v>
@@ -8576,7 +8576,7 @@
         <v>6.05000019073486</v>
       </c>
       <c r="G283" t="n">
-        <v>5.88612842559814</v>
+        <v>5.8861289024353</v>
       </c>
       <c r="H283" t="n">
         <v>4800</v>
@@ -8605,7 +8605,7 @@
         <v>6.05000019073486</v>
       </c>
       <c r="G284" t="n">
-        <v>5.88612842559814</v>
+        <v>5.8861289024353</v>
       </c>
       <c r="H284" t="n">
         <v>0</v>
@@ -9330,7 +9330,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G309" t="n">
-        <v>5.6915454864502</v>
+        <v>5.69154596328735</v>
       </c>
       <c r="H309" t="n">
         <v>5100</v>
@@ -9359,7 +9359,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G310" t="n">
-        <v>5.6915454864502</v>
+        <v>5.69154596328735</v>
       </c>
       <c r="H310" t="n">
         <v>4200</v>
@@ -9388,7 +9388,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G311" t="n">
-        <v>5.6915454864502</v>
+        <v>5.69154596328735</v>
       </c>
       <c r="H311" t="n">
         <v>3000</v>
@@ -9417,7 +9417,7 @@
         <v>5.75</v>
       </c>
       <c r="G312" t="n">
-        <v>5.59425401687622</v>
+        <v>5.59425449371338</v>
       </c>
       <c r="H312" t="n">
         <v>2400</v>
@@ -9446,7 +9446,7 @@
         <v>5.75</v>
       </c>
       <c r="G313" t="n">
-        <v>5.59425401687622</v>
+        <v>5.59425449371338</v>
       </c>
       <c r="H313" t="n">
         <v>5100</v>
@@ -9475,7 +9475,7 @@
         <v>5.75</v>
       </c>
       <c r="G314" t="n">
-        <v>5.59425401687622</v>
+        <v>5.59425449371338</v>
       </c>
       <c r="H314" t="n">
         <v>0</v>
@@ -9504,7 +9504,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G315" t="n">
-        <v>5.6915454864502</v>
+        <v>5.69154596328735</v>
       </c>
       <c r="H315" t="n">
         <v>2100</v>
@@ -9533,7 +9533,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G316" t="n">
-        <v>5.6915454864502</v>
+        <v>5.69154596328735</v>
       </c>
       <c r="H316" t="n">
         <v>300</v>
@@ -9562,7 +9562,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G317" t="n">
-        <v>5.6915454864502</v>
+        <v>5.69154596328735</v>
       </c>
       <c r="H317" t="n">
         <v>0</v>
@@ -9591,7 +9591,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G318" t="n">
-        <v>5.6915454864502</v>
+        <v>5.69154596328735</v>
       </c>
       <c r="H318" t="n">
         <v>0</v>
@@ -9620,7 +9620,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G319" t="n">
-        <v>5.6915454864502</v>
+        <v>5.69154596328735</v>
       </c>
       <c r="H319" t="n">
         <v>0</v>
@@ -9765,7 +9765,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G324" t="n">
-        <v>5.64290046691895</v>
+        <v>5.64289999008179</v>
       </c>
       <c r="H324" t="n">
         <v>600</v>
@@ -9794,7 +9794,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G325" t="n">
-        <v>5.64290046691895</v>
+        <v>5.64289999008179</v>
       </c>
       <c r="H325" t="n">
         <v>0</v>
@@ -9823,7 +9823,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G326" t="n">
-        <v>5.64290046691895</v>
+        <v>5.64289999008179</v>
       </c>
       <c r="H326" t="n">
         <v>0</v>
@@ -9852,7 +9852,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G327" t="n">
-        <v>5.64290046691895</v>
+        <v>5.64289999008179</v>
       </c>
       <c r="H327" t="n">
         <v>0</v>
@@ -9881,7 +9881,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G328" t="n">
-        <v>5.64290046691895</v>
+        <v>5.64289999008179</v>
       </c>
       <c r="H328" t="n">
         <v>0</v>
@@ -9910,7 +9910,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G329" t="n">
-        <v>5.64290046691895</v>
+        <v>5.64289999008179</v>
       </c>
       <c r="H329" t="n">
         <v>0</v>
@@ -9939,7 +9939,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G330" t="n">
-        <v>5.64290046691895</v>
+        <v>5.64289999008179</v>
       </c>
       <c r="H330" t="n">
         <v>0</v>
@@ -9968,7 +9968,7 @@
         <v>6.05000019073486</v>
       </c>
       <c r="G331" t="n">
-        <v>5.88612842559814</v>
+        <v>5.8861289024353</v>
       </c>
       <c r="H331" t="n">
         <v>1500</v>
@@ -9997,7 +9997,7 @@
         <v>6.05000019073486</v>
       </c>
       <c r="G332" t="n">
-        <v>5.88612842559814</v>
+        <v>5.8861289024353</v>
       </c>
       <c r="H332" t="n">
         <v>0</v>
@@ -10026,7 +10026,7 @@
         <v>6.05000019073486</v>
       </c>
       <c r="G333" t="n">
-        <v>5.88612842559814</v>
+        <v>5.8861289024353</v>
       </c>
       <c r="H333" t="n">
         <v>0</v>
@@ -10055,7 +10055,7 @@
         <v>6.05000019073486</v>
       </c>
       <c r="G334" t="n">
-        <v>5.88612842559814</v>
+        <v>5.8861289024353</v>
       </c>
       <c r="H334" t="n">
         <v>0</v>
@@ -10084,7 +10084,7 @@
         <v>6.05000019073486</v>
       </c>
       <c r="G335" t="n">
-        <v>5.88612842559814</v>
+        <v>5.8861289024353</v>
       </c>
       <c r="H335" t="n">
         <v>0</v>
@@ -10113,7 +10113,7 @@
         <v>6.05000019073486</v>
       </c>
       <c r="G336" t="n">
-        <v>5.88612842559814</v>
+        <v>5.8861289024353</v>
       </c>
       <c r="H336" t="n">
         <v>0</v>
@@ -10142,7 +10142,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G337" t="n">
-        <v>5.64290046691895</v>
+        <v>5.64289999008179</v>
       </c>
       <c r="H337" t="n">
         <v>300</v>
@@ -10316,7 +10316,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G343" t="n">
-        <v>5.64290046691895</v>
+        <v>5.64289999008179</v>
       </c>
       <c r="H343" t="n">
         <v>1200</v>
@@ -10345,7 +10345,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G344" t="n">
-        <v>5.64290046691895</v>
+        <v>5.64289999008179</v>
       </c>
       <c r="H344" t="n">
         <v>0</v>
@@ -10374,7 +10374,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G345" t="n">
-        <v>5.64290046691895</v>
+        <v>5.64289999008179</v>
       </c>
       <c r="H345" t="n">
         <v>300</v>
@@ -10403,7 +10403,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G346" t="n">
-        <v>5.64290046691895</v>
+        <v>5.64289999008179</v>
       </c>
       <c r="H346" t="n">
         <v>0</v>
@@ -11128,7 +11128,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G371" t="n">
-        <v>5.64290046691895</v>
+        <v>5.64289999008179</v>
       </c>
       <c r="H371" t="n">
         <v>300</v>
@@ -11157,7 +11157,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G372" t="n">
-        <v>5.64290046691895</v>
+        <v>5.64289999008179</v>
       </c>
       <c r="H372" t="n">
         <v>0</v>
@@ -11186,7 +11186,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G373" t="n">
-        <v>5.64290046691895</v>
+        <v>5.64289999008179</v>
       </c>
       <c r="H373" t="n">
         <v>0</v>
@@ -11215,7 +11215,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G374" t="n">
-        <v>5.64290046691895</v>
+        <v>5.64289999008179</v>
       </c>
       <c r="H374" t="n">
         <v>0</v>
@@ -11244,7 +11244,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G375" t="n">
-        <v>5.64290046691895</v>
+        <v>5.64289999008179</v>
       </c>
       <c r="H375" t="n">
         <v>600</v>
@@ -11273,7 +11273,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G376" t="n">
-        <v>5.64290046691895</v>
+        <v>5.64289999008179</v>
       </c>
       <c r="H376" t="n">
         <v>0</v>
@@ -11302,7 +11302,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G377" t="n">
-        <v>5.64290046691895</v>
+        <v>5.64289999008179</v>
       </c>
       <c r="H377" t="n">
         <v>0</v>
@@ -11331,7 +11331,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G378" t="n">
-        <v>5.64290046691895</v>
+        <v>5.64289999008179</v>
       </c>
       <c r="H378" t="n">
         <v>0</v>
@@ -11360,7 +11360,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G379" t="n">
-        <v>5.64290046691895</v>
+        <v>5.64289999008179</v>
       </c>
       <c r="H379" t="n">
         <v>0</v>
@@ -11389,7 +11389,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G380" t="n">
-        <v>5.64290046691895</v>
+        <v>5.64289999008179</v>
       </c>
       <c r="H380" t="n">
         <v>0</v>
@@ -11650,7 +11650,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G389" t="n">
-        <v>5.6915454864502</v>
+        <v>5.69154596328735</v>
       </c>
       <c r="H389" t="n">
         <v>300</v>
@@ -11679,7 +11679,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G390" t="n">
-        <v>5.6915454864502</v>
+        <v>5.69154596328735</v>
       </c>
       <c r="H390" t="n">
         <v>0</v>
@@ -11708,7 +11708,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G391" t="n">
-        <v>5.6915454864502</v>
+        <v>5.69154596328735</v>
       </c>
       <c r="H391" t="n">
         <v>0</v>
@@ -11940,7 +11940,7 @@
         <v>5.75</v>
       </c>
       <c r="G399" t="n">
-        <v>5.59425401687622</v>
+        <v>5.59425449371338</v>
       </c>
       <c r="H399" t="n">
         <v>1500</v>
@@ -11969,7 +11969,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G400" t="n">
-        <v>5.6915454864502</v>
+        <v>5.69154596328735</v>
       </c>
       <c r="H400" t="n">
         <v>1200</v>
@@ -11998,7 +11998,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G401" t="n">
-        <v>5.6915454864502</v>
+        <v>5.69154596328735</v>
       </c>
       <c r="H401" t="n">
         <v>4500</v>
@@ -12027,7 +12027,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G402" t="n">
-        <v>5.6915454864502</v>
+        <v>5.69154596328735</v>
       </c>
       <c r="H402" t="n">
         <v>0</v>
@@ -12056,7 +12056,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G403" t="n">
-        <v>5.6915454864502</v>
+        <v>5.69154596328735</v>
       </c>
       <c r="H403" t="n">
         <v>0</v>
@@ -12085,7 +12085,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G404" t="n">
-        <v>5.6915454864502</v>
+        <v>5.69154596328735</v>
       </c>
       <c r="H404" t="n">
         <v>1500</v>
@@ -12114,7 +12114,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G405" t="n">
-        <v>5.6915454864502</v>
+        <v>5.69154596328735</v>
       </c>
       <c r="H405" t="n">
         <v>600</v>
@@ -12143,7 +12143,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G406" t="n">
-        <v>5.6915454864502</v>
+        <v>5.69154596328735</v>
       </c>
       <c r="H406" t="n">
         <v>0</v>
@@ -12172,7 +12172,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G407" t="n">
-        <v>5.6915454864502</v>
+        <v>5.69154596328735</v>
       </c>
       <c r="H407" t="n">
         <v>600</v>
@@ -12201,7 +12201,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G408" t="n">
-        <v>5.6915454864502</v>
+        <v>5.69154596328735</v>
       </c>
       <c r="H408" t="n">
         <v>0</v>
@@ -12230,7 +12230,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G409" t="n">
-        <v>5.64290046691895</v>
+        <v>5.64289999008179</v>
       </c>
       <c r="H409" t="n">
         <v>1200</v>
@@ -12259,7 +12259,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G410" t="n">
-        <v>5.64290046691895</v>
+        <v>5.64289999008179</v>
       </c>
       <c r="H410" t="n">
         <v>0</v>
@@ -12288,7 +12288,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G411" t="n">
-        <v>5.64290046691895</v>
+        <v>5.64289999008179</v>
       </c>
       <c r="H411" t="n">
         <v>4800</v>
@@ -12317,7 +12317,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G412" t="n">
-        <v>5.64290046691895</v>
+        <v>5.64289999008179</v>
       </c>
       <c r="H412" t="n">
         <v>0</v>
@@ -12346,7 +12346,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G413" t="n">
-        <v>5.64290046691895</v>
+        <v>5.64289999008179</v>
       </c>
       <c r="H413" t="n">
         <v>0</v>
@@ -12375,7 +12375,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G414" t="n">
-        <v>5.64290046691895</v>
+        <v>5.64289999008179</v>
       </c>
       <c r="H414" t="n">
         <v>0</v>
@@ -12404,7 +12404,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G415" t="n">
-        <v>5.64290046691895</v>
+        <v>5.64289999008179</v>
       </c>
       <c r="H415" t="n">
         <v>0</v>
@@ -12462,7 +12462,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G417" t="n">
-        <v>5.6915454864502</v>
+        <v>5.69154596328735</v>
       </c>
       <c r="H417" t="n">
         <v>300</v>
@@ -12491,7 +12491,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G418" t="n">
-        <v>5.6915454864502</v>
+        <v>5.69154596328735</v>
       </c>
       <c r="H418" t="n">
         <v>0</v>
@@ -12520,7 +12520,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G419" t="n">
-        <v>5.6915454864502</v>
+        <v>5.69154596328735</v>
       </c>
       <c r="H419" t="n">
         <v>0</v>
@@ -12549,7 +12549,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G420" t="n">
-        <v>5.6915454864502</v>
+        <v>5.69154596328735</v>
       </c>
       <c r="H420" t="n">
         <v>0</v>
@@ -12578,7 +12578,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G421" t="n">
-        <v>5.6915454864502</v>
+        <v>5.69154596328735</v>
       </c>
       <c r="H421" t="n">
         <v>0</v>
@@ -12607,7 +12607,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G422" t="n">
-        <v>5.6915454864502</v>
+        <v>5.69154596328735</v>
       </c>
       <c r="H422" t="n">
         <v>0</v>
@@ -12665,7 +12665,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G424" t="n">
-        <v>5.6915454864502</v>
+        <v>5.69154596328735</v>
       </c>
       <c r="H424" t="n">
         <v>300</v>
@@ -12694,7 +12694,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G425" t="n">
-        <v>5.6915454864502</v>
+        <v>5.69154596328735</v>
       </c>
       <c r="H425" t="n">
         <v>0</v>
@@ -12723,7 +12723,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G426" t="n">
-        <v>5.64290046691895</v>
+        <v>5.64289999008179</v>
       </c>
       <c r="H426" t="n">
         <v>900</v>
@@ -12810,7 +12810,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G429" t="n">
-        <v>5.64290046691895</v>
+        <v>5.64289999008179</v>
       </c>
       <c r="H429" t="n">
         <v>1200</v>
@@ -12839,7 +12839,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G430" t="n">
-        <v>5.64290046691895</v>
+        <v>5.64289999008179</v>
       </c>
       <c r="H430" t="n">
         <v>300</v>
@@ -12868,7 +12868,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G431" t="n">
-        <v>5.64290046691895</v>
+        <v>5.64289999008179</v>
       </c>
       <c r="H431" t="n">
         <v>600</v>
@@ -12897,7 +12897,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G432" t="n">
-        <v>5.64290046691895</v>
+        <v>5.64289999008179</v>
       </c>
       <c r="H432" t="n">
         <v>0</v>
@@ -12926,7 +12926,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G433" t="n">
-        <v>5.64290046691895</v>
+        <v>5.64289999008179</v>
       </c>
       <c r="H433" t="n">
         <v>0</v>
@@ -12955,7 +12955,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G434" t="n">
-        <v>5.64290046691895</v>
+        <v>5.64289999008179</v>
       </c>
       <c r="H434" t="n">
         <v>0</v>
@@ -12984,7 +12984,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G435" t="n">
-        <v>5.64290046691895</v>
+        <v>5.64289999008179</v>
       </c>
       <c r="H435" t="n">
         <v>0</v>
@@ -13013,7 +13013,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G436" t="n">
-        <v>5.64290046691895</v>
+        <v>5.64289999008179</v>
       </c>
       <c r="H436" t="n">
         <v>0</v>
@@ -13042,7 +13042,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G437" t="n">
-        <v>5.64290046691895</v>
+        <v>5.64289999008179</v>
       </c>
       <c r="H437" t="n">
         <v>0</v>
@@ -13071,7 +13071,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G438" t="n">
-        <v>5.64290046691895</v>
+        <v>5.64289999008179</v>
       </c>
       <c r="H438" t="n">
         <v>0</v>
@@ -13100,7 +13100,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G439" t="n">
-        <v>5.64290046691895</v>
+        <v>5.64289999008179</v>
       </c>
       <c r="H439" t="n">
         <v>0</v>
@@ -13129,7 +13129,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G440" t="n">
-        <v>5.64290046691895</v>
+        <v>5.64289999008179</v>
       </c>
       <c r="H440" t="n">
         <v>0</v>
@@ -13158,7 +13158,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G441" t="n">
-        <v>5.64290046691895</v>
+        <v>5.64289999008179</v>
       </c>
       <c r="H441" t="n">
         <v>0</v>
@@ -13187,7 +13187,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G442" t="n">
-        <v>5.64290046691895</v>
+        <v>5.64289999008179</v>
       </c>
       <c r="H442" t="n">
         <v>0</v>
@@ -13216,7 +13216,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G443" t="n">
-        <v>5.64290046691895</v>
+        <v>5.64289999008179</v>
       </c>
       <c r="H443" t="n">
         <v>0</v>
@@ -13419,7 +13419,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G450" t="n">
-        <v>5.64290046691895</v>
+        <v>5.64289999008179</v>
       </c>
       <c r="H450" t="n">
         <v>4500</v>
@@ -13506,7 +13506,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G453" t="n">
-        <v>5.6915454864502</v>
+        <v>5.69154596328735</v>
       </c>
       <c r="H453" t="n">
         <v>900</v>
@@ -13535,7 +13535,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G454" t="n">
-        <v>5.6915454864502</v>
+        <v>5.69154596328735</v>
       </c>
       <c r="H454" t="n">
         <v>0</v>
@@ -13680,7 +13680,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G459" t="n">
-        <v>6.37258529663086</v>
+        <v>6.37258577346802</v>
       </c>
       <c r="H459" t="n">
         <v>1500</v>
@@ -13709,7 +13709,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G460" t="n">
-        <v>6.37258529663086</v>
+        <v>6.37258577346802</v>
       </c>
       <c r="H460" t="n">
         <v>0</v>
@@ -13738,7 +13738,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G461" t="n">
-        <v>6.37258529663086</v>
+        <v>6.37258577346802</v>
       </c>
       <c r="H461" t="n">
         <v>0</v>
@@ -13767,7 +13767,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G462" t="n">
-        <v>6.37258529663086</v>
+        <v>6.37258577346802</v>
       </c>
       <c r="H462" t="n">
         <v>0</v>
@@ -13796,7 +13796,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G463" t="n">
-        <v>6.37258529663086</v>
+        <v>6.37258577346802</v>
       </c>
       <c r="H463" t="n">
         <v>0</v>
@@ -13825,7 +13825,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G464" t="n">
-        <v>6.37258529663086</v>
+        <v>6.37258577346802</v>
       </c>
       <c r="H464" t="n">
         <v>300</v>
@@ -13854,7 +13854,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G465" t="n">
-        <v>6.37258529663086</v>
+        <v>6.37258577346802</v>
       </c>
       <c r="H465" t="n">
         <v>4800</v>
@@ -13912,7 +13912,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G467" t="n">
-        <v>6.42123126983643</v>
+        <v>6.42123079299927</v>
       </c>
       <c r="H467" t="n">
         <v>6900</v>
@@ -14028,7 +14028,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G471" t="n">
-        <v>6.37258529663086</v>
+        <v>6.37258577346802</v>
       </c>
       <c r="H471" t="n">
         <v>600</v>
@@ -14057,7 +14057,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G472" t="n">
-        <v>6.22664833068848</v>
+        <v>6.22664880752563</v>
       </c>
       <c r="H472" t="n">
         <v>600</v>
@@ -14086,7 +14086,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G473" t="n">
-        <v>6.22664833068848</v>
+        <v>6.22664880752563</v>
       </c>
       <c r="H473" t="n">
         <v>0</v>
@@ -14115,7 +14115,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G474" t="n">
-        <v>6.22664833068848</v>
+        <v>6.22664880752563</v>
       </c>
       <c r="H474" t="n">
         <v>0</v>
@@ -14144,7 +14144,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G475" t="n">
-        <v>6.22664833068848</v>
+        <v>6.22664880752563</v>
       </c>
       <c r="H475" t="n">
         <v>0</v>
@@ -14173,7 +14173,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G476" t="n">
-        <v>6.22664833068848</v>
+        <v>6.22664880752563</v>
       </c>
       <c r="H476" t="n">
         <v>0</v>
@@ -14202,7 +14202,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G477" t="n">
-        <v>6.22664833068848</v>
+        <v>6.22664880752563</v>
       </c>
       <c r="H477" t="n">
         <v>0</v>
@@ -14231,7 +14231,7 @@
         <v>6.65000009536743</v>
       </c>
       <c r="G478" t="n">
-        <v>6.46987676620483</v>
+        <v>6.46987724304199</v>
       </c>
       <c r="H478" t="n">
         <v>2400</v>
@@ -14289,7 +14289,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G480" t="n">
-        <v>6.37258529663086</v>
+        <v>6.37258577346802</v>
       </c>
       <c r="H480" t="n">
         <v>1800</v>
@@ -14347,7 +14347,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G482" t="n">
-        <v>6.22664833068848</v>
+        <v>6.22664880752563</v>
       </c>
       <c r="H482" t="n">
         <v>3000</v>
@@ -14376,7 +14376,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G483" t="n">
-        <v>6.22664833068848</v>
+        <v>6.22664880752563</v>
       </c>
       <c r="H483" t="n">
         <v>0</v>
@@ -14405,7 +14405,7 @@
         <v>6.65000009536743</v>
       </c>
       <c r="G484" t="n">
-        <v>6.46987676620483</v>
+        <v>6.46987724304199</v>
       </c>
       <c r="H484" t="n">
         <v>2400</v>
@@ -14434,7 +14434,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G485" t="n">
-        <v>6.22664833068848</v>
+        <v>6.22664880752563</v>
       </c>
       <c r="H485" t="n">
         <v>1500</v>
@@ -14521,7 +14521,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G488" t="n">
-        <v>6.22664833068848</v>
+        <v>6.22664880752563</v>
       </c>
       <c r="H488" t="n">
         <v>4200</v>
@@ -14956,7 +14956,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G503" t="n">
-        <v>6.37258529663086</v>
+        <v>6.37258577346802</v>
       </c>
       <c r="H503" t="n">
         <v>1800</v>
@@ -14985,7 +14985,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G504" t="n">
-        <v>6.22664833068848</v>
+        <v>6.22664880752563</v>
       </c>
       <c r="H504" t="n">
         <v>2700</v>
@@ -15014,7 +15014,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G505" t="n">
-        <v>6.22664833068848</v>
+        <v>6.22664880752563</v>
       </c>
       <c r="H505" t="n">
         <v>0</v>
@@ -15043,7 +15043,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G506" t="n">
-        <v>6.22664833068848</v>
+        <v>6.22664880752563</v>
       </c>
       <c r="H506" t="n">
         <v>0</v>
@@ -15710,7 +15710,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G529" t="n">
-        <v>6.22664833068848</v>
+        <v>6.22664880752563</v>
       </c>
       <c r="H529" t="n">
         <v>3300</v>
@@ -15768,7 +15768,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G531" t="n">
-        <v>6.42123126983643</v>
+        <v>6.42123079299927</v>
       </c>
       <c r="H531" t="n">
         <v>1200</v>
@@ -15826,7 +15826,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G533" t="n">
-        <v>5.6915454864502</v>
+        <v>5.69154596328735</v>
       </c>
       <c r="H533" t="n">
         <v>8700</v>
@@ -15855,7 +15855,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G534" t="n">
-        <v>5.6915454864502</v>
+        <v>5.69154596328735</v>
       </c>
       <c r="H534" t="n">
         <v>300</v>
@@ -15884,7 +15884,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G535" t="n">
-        <v>5.6915454864502</v>
+        <v>5.69154596328735</v>
       </c>
       <c r="H535" t="n">
         <v>0</v>
@@ -15913,7 +15913,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G536" t="n">
-        <v>5.64290046691895</v>
+        <v>5.64289999008179</v>
       </c>
       <c r="H536" t="n">
         <v>2400</v>
@@ -16232,7 +16232,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G547" t="n">
-        <v>6.22664833068848</v>
+        <v>6.22664880752563</v>
       </c>
       <c r="H547" t="n">
         <v>1500</v>
@@ -16261,7 +16261,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G548" t="n">
-        <v>6.22664833068848</v>
+        <v>6.22664880752563</v>
       </c>
       <c r="H548" t="n">
         <v>1200</v>
@@ -16290,7 +16290,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G549" t="n">
-        <v>6.22664833068848</v>
+        <v>6.22664880752563</v>
       </c>
       <c r="H549" t="n">
         <v>1200</v>
@@ -16348,7 +16348,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G551" t="n">
-        <v>6.37258529663086</v>
+        <v>6.37258577346802</v>
       </c>
       <c r="H551" t="n">
         <v>60600</v>
@@ -16377,7 +16377,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G552" t="n">
-        <v>6.37258529663086</v>
+        <v>6.37258577346802</v>
       </c>
       <c r="H552" t="n">
         <v>0</v>
@@ -16406,7 +16406,7 @@
         <v>6.65000009536743</v>
       </c>
       <c r="G553" t="n">
-        <v>6.46987676620483</v>
+        <v>6.46987724304199</v>
       </c>
       <c r="H553" t="n">
         <v>300</v>
@@ -16435,7 +16435,7 @@
         <v>6.65000009536743</v>
       </c>
       <c r="G554" t="n">
-        <v>6.46987676620483</v>
+        <v>6.46987724304199</v>
       </c>
       <c r="H554" t="n">
         <v>0</v>
@@ -27084,6 +27084,35 @@
         <v>0</v>
       </c>
       <c r="I921" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="922">
+      <c r="A922" t="s">
+        <v>9</v>
+      </c>
+      <c r="B922" s="1" t="n">
+        <v>46314.2916666667</v>
+      </c>
+      <c r="C922" t="n">
+        <v>12</v>
+      </c>
+      <c r="D922" t="n">
+        <v>12</v>
+      </c>
+      <c r="E922" t="n">
+        <v>12</v>
+      </c>
+      <c r="F922" t="n">
+        <v>12</v>
+      </c>
+      <c r="G922" t="n">
+        <v>12</v>
+      </c>
+      <c r="H922" t="n">
+        <v>0</v>
+      </c>
+      <c r="I922" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/VLT.MI.xlsx
+++ b/data/VLT.MI.xlsx
@@ -543,7 +543,7 @@
         <v>5.69799995422363</v>
       </c>
       <c r="G6" t="n">
-        <v>5.54366302490234</v>
+        <v>5.54366254806519</v>
       </c>
       <c r="H6" t="n">
         <v>18900</v>
@@ -717,7 +717,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G12" t="n">
-        <v>5.02023553848267</v>
+        <v>5.02023506164551</v>
       </c>
       <c r="H12" t="n">
         <v>3300</v>
@@ -804,7 +804,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G15" t="n">
-        <v>5.15644311904907</v>
+        <v>5.15644359588623</v>
       </c>
       <c r="H15" t="n">
         <v>1500</v>
@@ -1094,7 +1094,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G25" t="n">
-        <v>5.19536018371582</v>
+        <v>5.19535970687866</v>
       </c>
       <c r="H25" t="n">
         <v>1800</v>
@@ -1123,7 +1123,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G26" t="n">
-        <v>5.19536018371582</v>
+        <v>5.19535970687866</v>
       </c>
       <c r="H26" t="n">
         <v>0</v>
@@ -1152,7 +1152,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G27" t="n">
-        <v>5.19536018371582</v>
+        <v>5.19535970687866</v>
       </c>
       <c r="H27" t="n">
         <v>0</v>
@@ -1384,7 +1384,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G35" t="n">
-        <v>5.38994264602661</v>
+        <v>5.38994216918945</v>
       </c>
       <c r="H35" t="n">
         <v>300</v>
@@ -1848,7 +1848,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G51" t="n">
-        <v>4.65052843093872</v>
+        <v>4.65052795410156</v>
       </c>
       <c r="H51" t="n">
         <v>1500</v>
@@ -1993,7 +1993,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G56" t="n">
-        <v>4.70890331268311</v>
+        <v>4.70890283584595</v>
       </c>
       <c r="H56" t="n">
         <v>300</v>
@@ -2399,7 +2399,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G70" t="n">
-        <v>4.70890331268311</v>
+        <v>4.70890283584595</v>
       </c>
       <c r="H70" t="n">
         <v>300</v>
@@ -2747,7 +2747,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G82" t="n">
-        <v>4.70890331268311</v>
+        <v>4.70890283584595</v>
       </c>
       <c r="H82" t="n">
         <v>900</v>
@@ -2776,7 +2776,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G83" t="n">
-        <v>4.70890331268311</v>
+        <v>4.70890283584595</v>
       </c>
       <c r="H83" t="n">
         <v>0</v>
@@ -2805,7 +2805,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G84" t="n">
-        <v>4.66025686264038</v>
+        <v>4.66025733947754</v>
       </c>
       <c r="H84" t="n">
         <v>1200</v>
@@ -3298,7 +3298,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G101" t="n">
-        <v>4.70890331268311</v>
+        <v>4.70890283584595</v>
       </c>
       <c r="H101" t="n">
         <v>1200</v>
@@ -3356,7 +3356,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G103" t="n">
-        <v>4.66025686264038</v>
+        <v>4.66025733947754</v>
       </c>
       <c r="H103" t="n">
         <v>300</v>
@@ -3385,7 +3385,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G104" t="n">
-        <v>4.66025686264038</v>
+        <v>4.66025733947754</v>
       </c>
       <c r="H104" t="n">
         <v>0</v>
@@ -3414,7 +3414,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G105" t="n">
-        <v>4.66025686264038</v>
+        <v>4.66025733947754</v>
       </c>
       <c r="H105" t="n">
         <v>0</v>
@@ -3443,7 +3443,7 @@
         <v>4.5</v>
       </c>
       <c r="G106" t="n">
-        <v>4.37811183929443</v>
+        <v>4.37811231613159</v>
       </c>
       <c r="H106" t="n">
         <v>4800</v>
@@ -3472,7 +3472,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G107" t="n">
-        <v>4.47540330886841</v>
+        <v>4.47540378570557</v>
       </c>
       <c r="H107" t="n">
         <v>3600</v>
@@ -3501,7 +3501,7 @@
         <v>4.5</v>
       </c>
       <c r="G108" t="n">
-        <v>4.37811183929443</v>
+        <v>4.37811231613159</v>
       </c>
       <c r="H108" t="n">
         <v>600</v>
@@ -3646,7 +3646,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G113" t="n">
-        <v>4.47540330886841</v>
+        <v>4.47540378570557</v>
       </c>
       <c r="H113" t="n">
         <v>300</v>
@@ -3675,7 +3675,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G114" t="n">
-        <v>4.47540330886841</v>
+        <v>4.47540378570557</v>
       </c>
       <c r="H114" t="n">
         <v>300</v>
@@ -3733,7 +3733,7 @@
         <v>4.53000020980835</v>
       </c>
       <c r="G116" t="n">
-        <v>4.40729951858521</v>
+        <v>4.40729999542236</v>
       </c>
       <c r="H116" t="n">
         <v>2700</v>
@@ -3762,7 +3762,7 @@
         <v>4.53000020980835</v>
       </c>
       <c r="G117" t="n">
-        <v>4.40729951858521</v>
+        <v>4.40729999542236</v>
       </c>
       <c r="H117" t="n">
         <v>0</v>
@@ -4255,7 +4255,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G134" t="n">
-        <v>4.3586540222168</v>
+        <v>4.35865354537964</v>
       </c>
       <c r="H134" t="n">
         <v>600</v>
@@ -4284,7 +4284,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G135" t="n">
-        <v>4.3586540222168</v>
+        <v>4.35865354537964</v>
       </c>
       <c r="H135" t="n">
         <v>0</v>
@@ -4313,7 +4313,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G136" t="n">
-        <v>4.3586540222168</v>
+        <v>4.35865354537964</v>
       </c>
       <c r="H136" t="n">
         <v>0</v>
@@ -4342,7 +4342,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G137" t="n">
-        <v>4.3586540222168</v>
+        <v>4.35865354537964</v>
       </c>
       <c r="H137" t="n">
         <v>0</v>
@@ -4371,7 +4371,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G138" t="n">
-        <v>4.3586540222168</v>
+        <v>4.35865354537964</v>
       </c>
       <c r="H138" t="n">
         <v>0</v>
@@ -4400,7 +4400,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G139" t="n">
-        <v>4.3586540222168</v>
+        <v>4.35865354537964</v>
       </c>
       <c r="H139" t="n">
         <v>0</v>
@@ -4429,7 +4429,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G140" t="n">
-        <v>4.3586540222168</v>
+        <v>4.35865354537964</v>
       </c>
       <c r="H140" t="n">
         <v>3000</v>
@@ -4458,7 +4458,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G141" t="n">
-        <v>4.3586540222168</v>
+        <v>4.35865354537964</v>
       </c>
       <c r="H141" t="n">
         <v>0</v>
@@ -4632,7 +4632,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G147" t="n">
-        <v>4.96186017990112</v>
+        <v>4.96186065673828</v>
       </c>
       <c r="H147" t="n">
         <v>1500</v>
@@ -4661,7 +4661,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G148" t="n">
-        <v>4.73809051513672</v>
+        <v>4.73809003829956</v>
       </c>
       <c r="H148" t="n">
         <v>4500</v>
@@ -4690,7 +4690,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G149" t="n">
-        <v>4.66025686264038</v>
+        <v>4.66025733947754</v>
       </c>
       <c r="H149" t="n">
         <v>2100</v>
@@ -4777,7 +4777,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G152" t="n">
-        <v>4.70890331268311</v>
+        <v>4.70890283584595</v>
       </c>
       <c r="H152" t="n">
         <v>600</v>
@@ -4980,7 +4980,7 @@
         <v>4.5</v>
       </c>
       <c r="G159" t="n">
-        <v>4.37811183929443</v>
+        <v>4.37811231613159</v>
       </c>
       <c r="H159" t="n">
         <v>3900</v>
@@ -5009,7 +5009,7 @@
         <v>4.5</v>
       </c>
       <c r="G160" t="n">
-        <v>4.37811183929443</v>
+        <v>4.37811231613159</v>
       </c>
       <c r="H160" t="n">
         <v>0</v>
@@ -5038,7 +5038,7 @@
         <v>4.5</v>
       </c>
       <c r="G161" t="n">
-        <v>4.37811183929443</v>
+        <v>4.37811231613159</v>
       </c>
       <c r="H161" t="n">
         <v>1800</v>
@@ -5067,7 +5067,7 @@
         <v>4.5</v>
       </c>
       <c r="G162" t="n">
-        <v>4.37811183929443</v>
+        <v>4.37811231613159</v>
       </c>
       <c r="H162" t="n">
         <v>1200</v>
@@ -5212,7 +5212,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G167" t="n">
-        <v>4.47540330886841</v>
+        <v>4.47540378570557</v>
       </c>
       <c r="H167" t="n">
         <v>900</v>
@@ -5241,7 +5241,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G168" t="n">
-        <v>4.47540330886841</v>
+        <v>4.47540378570557</v>
       </c>
       <c r="H168" t="n">
         <v>0</v>
@@ -5270,7 +5270,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G169" t="n">
-        <v>4.47540330886841</v>
+        <v>4.47540378570557</v>
       </c>
       <c r="H169" t="n">
         <v>0</v>
@@ -5299,7 +5299,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G170" t="n">
-        <v>4.47540330886841</v>
+        <v>4.47540378570557</v>
       </c>
       <c r="H170" t="n">
         <v>0</v>
@@ -5328,7 +5328,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G171" t="n">
-        <v>4.47540330886841</v>
+        <v>4.47540378570557</v>
       </c>
       <c r="H171" t="n">
         <v>0</v>
@@ -5357,7 +5357,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G172" t="n">
-        <v>4.47540330886841</v>
+        <v>4.47540378570557</v>
       </c>
       <c r="H172" t="n">
         <v>0</v>
@@ -5386,7 +5386,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G173" t="n">
-        <v>4.47540330886841</v>
+        <v>4.47540378570557</v>
       </c>
       <c r="H173" t="n">
         <v>0</v>
@@ -5415,7 +5415,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G174" t="n">
-        <v>4.47540330886841</v>
+        <v>4.47540378570557</v>
       </c>
       <c r="H174" t="n">
         <v>0</v>
@@ -5560,7 +5560,7 @@
         <v>4.76999998092651</v>
       </c>
       <c r="G179" t="n">
-        <v>4.64079904556274</v>
+        <v>4.64079856872559</v>
       </c>
       <c r="H179" t="n">
         <v>1200</v>
@@ -5618,7 +5618,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G181" t="n">
-        <v>4.68944454193115</v>
+        <v>4.68944501876831</v>
       </c>
       <c r="H181" t="n">
         <v>600</v>
@@ -5647,7 +5647,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G182" t="n">
-        <v>4.68944454193115</v>
+        <v>4.68944501876831</v>
       </c>
       <c r="H182" t="n">
         <v>300</v>
@@ -5676,7 +5676,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G183" t="n">
-        <v>4.68944454193115</v>
+        <v>4.68944501876831</v>
       </c>
       <c r="H183" t="n">
         <v>2400</v>
@@ -5705,7 +5705,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G184" t="n">
-        <v>4.68944454193115</v>
+        <v>4.68944501876831</v>
       </c>
       <c r="H184" t="n">
         <v>0</v>
@@ -5821,7 +5821,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G188" t="n">
-        <v>5.15644311904907</v>
+        <v>5.15644359588623</v>
       </c>
       <c r="H188" t="n">
         <v>600</v>
@@ -6198,7 +6198,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G201" t="n">
-        <v>4.96186017990112</v>
+        <v>4.96186065673828</v>
       </c>
       <c r="H201" t="n">
         <v>600</v>
@@ -6227,7 +6227,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G202" t="n">
-        <v>4.96186017990112</v>
+        <v>4.96186065673828</v>
       </c>
       <c r="H202" t="n">
         <v>300</v>
@@ -6256,7 +6256,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G203" t="n">
-        <v>4.96186017990112</v>
+        <v>4.96186065673828</v>
       </c>
       <c r="H203" t="n">
         <v>300</v>
@@ -6575,7 +6575,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G214" t="n">
-        <v>5.42885875701904</v>
+        <v>5.4288592338562</v>
       </c>
       <c r="H214" t="n">
         <v>3600</v>
@@ -6720,7 +6720,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G219" t="n">
-        <v>5.40940093994141</v>
+        <v>5.40940046310425</v>
       </c>
       <c r="H219" t="n">
         <v>1800</v>
@@ -7445,7 +7445,7 @@
         <v>6.03999996185303</v>
       </c>
       <c r="G244" t="n">
-        <v>5.87639951705933</v>
+        <v>5.87639904022217</v>
       </c>
       <c r="H244" t="n">
         <v>9300</v>
@@ -7909,7 +7909,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G260" t="n">
-        <v>5.64289999008179</v>
+        <v>5.64290046691895</v>
       </c>
       <c r="H260" t="n">
         <v>300</v>
@@ -7938,7 +7938,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G261" t="n">
-        <v>5.64289999008179</v>
+        <v>5.64290046691895</v>
       </c>
       <c r="H261" t="n">
         <v>0</v>
@@ -7967,7 +7967,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G262" t="n">
-        <v>5.64289999008179</v>
+        <v>5.64290046691895</v>
       </c>
       <c r="H262" t="n">
         <v>0</v>
@@ -7996,7 +7996,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G263" t="n">
-        <v>5.64289999008179</v>
+        <v>5.64290046691895</v>
       </c>
       <c r="H263" t="n">
         <v>0</v>
@@ -8025,7 +8025,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G264" t="n">
-        <v>5.64289999008179</v>
+        <v>5.64290046691895</v>
       </c>
       <c r="H264" t="n">
         <v>300</v>
@@ -8054,7 +8054,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G265" t="n">
-        <v>5.64289999008179</v>
+        <v>5.64290046691895</v>
       </c>
       <c r="H265" t="n">
         <v>0</v>
@@ -8112,7 +8112,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G267" t="n">
-        <v>5.64289999008179</v>
+        <v>5.64290046691895</v>
       </c>
       <c r="H267" t="n">
         <v>300</v>
@@ -8141,7 +8141,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G268" t="n">
-        <v>5.64289999008179</v>
+        <v>5.64290046691895</v>
       </c>
       <c r="H268" t="n">
         <v>0</v>
@@ -8315,7 +8315,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G274" t="n">
-        <v>5.72073316574097</v>
+        <v>5.72073364257812</v>
       </c>
       <c r="H274" t="n">
         <v>900</v>
@@ -8489,7 +8489,7 @@
         <v>6.05000019073486</v>
       </c>
       <c r="G280" t="n">
-        <v>5.8861289024353</v>
+        <v>5.88612842559814</v>
       </c>
       <c r="H280" t="n">
         <v>3900</v>
@@ -8576,7 +8576,7 @@
         <v>6.05000019073486</v>
       </c>
       <c r="G283" t="n">
-        <v>5.8861289024353</v>
+        <v>5.88612842559814</v>
       </c>
       <c r="H283" t="n">
         <v>4800</v>
@@ -8605,7 +8605,7 @@
         <v>6.05000019073486</v>
       </c>
       <c r="G284" t="n">
-        <v>5.8861289024353</v>
+        <v>5.88612842559814</v>
       </c>
       <c r="H284" t="n">
         <v>0</v>
@@ -9330,7 +9330,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G309" t="n">
-        <v>5.69154596328735</v>
+        <v>5.6915454864502</v>
       </c>
       <c r="H309" t="n">
         <v>5100</v>
@@ -9359,7 +9359,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G310" t="n">
-        <v>5.69154596328735</v>
+        <v>5.6915454864502</v>
       </c>
       <c r="H310" t="n">
         <v>4200</v>
@@ -9388,7 +9388,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G311" t="n">
-        <v>5.69154596328735</v>
+        <v>5.6915454864502</v>
       </c>
       <c r="H311" t="n">
         <v>3000</v>
@@ -9417,7 +9417,7 @@
         <v>5.75</v>
       </c>
       <c r="G312" t="n">
-        <v>5.59425449371338</v>
+        <v>5.59425401687622</v>
       </c>
       <c r="H312" t="n">
         <v>2400</v>
@@ -9446,7 +9446,7 @@
         <v>5.75</v>
       </c>
       <c r="G313" t="n">
-        <v>5.59425449371338</v>
+        <v>5.59425401687622</v>
       </c>
       <c r="H313" t="n">
         <v>5100</v>
@@ -9475,7 +9475,7 @@
         <v>5.75</v>
       </c>
       <c r="G314" t="n">
-        <v>5.59425449371338</v>
+        <v>5.59425401687622</v>
       </c>
       <c r="H314" t="n">
         <v>0</v>
@@ -9504,7 +9504,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G315" t="n">
-        <v>5.69154596328735</v>
+        <v>5.6915454864502</v>
       </c>
       <c r="H315" t="n">
         <v>2100</v>
@@ -9533,7 +9533,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G316" t="n">
-        <v>5.69154596328735</v>
+        <v>5.6915454864502</v>
       </c>
       <c r="H316" t="n">
         <v>300</v>
@@ -9562,7 +9562,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G317" t="n">
-        <v>5.69154596328735</v>
+        <v>5.6915454864502</v>
       </c>
       <c r="H317" t="n">
         <v>0</v>
@@ -9591,7 +9591,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G318" t="n">
-        <v>5.69154596328735</v>
+        <v>5.6915454864502</v>
       </c>
       <c r="H318" t="n">
         <v>0</v>
@@ -9620,7 +9620,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G319" t="n">
-        <v>5.69154596328735</v>
+        <v>5.6915454864502</v>
       </c>
       <c r="H319" t="n">
         <v>0</v>
@@ -9765,7 +9765,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G324" t="n">
-        <v>5.64289999008179</v>
+        <v>5.64290046691895</v>
       </c>
       <c r="H324" t="n">
         <v>600</v>
@@ -9794,7 +9794,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G325" t="n">
-        <v>5.64289999008179</v>
+        <v>5.64290046691895</v>
       </c>
       <c r="H325" t="n">
         <v>0</v>
@@ -9823,7 +9823,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G326" t="n">
-        <v>5.64289999008179</v>
+        <v>5.64290046691895</v>
       </c>
       <c r="H326" t="n">
         <v>0</v>
@@ -9852,7 +9852,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G327" t="n">
-        <v>5.64289999008179</v>
+        <v>5.64290046691895</v>
       </c>
       <c r="H327" t="n">
         <v>0</v>
@@ -9881,7 +9881,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G328" t="n">
-        <v>5.64289999008179</v>
+        <v>5.64290046691895</v>
       </c>
       <c r="H328" t="n">
         <v>0</v>
@@ -9910,7 +9910,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G329" t="n">
-        <v>5.64289999008179</v>
+        <v>5.64290046691895</v>
       </c>
       <c r="H329" t="n">
         <v>0</v>
@@ -9939,7 +9939,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G330" t="n">
-        <v>5.64289999008179</v>
+        <v>5.64290046691895</v>
       </c>
       <c r="H330" t="n">
         <v>0</v>
@@ -9968,7 +9968,7 @@
         <v>6.05000019073486</v>
       </c>
       <c r="G331" t="n">
-        <v>5.8861289024353</v>
+        <v>5.88612842559814</v>
       </c>
       <c r="H331" t="n">
         <v>1500</v>
@@ -9997,7 +9997,7 @@
         <v>6.05000019073486</v>
       </c>
       <c r="G332" t="n">
-        <v>5.8861289024353</v>
+        <v>5.88612842559814</v>
       </c>
       <c r="H332" t="n">
         <v>0</v>
@@ -10026,7 +10026,7 @@
         <v>6.05000019073486</v>
       </c>
       <c r="G333" t="n">
-        <v>5.8861289024353</v>
+        <v>5.88612842559814</v>
       </c>
       <c r="H333" t="n">
         <v>0</v>
@@ -10055,7 +10055,7 @@
         <v>6.05000019073486</v>
       </c>
       <c r="G334" t="n">
-        <v>5.8861289024353</v>
+        <v>5.88612842559814</v>
       </c>
       <c r="H334" t="n">
         <v>0</v>
@@ -10084,7 +10084,7 @@
         <v>6.05000019073486</v>
       </c>
       <c r="G335" t="n">
-        <v>5.8861289024353</v>
+        <v>5.88612842559814</v>
       </c>
       <c r="H335" t="n">
         <v>0</v>
@@ -10113,7 +10113,7 @@
         <v>6.05000019073486</v>
       </c>
       <c r="G336" t="n">
-        <v>5.8861289024353</v>
+        <v>5.88612842559814</v>
       </c>
       <c r="H336" t="n">
         <v>0</v>
@@ -10142,7 +10142,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G337" t="n">
-        <v>5.64289999008179</v>
+        <v>5.64290046691895</v>
       </c>
       <c r="H337" t="n">
         <v>300</v>
@@ -10316,7 +10316,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G343" t="n">
-        <v>5.64289999008179</v>
+        <v>5.64290046691895</v>
       </c>
       <c r="H343" t="n">
         <v>1200</v>
@@ -10345,7 +10345,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G344" t="n">
-        <v>5.64289999008179</v>
+        <v>5.64290046691895</v>
       </c>
       <c r="H344" t="n">
         <v>0</v>
@@ -10374,7 +10374,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G345" t="n">
-        <v>5.64289999008179</v>
+        <v>5.64290046691895</v>
       </c>
       <c r="H345" t="n">
         <v>300</v>
@@ -10403,7 +10403,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G346" t="n">
-        <v>5.64289999008179</v>
+        <v>5.64290046691895</v>
       </c>
       <c r="H346" t="n">
         <v>0</v>
@@ -11128,7 +11128,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G371" t="n">
-        <v>5.64289999008179</v>
+        <v>5.64290046691895</v>
       </c>
       <c r="H371" t="n">
         <v>300</v>
@@ -11157,7 +11157,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G372" t="n">
-        <v>5.64289999008179</v>
+        <v>5.64290046691895</v>
       </c>
       <c r="H372" t="n">
         <v>0</v>
@@ -11186,7 +11186,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G373" t="n">
-        <v>5.64289999008179</v>
+        <v>5.64290046691895</v>
       </c>
       <c r="H373" t="n">
         <v>0</v>
@@ -11215,7 +11215,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G374" t="n">
-        <v>5.64289999008179</v>
+        <v>5.64290046691895</v>
       </c>
       <c r="H374" t="n">
         <v>0</v>
@@ -11244,7 +11244,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G375" t="n">
-        <v>5.64289999008179</v>
+        <v>5.64290046691895</v>
       </c>
       <c r="H375" t="n">
         <v>600</v>
@@ -11273,7 +11273,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G376" t="n">
-        <v>5.64289999008179</v>
+        <v>5.64290046691895</v>
       </c>
       <c r="H376" t="n">
         <v>0</v>
@@ -11302,7 +11302,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G377" t="n">
-        <v>5.64289999008179</v>
+        <v>5.64290046691895</v>
       </c>
       <c r="H377" t="n">
         <v>0</v>
@@ -11331,7 +11331,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G378" t="n">
-        <v>5.64289999008179</v>
+        <v>5.64290046691895</v>
       </c>
       <c r="H378" t="n">
         <v>0</v>
@@ -11360,7 +11360,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G379" t="n">
-        <v>5.64289999008179</v>
+        <v>5.64290046691895</v>
       </c>
       <c r="H379" t="n">
         <v>0</v>
@@ -11389,7 +11389,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G380" t="n">
-        <v>5.64289999008179</v>
+        <v>5.64290046691895</v>
       </c>
       <c r="H380" t="n">
         <v>0</v>
@@ -11650,7 +11650,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G389" t="n">
-        <v>5.69154596328735</v>
+        <v>5.6915454864502</v>
       </c>
       <c r="H389" t="n">
         <v>300</v>
@@ -11679,7 +11679,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G390" t="n">
-        <v>5.69154596328735</v>
+        <v>5.6915454864502</v>
       </c>
       <c r="H390" t="n">
         <v>0</v>
@@ -11708,7 +11708,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G391" t="n">
-        <v>5.69154596328735</v>
+        <v>5.6915454864502</v>
       </c>
       <c r="H391" t="n">
         <v>0</v>
@@ -11940,7 +11940,7 @@
         <v>5.75</v>
       </c>
       <c r="G399" t="n">
-        <v>5.59425449371338</v>
+        <v>5.59425401687622</v>
       </c>
       <c r="H399" t="n">
         <v>1500</v>
@@ -11969,7 +11969,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G400" t="n">
-        <v>5.69154596328735</v>
+        <v>5.6915454864502</v>
       </c>
       <c r="H400" t="n">
         <v>1200</v>
@@ -11998,7 +11998,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G401" t="n">
-        <v>5.69154596328735</v>
+        <v>5.6915454864502</v>
       </c>
       <c r="H401" t="n">
         <v>4500</v>
@@ -12027,7 +12027,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G402" t="n">
-        <v>5.69154596328735</v>
+        <v>5.6915454864502</v>
       </c>
       <c r="H402" t="n">
         <v>0</v>
@@ -12056,7 +12056,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G403" t="n">
-        <v>5.69154596328735</v>
+        <v>5.6915454864502</v>
       </c>
       <c r="H403" t="n">
         <v>0</v>
@@ -12085,7 +12085,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G404" t="n">
-        <v>5.69154596328735</v>
+        <v>5.6915454864502</v>
       </c>
       <c r="H404" t="n">
         <v>1500</v>
@@ -12114,7 +12114,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G405" t="n">
-        <v>5.69154596328735</v>
+        <v>5.6915454864502</v>
       </c>
       <c r="H405" t="n">
         <v>600</v>
@@ -12143,7 +12143,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G406" t="n">
-        <v>5.69154596328735</v>
+        <v>5.6915454864502</v>
       </c>
       <c r="H406" t="n">
         <v>0</v>
@@ -12172,7 +12172,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G407" t="n">
-        <v>5.69154596328735</v>
+        <v>5.6915454864502</v>
       </c>
       <c r="H407" t="n">
         <v>600</v>
@@ -12201,7 +12201,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G408" t="n">
-        <v>5.69154596328735</v>
+        <v>5.6915454864502</v>
       </c>
       <c r="H408" t="n">
         <v>0</v>
@@ -12230,7 +12230,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G409" t="n">
-        <v>5.64289999008179</v>
+        <v>5.64290046691895</v>
       </c>
       <c r="H409" t="n">
         <v>1200</v>
@@ -12259,7 +12259,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G410" t="n">
-        <v>5.64289999008179</v>
+        <v>5.64290046691895</v>
       </c>
       <c r="H410" t="n">
         <v>0</v>
@@ -12288,7 +12288,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G411" t="n">
-        <v>5.64289999008179</v>
+        <v>5.64290046691895</v>
       </c>
       <c r="H411" t="n">
         <v>4800</v>
@@ -12317,7 +12317,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G412" t="n">
-        <v>5.64289999008179</v>
+        <v>5.64290046691895</v>
       </c>
       <c r="H412" t="n">
         <v>0</v>
@@ -12346,7 +12346,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G413" t="n">
-        <v>5.64289999008179</v>
+        <v>5.64290046691895</v>
       </c>
       <c r="H413" t="n">
         <v>0</v>
@@ -12375,7 +12375,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G414" t="n">
-        <v>5.64289999008179</v>
+        <v>5.64290046691895</v>
       </c>
       <c r="H414" t="n">
         <v>0</v>
@@ -12404,7 +12404,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G415" t="n">
-        <v>5.64289999008179</v>
+        <v>5.64290046691895</v>
       </c>
       <c r="H415" t="n">
         <v>0</v>
@@ -12462,7 +12462,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G417" t="n">
-        <v>5.69154596328735</v>
+        <v>5.6915454864502</v>
       </c>
       <c r="H417" t="n">
         <v>300</v>
@@ -12491,7 +12491,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G418" t="n">
-        <v>5.69154596328735</v>
+        <v>5.6915454864502</v>
       </c>
       <c r="H418" t="n">
         <v>0</v>
@@ -12520,7 +12520,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G419" t="n">
-        <v>5.69154596328735</v>
+        <v>5.6915454864502</v>
       </c>
       <c r="H419" t="n">
         <v>0</v>
@@ -12549,7 +12549,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G420" t="n">
-        <v>5.69154596328735</v>
+        <v>5.6915454864502</v>
       </c>
       <c r="H420" t="n">
         <v>0</v>
@@ -12578,7 +12578,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G421" t="n">
-        <v>5.69154596328735</v>
+        <v>5.6915454864502</v>
       </c>
       <c r="H421" t="n">
         <v>0</v>
@@ -12607,7 +12607,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G422" t="n">
-        <v>5.69154596328735</v>
+        <v>5.6915454864502</v>
       </c>
       <c r="H422" t="n">
         <v>0</v>
@@ -12665,7 +12665,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G424" t="n">
-        <v>5.69154596328735</v>
+        <v>5.6915454864502</v>
       </c>
       <c r="H424" t="n">
         <v>300</v>
@@ -12694,7 +12694,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G425" t="n">
-        <v>5.69154596328735</v>
+        <v>5.6915454864502</v>
       </c>
       <c r="H425" t="n">
         <v>0</v>
@@ -12723,7 +12723,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G426" t="n">
-        <v>5.64289999008179</v>
+        <v>5.64290046691895</v>
       </c>
       <c r="H426" t="n">
         <v>900</v>
@@ -12810,7 +12810,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G429" t="n">
-        <v>5.64289999008179</v>
+        <v>5.64290046691895</v>
       </c>
       <c r="H429" t="n">
         <v>1200</v>
@@ -12839,7 +12839,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G430" t="n">
-        <v>5.64289999008179</v>
+        <v>5.64290046691895</v>
       </c>
       <c r="H430" t="n">
         <v>300</v>
@@ -12868,7 +12868,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G431" t="n">
-        <v>5.64289999008179</v>
+        <v>5.64290046691895</v>
       </c>
       <c r="H431" t="n">
         <v>600</v>
@@ -12897,7 +12897,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G432" t="n">
-        <v>5.64289999008179</v>
+        <v>5.64290046691895</v>
       </c>
       <c r="H432" t="n">
         <v>0</v>
@@ -12926,7 +12926,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G433" t="n">
-        <v>5.64289999008179</v>
+        <v>5.64290046691895</v>
       </c>
       <c r="H433" t="n">
         <v>0</v>
@@ -12955,7 +12955,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G434" t="n">
-        <v>5.64289999008179</v>
+        <v>5.64290046691895</v>
       </c>
       <c r="H434" t="n">
         <v>0</v>
@@ -12984,7 +12984,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G435" t="n">
-        <v>5.64289999008179</v>
+        <v>5.64290046691895</v>
       </c>
       <c r="H435" t="n">
         <v>0</v>
@@ -13013,7 +13013,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G436" t="n">
-        <v>5.64289999008179</v>
+        <v>5.64290046691895</v>
       </c>
       <c r="H436" t="n">
         <v>0</v>
@@ -13042,7 +13042,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G437" t="n">
-        <v>5.64289999008179</v>
+        <v>5.64290046691895</v>
       </c>
       <c r="H437" t="n">
         <v>0</v>
@@ -13071,7 +13071,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G438" t="n">
-        <v>5.64289999008179</v>
+        <v>5.64290046691895</v>
       </c>
       <c r="H438" t="n">
         <v>0</v>
@@ -13100,7 +13100,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G439" t="n">
-        <v>5.64289999008179</v>
+        <v>5.64290046691895</v>
       </c>
       <c r="H439" t="n">
         <v>0</v>
@@ -13129,7 +13129,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G440" t="n">
-        <v>5.64289999008179</v>
+        <v>5.64290046691895</v>
       </c>
       <c r="H440" t="n">
         <v>0</v>
@@ -13158,7 +13158,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G441" t="n">
-        <v>5.64289999008179</v>
+        <v>5.64290046691895</v>
       </c>
       <c r="H441" t="n">
         <v>0</v>
@@ -13187,7 +13187,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G442" t="n">
-        <v>5.64289999008179</v>
+        <v>5.64290046691895</v>
       </c>
       <c r="H442" t="n">
         <v>0</v>
@@ -13216,7 +13216,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G443" t="n">
-        <v>5.64289999008179</v>
+        <v>5.64290046691895</v>
       </c>
       <c r="H443" t="n">
         <v>0</v>
@@ -13419,7 +13419,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G450" t="n">
-        <v>5.64289999008179</v>
+        <v>5.64290046691895</v>
       </c>
       <c r="H450" t="n">
         <v>4500</v>
@@ -13506,7 +13506,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G453" t="n">
-        <v>5.69154596328735</v>
+        <v>5.6915454864502</v>
       </c>
       <c r="H453" t="n">
         <v>900</v>
@@ -13535,7 +13535,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G454" t="n">
-        <v>5.69154596328735</v>
+        <v>5.6915454864502</v>
       </c>
       <c r="H454" t="n">
         <v>0</v>
@@ -13680,7 +13680,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G459" t="n">
-        <v>6.37258577346802</v>
+        <v>6.37258529663086</v>
       </c>
       <c r="H459" t="n">
         <v>1500</v>
@@ -13709,7 +13709,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G460" t="n">
-        <v>6.37258577346802</v>
+        <v>6.37258529663086</v>
       </c>
       <c r="H460" t="n">
         <v>0</v>
@@ -13738,7 +13738,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G461" t="n">
-        <v>6.37258577346802</v>
+        <v>6.37258529663086</v>
       </c>
       <c r="H461" t="n">
         <v>0</v>
@@ -13767,7 +13767,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G462" t="n">
-        <v>6.37258577346802</v>
+        <v>6.37258529663086</v>
       </c>
       <c r="H462" t="n">
         <v>0</v>
@@ -13796,7 +13796,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G463" t="n">
-        <v>6.37258577346802</v>
+        <v>6.37258529663086</v>
       </c>
       <c r="H463" t="n">
         <v>0</v>
@@ -13825,7 +13825,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G464" t="n">
-        <v>6.37258577346802</v>
+        <v>6.37258529663086</v>
       </c>
       <c r="H464" t="n">
         <v>300</v>
@@ -13854,7 +13854,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G465" t="n">
-        <v>6.37258577346802</v>
+        <v>6.37258529663086</v>
       </c>
       <c r="H465" t="n">
         <v>4800</v>
@@ -13912,7 +13912,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G467" t="n">
-        <v>6.42123079299927</v>
+        <v>6.42123126983643</v>
       </c>
       <c r="H467" t="n">
         <v>6900</v>
@@ -14028,7 +14028,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G471" t="n">
-        <v>6.37258577346802</v>
+        <v>6.37258529663086</v>
       </c>
       <c r="H471" t="n">
         <v>600</v>
@@ -14057,7 +14057,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G472" t="n">
-        <v>6.22664880752563</v>
+        <v>6.22664833068848</v>
       </c>
       <c r="H472" t="n">
         <v>600</v>
@@ -14086,7 +14086,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G473" t="n">
-        <v>6.22664880752563</v>
+        <v>6.22664833068848</v>
       </c>
       <c r="H473" t="n">
         <v>0</v>
@@ -14115,7 +14115,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G474" t="n">
-        <v>6.22664880752563</v>
+        <v>6.22664833068848</v>
       </c>
       <c r="H474" t="n">
         <v>0</v>
@@ -14144,7 +14144,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G475" t="n">
-        <v>6.22664880752563</v>
+        <v>6.22664833068848</v>
       </c>
       <c r="H475" t="n">
         <v>0</v>
@@ -14173,7 +14173,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G476" t="n">
-        <v>6.22664880752563</v>
+        <v>6.22664833068848</v>
       </c>
       <c r="H476" t="n">
         <v>0</v>
@@ -14202,7 +14202,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G477" t="n">
-        <v>6.22664880752563</v>
+        <v>6.22664833068848</v>
       </c>
       <c r="H477" t="n">
         <v>0</v>
@@ -14231,7 +14231,7 @@
         <v>6.65000009536743</v>
       </c>
       <c r="G478" t="n">
-        <v>6.46987724304199</v>
+        <v>6.46987676620483</v>
       </c>
       <c r="H478" t="n">
         <v>2400</v>
@@ -14289,7 +14289,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G480" t="n">
-        <v>6.37258577346802</v>
+        <v>6.37258529663086</v>
       </c>
       <c r="H480" t="n">
         <v>1800</v>
@@ -14347,7 +14347,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G482" t="n">
-        <v>6.22664880752563</v>
+        <v>6.22664833068848</v>
       </c>
       <c r="H482" t="n">
         <v>3000</v>
@@ -14376,7 +14376,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G483" t="n">
-        <v>6.22664880752563</v>
+        <v>6.22664833068848</v>
       </c>
       <c r="H483" t="n">
         <v>0</v>
@@ -14405,7 +14405,7 @@
         <v>6.65000009536743</v>
       </c>
       <c r="G484" t="n">
-        <v>6.46987724304199</v>
+        <v>6.46987676620483</v>
       </c>
       <c r="H484" t="n">
         <v>2400</v>
@@ -14434,7 +14434,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G485" t="n">
-        <v>6.22664880752563</v>
+        <v>6.22664833068848</v>
       </c>
       <c r="H485" t="n">
         <v>1500</v>
@@ -14521,7 +14521,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G488" t="n">
-        <v>6.22664880752563</v>
+        <v>6.22664833068848</v>
       </c>
       <c r="H488" t="n">
         <v>4200</v>
@@ -14956,7 +14956,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G503" t="n">
-        <v>6.37258577346802</v>
+        <v>6.37258529663086</v>
       </c>
       <c r="H503" t="n">
         <v>1800</v>
@@ -14985,7 +14985,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G504" t="n">
-        <v>6.22664880752563</v>
+        <v>6.22664833068848</v>
       </c>
       <c r="H504" t="n">
         <v>2700</v>
@@ -15014,7 +15014,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G505" t="n">
-        <v>6.22664880752563</v>
+        <v>6.22664833068848</v>
       </c>
       <c r="H505" t="n">
         <v>0</v>
@@ -15043,7 +15043,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G506" t="n">
-        <v>6.22664880752563</v>
+        <v>6.22664833068848</v>
       </c>
       <c r="H506" t="n">
         <v>0</v>
@@ -15710,7 +15710,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G529" t="n">
-        <v>6.22664880752563</v>
+        <v>6.22664833068848</v>
       </c>
       <c r="H529" t="n">
         <v>3300</v>
@@ -15768,7 +15768,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G531" t="n">
-        <v>6.42123079299927</v>
+        <v>6.42123126983643</v>
       </c>
       <c r="H531" t="n">
         <v>1200</v>
@@ -15826,7 +15826,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G533" t="n">
-        <v>5.69154596328735</v>
+        <v>5.6915454864502</v>
       </c>
       <c r="H533" t="n">
         <v>8700</v>
@@ -15855,7 +15855,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G534" t="n">
-        <v>5.69154596328735</v>
+        <v>5.6915454864502</v>
       </c>
       <c r="H534" t="n">
         <v>300</v>
@@ -15884,7 +15884,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G535" t="n">
-        <v>5.69154596328735</v>
+        <v>5.6915454864502</v>
       </c>
       <c r="H535" t="n">
         <v>0</v>
@@ -15913,7 +15913,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G536" t="n">
-        <v>5.64289999008179</v>
+        <v>5.64290046691895</v>
       </c>
       <c r="H536" t="n">
         <v>2400</v>
@@ -16232,7 +16232,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G547" t="n">
-        <v>6.22664880752563</v>
+        <v>6.22664833068848</v>
       </c>
       <c r="H547" t="n">
         <v>1500</v>
@@ -16261,7 +16261,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G548" t="n">
-        <v>6.22664880752563</v>
+        <v>6.22664833068848</v>
       </c>
       <c r="H548" t="n">
         <v>1200</v>
@@ -16290,7 +16290,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G549" t="n">
-        <v>6.22664880752563</v>
+        <v>6.22664833068848</v>
       </c>
       <c r="H549" t="n">
         <v>1200</v>
@@ -16348,7 +16348,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G551" t="n">
-        <v>6.37258577346802</v>
+        <v>6.37258529663086</v>
       </c>
       <c r="H551" t="n">
         <v>60600</v>
@@ -16377,7 +16377,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G552" t="n">
-        <v>6.37258577346802</v>
+        <v>6.37258529663086</v>
       </c>
       <c r="H552" t="n">
         <v>0</v>
@@ -16406,7 +16406,7 @@
         <v>6.65000009536743</v>
       </c>
       <c r="G553" t="n">
-        <v>6.46987724304199</v>
+        <v>6.46987676620483</v>
       </c>
       <c r="H553" t="n">
         <v>300</v>
@@ -16435,7 +16435,7 @@
         <v>6.65000009536743</v>
       </c>
       <c r="G554" t="n">
-        <v>6.46987724304199</v>
+        <v>6.46987676620483</v>
       </c>
       <c r="H554" t="n">
         <v>0</v>
@@ -27113,6 +27113,64 @@
         <v>0</v>
       </c>
       <c r="I922" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="923">
+      <c r="A923" t="s">
+        <v>9</v>
+      </c>
+      <c r="B923" s="1" t="n">
+        <v>46315.2916666667</v>
+      </c>
+      <c r="C923" t="n">
+        <v>12</v>
+      </c>
+      <c r="D923" t="n">
+        <v>12</v>
+      </c>
+      <c r="E923" t="n">
+        <v>12</v>
+      </c>
+      <c r="F923" t="n">
+        <v>12</v>
+      </c>
+      <c r="G923" t="n">
+        <v>12</v>
+      </c>
+      <c r="H923" t="n">
+        <v>0</v>
+      </c>
+      <c r="I923" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="924">
+      <c r="A924" t="s">
+        <v>9</v>
+      </c>
+      <c r="B924" s="1" t="n">
+        <v>46316.2916666667</v>
+      </c>
+      <c r="C924" t="n">
+        <v>11.8999996185303</v>
+      </c>
+      <c r="D924" t="n">
+        <v>11.8999996185303</v>
+      </c>
+      <c r="E924" t="n">
+        <v>11.8999996185303</v>
+      </c>
+      <c r="F924" t="n">
+        <v>11.8999996185303</v>
+      </c>
+      <c r="G924" t="n">
+        <v>11.8999996185303</v>
+      </c>
+      <c r="H924" t="n">
+        <v>300</v>
+      </c>
+      <c r="I924" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/VLT.MI.xlsx
+++ b/data/VLT.MI.xlsx
@@ -543,7 +543,7 @@
         <v>5.69799995422363</v>
       </c>
       <c r="G6" t="n">
-        <v>5.54366254806519</v>
+        <v>5.54366302490234</v>
       </c>
       <c r="H6" t="n">
         <v>18900</v>
@@ -717,7 +717,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G12" t="n">
-        <v>5.02023506164551</v>
+        <v>5.02023553848267</v>
       </c>
       <c r="H12" t="n">
         <v>3300</v>
@@ -804,7 +804,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G15" t="n">
-        <v>5.15644359588623</v>
+        <v>5.15644311904907</v>
       </c>
       <c r="H15" t="n">
         <v>1500</v>
@@ -1094,7 +1094,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G25" t="n">
-        <v>5.19535970687866</v>
+        <v>5.19536018371582</v>
       </c>
       <c r="H25" t="n">
         <v>1800</v>
@@ -1123,7 +1123,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G26" t="n">
-        <v>5.19535970687866</v>
+        <v>5.19536018371582</v>
       </c>
       <c r="H26" t="n">
         <v>0</v>
@@ -1152,7 +1152,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G27" t="n">
-        <v>5.19535970687866</v>
+        <v>5.19536018371582</v>
       </c>
       <c r="H27" t="n">
         <v>0</v>
@@ -1384,7 +1384,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G35" t="n">
-        <v>5.38994216918945</v>
+        <v>5.38994264602661</v>
       </c>
       <c r="H35" t="n">
         <v>300</v>
@@ -1848,7 +1848,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G51" t="n">
-        <v>4.65052795410156</v>
+        <v>4.65052843093872</v>
       </c>
       <c r="H51" t="n">
         <v>1500</v>
@@ -1993,7 +1993,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G56" t="n">
-        <v>4.70890283584595</v>
+        <v>4.70890331268311</v>
       </c>
       <c r="H56" t="n">
         <v>300</v>
@@ -2399,7 +2399,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G70" t="n">
-        <v>4.70890283584595</v>
+        <v>4.70890331268311</v>
       </c>
       <c r="H70" t="n">
         <v>300</v>
@@ -2747,7 +2747,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G82" t="n">
-        <v>4.70890283584595</v>
+        <v>4.70890331268311</v>
       </c>
       <c r="H82" t="n">
         <v>900</v>
@@ -2776,7 +2776,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G83" t="n">
-        <v>4.70890283584595</v>
+        <v>4.70890331268311</v>
       </c>
       <c r="H83" t="n">
         <v>0</v>
@@ -2805,7 +2805,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G84" t="n">
-        <v>4.66025733947754</v>
+        <v>4.66025686264038</v>
       </c>
       <c r="H84" t="n">
         <v>1200</v>
@@ -3298,7 +3298,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G101" t="n">
-        <v>4.70890283584595</v>
+        <v>4.70890331268311</v>
       </c>
       <c r="H101" t="n">
         <v>1200</v>
@@ -3356,7 +3356,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G103" t="n">
-        <v>4.66025733947754</v>
+        <v>4.66025686264038</v>
       </c>
       <c r="H103" t="n">
         <v>300</v>
@@ -3385,7 +3385,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G104" t="n">
-        <v>4.66025733947754</v>
+        <v>4.66025686264038</v>
       </c>
       <c r="H104" t="n">
         <v>0</v>
@@ -3414,7 +3414,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G105" t="n">
-        <v>4.66025733947754</v>
+        <v>4.66025686264038</v>
       </c>
       <c r="H105" t="n">
         <v>0</v>
@@ -3443,7 +3443,7 @@
         <v>4.5</v>
       </c>
       <c r="G106" t="n">
-        <v>4.37811231613159</v>
+        <v>4.37811183929443</v>
       </c>
       <c r="H106" t="n">
         <v>4800</v>
@@ -3472,7 +3472,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G107" t="n">
-        <v>4.47540378570557</v>
+        <v>4.47540330886841</v>
       </c>
       <c r="H107" t="n">
         <v>3600</v>
@@ -3501,7 +3501,7 @@
         <v>4.5</v>
       </c>
       <c r="G108" t="n">
-        <v>4.37811231613159</v>
+        <v>4.37811183929443</v>
       </c>
       <c r="H108" t="n">
         <v>600</v>
@@ -3646,7 +3646,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G113" t="n">
-        <v>4.47540378570557</v>
+        <v>4.47540330886841</v>
       </c>
       <c r="H113" t="n">
         <v>300</v>
@@ -3675,7 +3675,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G114" t="n">
-        <v>4.47540378570557</v>
+        <v>4.47540330886841</v>
       </c>
       <c r="H114" t="n">
         <v>300</v>
@@ -3733,7 +3733,7 @@
         <v>4.53000020980835</v>
       </c>
       <c r="G116" t="n">
-        <v>4.40729999542236</v>
+        <v>4.40729951858521</v>
       </c>
       <c r="H116" t="n">
         <v>2700</v>
@@ -3762,7 +3762,7 @@
         <v>4.53000020980835</v>
       </c>
       <c r="G117" t="n">
-        <v>4.40729999542236</v>
+        <v>4.40729951858521</v>
       </c>
       <c r="H117" t="n">
         <v>0</v>
@@ -4255,7 +4255,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G134" t="n">
-        <v>4.35865354537964</v>
+        <v>4.3586540222168</v>
       </c>
       <c r="H134" t="n">
         <v>600</v>
@@ -4284,7 +4284,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G135" t="n">
-        <v>4.35865354537964</v>
+        <v>4.3586540222168</v>
       </c>
       <c r="H135" t="n">
         <v>0</v>
@@ -4313,7 +4313,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G136" t="n">
-        <v>4.35865354537964</v>
+        <v>4.3586540222168</v>
       </c>
       <c r="H136" t="n">
         <v>0</v>
@@ -4342,7 +4342,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G137" t="n">
-        <v>4.35865354537964</v>
+        <v>4.3586540222168</v>
       </c>
       <c r="H137" t="n">
         <v>0</v>
@@ -4371,7 +4371,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G138" t="n">
-        <v>4.35865354537964</v>
+        <v>4.3586540222168</v>
       </c>
       <c r="H138" t="n">
         <v>0</v>
@@ -4400,7 +4400,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G139" t="n">
-        <v>4.35865354537964</v>
+        <v>4.3586540222168</v>
       </c>
       <c r="H139" t="n">
         <v>0</v>
@@ -4429,7 +4429,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G140" t="n">
-        <v>4.35865354537964</v>
+        <v>4.3586540222168</v>
       </c>
       <c r="H140" t="n">
         <v>3000</v>
@@ -4458,7 +4458,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G141" t="n">
-        <v>4.35865354537964</v>
+        <v>4.3586540222168</v>
       </c>
       <c r="H141" t="n">
         <v>0</v>
@@ -4632,7 +4632,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G147" t="n">
-        <v>4.96186065673828</v>
+        <v>4.96186017990112</v>
       </c>
       <c r="H147" t="n">
         <v>1500</v>
@@ -4661,7 +4661,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G148" t="n">
-        <v>4.73809003829956</v>
+        <v>4.73809051513672</v>
       </c>
       <c r="H148" t="n">
         <v>4500</v>
@@ -4690,7 +4690,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G149" t="n">
-        <v>4.66025733947754</v>
+        <v>4.66025686264038</v>
       </c>
       <c r="H149" t="n">
         <v>2100</v>
@@ -4777,7 +4777,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G152" t="n">
-        <v>4.70890283584595</v>
+        <v>4.70890331268311</v>
       </c>
       <c r="H152" t="n">
         <v>600</v>
@@ -4980,7 +4980,7 @@
         <v>4.5</v>
       </c>
       <c r="G159" t="n">
-        <v>4.37811231613159</v>
+        <v>4.37811183929443</v>
       </c>
       <c r="H159" t="n">
         <v>3900</v>
@@ -5009,7 +5009,7 @@
         <v>4.5</v>
       </c>
       <c r="G160" t="n">
-        <v>4.37811231613159</v>
+        <v>4.37811183929443</v>
       </c>
       <c r="H160" t="n">
         <v>0</v>
@@ -5038,7 +5038,7 @@
         <v>4.5</v>
       </c>
       <c r="G161" t="n">
-        <v>4.37811231613159</v>
+        <v>4.37811183929443</v>
       </c>
       <c r="H161" t="n">
         <v>1800</v>
@@ -5067,7 +5067,7 @@
         <v>4.5</v>
       </c>
       <c r="G162" t="n">
-        <v>4.37811231613159</v>
+        <v>4.37811183929443</v>
       </c>
       <c r="H162" t="n">
         <v>1200</v>
@@ -5212,7 +5212,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G167" t="n">
-        <v>4.47540378570557</v>
+        <v>4.47540330886841</v>
       </c>
       <c r="H167" t="n">
         <v>900</v>
@@ -5241,7 +5241,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G168" t="n">
-        <v>4.47540378570557</v>
+        <v>4.47540330886841</v>
       </c>
       <c r="H168" t="n">
         <v>0</v>
@@ -5270,7 +5270,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G169" t="n">
-        <v>4.47540378570557</v>
+        <v>4.47540330886841</v>
       </c>
       <c r="H169" t="n">
         <v>0</v>
@@ -5299,7 +5299,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G170" t="n">
-        <v>4.47540378570557</v>
+        <v>4.47540330886841</v>
       </c>
       <c r="H170" t="n">
         <v>0</v>
@@ -5328,7 +5328,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G171" t="n">
-        <v>4.47540378570557</v>
+        <v>4.47540330886841</v>
       </c>
       <c r="H171" t="n">
         <v>0</v>
@@ -5357,7 +5357,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G172" t="n">
-        <v>4.47540378570557</v>
+        <v>4.47540330886841</v>
       </c>
       <c r="H172" t="n">
         <v>0</v>
@@ -5386,7 +5386,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G173" t="n">
-        <v>4.47540378570557</v>
+        <v>4.47540330886841</v>
       </c>
       <c r="H173" t="n">
         <v>0</v>
@@ -5415,7 +5415,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G174" t="n">
-        <v>4.47540378570557</v>
+        <v>4.47540330886841</v>
       </c>
       <c r="H174" t="n">
         <v>0</v>
@@ -5560,7 +5560,7 @@
         <v>4.76999998092651</v>
       </c>
       <c r="G179" t="n">
-        <v>4.64079856872559</v>
+        <v>4.64079904556274</v>
       </c>
       <c r="H179" t="n">
         <v>1200</v>
@@ -5618,7 +5618,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G181" t="n">
-        <v>4.68944501876831</v>
+        <v>4.68944454193115</v>
       </c>
       <c r="H181" t="n">
         <v>600</v>
@@ -5647,7 +5647,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G182" t="n">
-        <v>4.68944501876831</v>
+        <v>4.68944454193115</v>
       </c>
       <c r="H182" t="n">
         <v>300</v>
@@ -5676,7 +5676,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G183" t="n">
-        <v>4.68944501876831</v>
+        <v>4.68944454193115</v>
       </c>
       <c r="H183" t="n">
         <v>2400</v>
@@ -5705,7 +5705,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G184" t="n">
-        <v>4.68944501876831</v>
+        <v>4.68944454193115</v>
       </c>
       <c r="H184" t="n">
         <v>0</v>
@@ -5821,7 +5821,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G188" t="n">
-        <v>5.15644359588623</v>
+        <v>5.15644311904907</v>
       </c>
       <c r="H188" t="n">
         <v>600</v>
@@ -6198,7 +6198,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G201" t="n">
-        <v>4.96186065673828</v>
+        <v>4.96186017990112</v>
       </c>
       <c r="H201" t="n">
         <v>600</v>
@@ -6227,7 +6227,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G202" t="n">
-        <v>4.96186065673828</v>
+        <v>4.96186017990112</v>
       </c>
       <c r="H202" t="n">
         <v>300</v>
@@ -6256,7 +6256,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G203" t="n">
-        <v>4.96186065673828</v>
+        <v>4.96186017990112</v>
       </c>
       <c r="H203" t="n">
         <v>300</v>
@@ -6575,7 +6575,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G214" t="n">
-        <v>5.4288592338562</v>
+        <v>5.42885875701904</v>
       </c>
       <c r="H214" t="n">
         <v>3600</v>
@@ -6720,7 +6720,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G219" t="n">
-        <v>5.40940046310425</v>
+        <v>5.40940093994141</v>
       </c>
       <c r="H219" t="n">
         <v>1800</v>
@@ -7445,7 +7445,7 @@
         <v>6.03999996185303</v>
       </c>
       <c r="G244" t="n">
-        <v>5.87639904022217</v>
+        <v>5.87639951705933</v>
       </c>
       <c r="H244" t="n">
         <v>9300</v>
@@ -7909,7 +7909,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G260" t="n">
-        <v>5.64290046691895</v>
+        <v>5.64289999008179</v>
       </c>
       <c r="H260" t="n">
         <v>300</v>
@@ -7938,7 +7938,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G261" t="n">
-        <v>5.64290046691895</v>
+        <v>5.64289999008179</v>
       </c>
       <c r="H261" t="n">
         <v>0</v>
@@ -7967,7 +7967,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G262" t="n">
-        <v>5.64290046691895</v>
+        <v>5.64289999008179</v>
       </c>
       <c r="H262" t="n">
         <v>0</v>
@@ -7996,7 +7996,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G263" t="n">
-        <v>5.64290046691895</v>
+        <v>5.64289999008179</v>
       </c>
       <c r="H263" t="n">
         <v>0</v>
@@ -8025,7 +8025,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G264" t="n">
-        <v>5.64290046691895</v>
+        <v>5.64289999008179</v>
       </c>
       <c r="H264" t="n">
         <v>300</v>
@@ -8054,7 +8054,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G265" t="n">
-        <v>5.64290046691895</v>
+        <v>5.64289999008179</v>
       </c>
       <c r="H265" t="n">
         <v>0</v>
@@ -8112,7 +8112,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G267" t="n">
-        <v>5.64290046691895</v>
+        <v>5.64289999008179</v>
       </c>
       <c r="H267" t="n">
         <v>300</v>
@@ -8141,7 +8141,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G268" t="n">
-        <v>5.64290046691895</v>
+        <v>5.64289999008179</v>
       </c>
       <c r="H268" t="n">
         <v>0</v>
@@ -8315,7 +8315,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G274" t="n">
-        <v>5.72073364257812</v>
+        <v>5.72073316574097</v>
       </c>
       <c r="H274" t="n">
         <v>900</v>
@@ -8489,7 +8489,7 @@
         <v>6.05000019073486</v>
       </c>
       <c r="G280" t="n">
-        <v>5.88612842559814</v>
+        <v>5.8861289024353</v>
       </c>
       <c r="H280" t="n">
         <v>3900</v>
@@ -8576,7 +8576,7 @@
         <v>6.05000019073486</v>
       </c>
       <c r="G283" t="n">
-        <v>5.88612842559814</v>
+        <v>5.8861289024353</v>
       </c>
       <c r="H283" t="n">
         <v>4800</v>
@@ -8605,7 +8605,7 @@
         <v>6.05000019073486</v>
       </c>
       <c r="G284" t="n">
-        <v>5.88612842559814</v>
+        <v>5.8861289024353</v>
       </c>
       <c r="H284" t="n">
         <v>0</v>
@@ -9330,7 +9330,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G309" t="n">
-        <v>5.6915454864502</v>
+        <v>5.69154596328735</v>
       </c>
       <c r="H309" t="n">
         <v>5100</v>
@@ -9359,7 +9359,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G310" t="n">
-        <v>5.6915454864502</v>
+        <v>5.69154596328735</v>
       </c>
       <c r="H310" t="n">
         <v>4200</v>
@@ -9388,7 +9388,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G311" t="n">
-        <v>5.6915454864502</v>
+        <v>5.69154596328735</v>
       </c>
       <c r="H311" t="n">
         <v>3000</v>
@@ -9417,7 +9417,7 @@
         <v>5.75</v>
       </c>
       <c r="G312" t="n">
-        <v>5.59425401687622</v>
+        <v>5.59425449371338</v>
       </c>
       <c r="H312" t="n">
         <v>2400</v>
@@ -9446,7 +9446,7 @@
         <v>5.75</v>
       </c>
       <c r="G313" t="n">
-        <v>5.59425401687622</v>
+        <v>5.59425449371338</v>
       </c>
       <c r="H313" t="n">
         <v>5100</v>
@@ -9475,7 +9475,7 @@
         <v>5.75</v>
       </c>
       <c r="G314" t="n">
-        <v>5.59425401687622</v>
+        <v>5.59425449371338</v>
       </c>
       <c r="H314" t="n">
         <v>0</v>
@@ -9504,7 +9504,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G315" t="n">
-        <v>5.6915454864502</v>
+        <v>5.69154596328735</v>
       </c>
       <c r="H315" t="n">
         <v>2100</v>
@@ -9533,7 +9533,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G316" t="n">
-        <v>5.6915454864502</v>
+        <v>5.69154596328735</v>
       </c>
       <c r="H316" t="n">
         <v>300</v>
@@ -9562,7 +9562,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G317" t="n">
-        <v>5.6915454864502</v>
+        <v>5.69154596328735</v>
       </c>
       <c r="H317" t="n">
         <v>0</v>
@@ -9591,7 +9591,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G318" t="n">
-        <v>5.6915454864502</v>
+        <v>5.69154596328735</v>
       </c>
       <c r="H318" t="n">
         <v>0</v>
@@ -9620,7 +9620,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G319" t="n">
-        <v>5.6915454864502</v>
+        <v>5.69154596328735</v>
       </c>
       <c r="H319" t="n">
         <v>0</v>
@@ -9765,7 +9765,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G324" t="n">
-        <v>5.64290046691895</v>
+        <v>5.64289999008179</v>
       </c>
       <c r="H324" t="n">
         <v>600</v>
@@ -9794,7 +9794,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G325" t="n">
-        <v>5.64290046691895</v>
+        <v>5.64289999008179</v>
       </c>
       <c r="H325" t="n">
         <v>0</v>
@@ -9823,7 +9823,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G326" t="n">
-        <v>5.64290046691895</v>
+        <v>5.64289999008179</v>
       </c>
       <c r="H326" t="n">
         <v>0</v>
@@ -9852,7 +9852,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G327" t="n">
-        <v>5.64290046691895</v>
+        <v>5.64289999008179</v>
       </c>
       <c r="H327" t="n">
         <v>0</v>
@@ -9881,7 +9881,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G328" t="n">
-        <v>5.64290046691895</v>
+        <v>5.64289999008179</v>
       </c>
       <c r="H328" t="n">
         <v>0</v>
@@ -9910,7 +9910,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G329" t="n">
-        <v>5.64290046691895</v>
+        <v>5.64289999008179</v>
       </c>
       <c r="H329" t="n">
         <v>0</v>
@@ -9939,7 +9939,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G330" t="n">
-        <v>5.64290046691895</v>
+        <v>5.64289999008179</v>
       </c>
       <c r="H330" t="n">
         <v>0</v>
@@ -9968,7 +9968,7 @@
         <v>6.05000019073486</v>
       </c>
       <c r="G331" t="n">
-        <v>5.88612842559814</v>
+        <v>5.8861289024353</v>
       </c>
       <c r="H331" t="n">
         <v>1500</v>
@@ -9997,7 +9997,7 @@
         <v>6.05000019073486</v>
       </c>
       <c r="G332" t="n">
-        <v>5.88612842559814</v>
+        <v>5.8861289024353</v>
       </c>
       <c r="H332" t="n">
         <v>0</v>
@@ -10026,7 +10026,7 @@
         <v>6.05000019073486</v>
       </c>
       <c r="G333" t="n">
-        <v>5.88612842559814</v>
+        <v>5.8861289024353</v>
       </c>
       <c r="H333" t="n">
         <v>0</v>
@@ -10055,7 +10055,7 @@
         <v>6.05000019073486</v>
       </c>
       <c r="G334" t="n">
-        <v>5.88612842559814</v>
+        <v>5.8861289024353</v>
       </c>
       <c r="H334" t="n">
         <v>0</v>
@@ -10084,7 +10084,7 @@
         <v>6.05000019073486</v>
       </c>
       <c r="G335" t="n">
-        <v>5.88612842559814</v>
+        <v>5.8861289024353</v>
       </c>
       <c r="H335" t="n">
         <v>0</v>
@@ -10113,7 +10113,7 @@
         <v>6.05000019073486</v>
       </c>
       <c r="G336" t="n">
-        <v>5.88612842559814</v>
+        <v>5.8861289024353</v>
       </c>
       <c r="H336" t="n">
         <v>0</v>
@@ -10142,7 +10142,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G337" t="n">
-        <v>5.64290046691895</v>
+        <v>5.64289999008179</v>
       </c>
       <c r="H337" t="n">
         <v>300</v>
@@ -10316,7 +10316,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G343" t="n">
-        <v>5.64290046691895</v>
+        <v>5.64289999008179</v>
       </c>
       <c r="H343" t="n">
         <v>1200</v>
@@ -10345,7 +10345,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G344" t="n">
-        <v>5.64290046691895</v>
+        <v>5.64289999008179</v>
       </c>
       <c r="H344" t="n">
         <v>0</v>
@@ -10374,7 +10374,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G345" t="n">
-        <v>5.64290046691895</v>
+        <v>5.64289999008179</v>
       </c>
       <c r="H345" t="n">
         <v>300</v>
@@ -10403,7 +10403,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G346" t="n">
-        <v>5.64290046691895</v>
+        <v>5.64289999008179</v>
       </c>
       <c r="H346" t="n">
         <v>0</v>
@@ -11128,7 +11128,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G371" t="n">
-        <v>5.64290046691895</v>
+        <v>5.64289999008179</v>
       </c>
       <c r="H371" t="n">
         <v>300</v>
@@ -11157,7 +11157,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G372" t="n">
-        <v>5.64290046691895</v>
+        <v>5.64289999008179</v>
       </c>
       <c r="H372" t="n">
         <v>0</v>
@@ -11186,7 +11186,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G373" t="n">
-        <v>5.64290046691895</v>
+        <v>5.64289999008179</v>
       </c>
       <c r="H373" t="n">
         <v>0</v>
@@ -11215,7 +11215,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G374" t="n">
-        <v>5.64290046691895</v>
+        <v>5.64289999008179</v>
       </c>
       <c r="H374" t="n">
         <v>0</v>
@@ -11244,7 +11244,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G375" t="n">
-        <v>5.64290046691895</v>
+        <v>5.64289999008179</v>
       </c>
       <c r="H375" t="n">
         <v>600</v>
@@ -11273,7 +11273,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G376" t="n">
-        <v>5.64290046691895</v>
+        <v>5.64289999008179</v>
       </c>
       <c r="H376" t="n">
         <v>0</v>
@@ -11302,7 +11302,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G377" t="n">
-        <v>5.64290046691895</v>
+        <v>5.64289999008179</v>
       </c>
       <c r="H377" t="n">
         <v>0</v>
@@ -11331,7 +11331,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G378" t="n">
-        <v>5.64290046691895</v>
+        <v>5.64289999008179</v>
       </c>
       <c r="H378" t="n">
         <v>0</v>
@@ -11360,7 +11360,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G379" t="n">
-        <v>5.64290046691895</v>
+        <v>5.64289999008179</v>
       </c>
       <c r="H379" t="n">
         <v>0</v>
@@ -11389,7 +11389,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G380" t="n">
-        <v>5.64290046691895</v>
+        <v>5.64289999008179</v>
       </c>
       <c r="H380" t="n">
         <v>0</v>
@@ -11650,7 +11650,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G389" t="n">
-        <v>5.6915454864502</v>
+        <v>5.69154596328735</v>
       </c>
       <c r="H389" t="n">
         <v>300</v>
@@ -11679,7 +11679,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G390" t="n">
-        <v>5.6915454864502</v>
+        <v>5.69154596328735</v>
       </c>
       <c r="H390" t="n">
         <v>0</v>
@@ -11708,7 +11708,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G391" t="n">
-        <v>5.6915454864502</v>
+        <v>5.69154596328735</v>
       </c>
       <c r="H391" t="n">
         <v>0</v>
@@ -11940,7 +11940,7 @@
         <v>5.75</v>
       </c>
       <c r="G399" t="n">
-        <v>5.59425401687622</v>
+        <v>5.59425449371338</v>
       </c>
       <c r="H399" t="n">
         <v>1500</v>
@@ -11969,7 +11969,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G400" t="n">
-        <v>5.6915454864502</v>
+        <v>5.69154596328735</v>
       </c>
       <c r="H400" t="n">
         <v>1200</v>
@@ -11998,7 +11998,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G401" t="n">
-        <v>5.6915454864502</v>
+        <v>5.69154596328735</v>
       </c>
       <c r="H401" t="n">
         <v>4500</v>
@@ -12027,7 +12027,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G402" t="n">
-        <v>5.6915454864502</v>
+        <v>5.69154596328735</v>
       </c>
       <c r="H402" t="n">
         <v>0</v>
@@ -12056,7 +12056,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G403" t="n">
-        <v>5.6915454864502</v>
+        <v>5.69154596328735</v>
       </c>
       <c r="H403" t="n">
         <v>0</v>
@@ -12085,7 +12085,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G404" t="n">
-        <v>5.6915454864502</v>
+        <v>5.69154596328735</v>
       </c>
       <c r="H404" t="n">
         <v>1500</v>
@@ -12114,7 +12114,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G405" t="n">
-        <v>5.6915454864502</v>
+        <v>5.69154596328735</v>
       </c>
       <c r="H405" t="n">
         <v>600</v>
@@ -12143,7 +12143,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G406" t="n">
-        <v>5.6915454864502</v>
+        <v>5.69154596328735</v>
       </c>
       <c r="H406" t="n">
         <v>0</v>
@@ -12172,7 +12172,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G407" t="n">
-        <v>5.6915454864502</v>
+        <v>5.69154596328735</v>
       </c>
       <c r="H407" t="n">
         <v>600</v>
@@ -12201,7 +12201,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G408" t="n">
-        <v>5.6915454864502</v>
+        <v>5.69154596328735</v>
       </c>
       <c r="H408" t="n">
         <v>0</v>
@@ -12230,7 +12230,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G409" t="n">
-        <v>5.64290046691895</v>
+        <v>5.64289999008179</v>
       </c>
       <c r="H409" t="n">
         <v>1200</v>
@@ -12259,7 +12259,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G410" t="n">
-        <v>5.64290046691895</v>
+        <v>5.64289999008179</v>
       </c>
       <c r="H410" t="n">
         <v>0</v>
@@ -12288,7 +12288,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G411" t="n">
-        <v>5.64290046691895</v>
+        <v>5.64289999008179</v>
       </c>
       <c r="H411" t="n">
         <v>4800</v>
@@ -12317,7 +12317,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G412" t="n">
-        <v>5.64290046691895</v>
+        <v>5.64289999008179</v>
       </c>
       <c r="H412" t="n">
         <v>0</v>
@@ -12346,7 +12346,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G413" t="n">
-        <v>5.64290046691895</v>
+        <v>5.64289999008179</v>
       </c>
       <c r="H413" t="n">
         <v>0</v>
@@ -12375,7 +12375,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G414" t="n">
-        <v>5.64290046691895</v>
+        <v>5.64289999008179</v>
       </c>
       <c r="H414" t="n">
         <v>0</v>
@@ -12404,7 +12404,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G415" t="n">
-        <v>5.64290046691895</v>
+        <v>5.64289999008179</v>
       </c>
       <c r="H415" t="n">
         <v>0</v>
@@ -12462,7 +12462,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G417" t="n">
-        <v>5.6915454864502</v>
+        <v>5.69154596328735</v>
       </c>
       <c r="H417" t="n">
         <v>300</v>
@@ -12491,7 +12491,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G418" t="n">
-        <v>5.6915454864502</v>
+        <v>5.69154596328735</v>
       </c>
       <c r="H418" t="n">
         <v>0</v>
@@ -12520,7 +12520,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G419" t="n">
-        <v>5.6915454864502</v>
+        <v>5.69154596328735</v>
       </c>
       <c r="H419" t="n">
         <v>0</v>
@@ -12549,7 +12549,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G420" t="n">
-        <v>5.6915454864502</v>
+        <v>5.69154596328735</v>
       </c>
       <c r="H420" t="n">
         <v>0</v>
@@ -12578,7 +12578,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G421" t="n">
-        <v>5.6915454864502</v>
+        <v>5.69154596328735</v>
       </c>
       <c r="H421" t="n">
         <v>0</v>
@@ -12607,7 +12607,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G422" t="n">
-        <v>5.6915454864502</v>
+        <v>5.69154596328735</v>
       </c>
       <c r="H422" t="n">
         <v>0</v>
@@ -12665,7 +12665,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G424" t="n">
-        <v>5.6915454864502</v>
+        <v>5.69154596328735</v>
       </c>
       <c r="H424" t="n">
         <v>300</v>
@@ -12694,7 +12694,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G425" t="n">
-        <v>5.6915454864502</v>
+        <v>5.69154596328735</v>
       </c>
       <c r="H425" t="n">
         <v>0</v>
@@ -12723,7 +12723,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G426" t="n">
-        <v>5.64290046691895</v>
+        <v>5.64289999008179</v>
       </c>
       <c r="H426" t="n">
         <v>900</v>
@@ -12810,7 +12810,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G429" t="n">
-        <v>5.64290046691895</v>
+        <v>5.64289999008179</v>
       </c>
       <c r="H429" t="n">
         <v>1200</v>
@@ -12839,7 +12839,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G430" t="n">
-        <v>5.64290046691895</v>
+        <v>5.64289999008179</v>
       </c>
       <c r="H430" t="n">
         <v>300</v>
@@ -12868,7 +12868,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G431" t="n">
-        <v>5.64290046691895</v>
+        <v>5.64289999008179</v>
       </c>
       <c r="H431" t="n">
         <v>600</v>
@@ -12897,7 +12897,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G432" t="n">
-        <v>5.64290046691895</v>
+        <v>5.64289999008179</v>
       </c>
       <c r="H432" t="n">
         <v>0</v>
@@ -12926,7 +12926,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G433" t="n">
-        <v>5.64290046691895</v>
+        <v>5.64289999008179</v>
       </c>
       <c r="H433" t="n">
         <v>0</v>
@@ -12955,7 +12955,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G434" t="n">
-        <v>5.64290046691895</v>
+        <v>5.64289999008179</v>
       </c>
       <c r="H434" t="n">
         <v>0</v>
@@ -12984,7 +12984,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G435" t="n">
-        <v>5.64290046691895</v>
+        <v>5.64289999008179</v>
       </c>
       <c r="H435" t="n">
         <v>0</v>
@@ -13013,7 +13013,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G436" t="n">
-        <v>5.64290046691895</v>
+        <v>5.64289999008179</v>
       </c>
       <c r="H436" t="n">
         <v>0</v>
@@ -13042,7 +13042,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G437" t="n">
-        <v>5.64290046691895</v>
+        <v>5.64289999008179</v>
       </c>
       <c r="H437" t="n">
         <v>0</v>
@@ -13071,7 +13071,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G438" t="n">
-        <v>5.64290046691895</v>
+        <v>5.64289999008179</v>
       </c>
       <c r="H438" t="n">
         <v>0</v>
@@ -13100,7 +13100,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G439" t="n">
-        <v>5.64290046691895</v>
+        <v>5.64289999008179</v>
       </c>
       <c r="H439" t="n">
         <v>0</v>
@@ -13129,7 +13129,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G440" t="n">
-        <v>5.64290046691895</v>
+        <v>5.64289999008179</v>
       </c>
       <c r="H440" t="n">
         <v>0</v>
@@ -13158,7 +13158,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G441" t="n">
-        <v>5.64290046691895</v>
+        <v>5.64289999008179</v>
       </c>
       <c r="H441" t="n">
         <v>0</v>
@@ -13187,7 +13187,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G442" t="n">
-        <v>5.64290046691895</v>
+        <v>5.64289999008179</v>
       </c>
       <c r="H442" t="n">
         <v>0</v>
@@ -13216,7 +13216,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G443" t="n">
-        <v>5.64290046691895</v>
+        <v>5.64289999008179</v>
       </c>
       <c r="H443" t="n">
         <v>0</v>
@@ -13419,7 +13419,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G450" t="n">
-        <v>5.64290046691895</v>
+        <v>5.64289999008179</v>
       </c>
       <c r="H450" t="n">
         <v>4500</v>
@@ -13506,7 +13506,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G453" t="n">
-        <v>5.6915454864502</v>
+        <v>5.69154596328735</v>
       </c>
       <c r="H453" t="n">
         <v>900</v>
@@ -13535,7 +13535,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G454" t="n">
-        <v>5.6915454864502</v>
+        <v>5.69154596328735</v>
       </c>
       <c r="H454" t="n">
         <v>0</v>
@@ -13680,7 +13680,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G459" t="n">
-        <v>6.37258529663086</v>
+        <v>6.37258577346802</v>
       </c>
       <c r="H459" t="n">
         <v>1500</v>
@@ -13709,7 +13709,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G460" t="n">
-        <v>6.37258529663086</v>
+        <v>6.37258577346802</v>
       </c>
       <c r="H460" t="n">
         <v>0</v>
@@ -13738,7 +13738,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G461" t="n">
-        <v>6.37258529663086</v>
+        <v>6.37258577346802</v>
       </c>
       <c r="H461" t="n">
         <v>0</v>
@@ -13767,7 +13767,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G462" t="n">
-        <v>6.37258529663086</v>
+        <v>6.37258577346802</v>
       </c>
       <c r="H462" t="n">
         <v>0</v>
@@ -13796,7 +13796,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G463" t="n">
-        <v>6.37258529663086</v>
+        <v>6.37258577346802</v>
       </c>
       <c r="H463" t="n">
         <v>0</v>
@@ -13825,7 +13825,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G464" t="n">
-        <v>6.37258529663086</v>
+        <v>6.37258577346802</v>
       </c>
       <c r="H464" t="n">
         <v>300</v>
@@ -13854,7 +13854,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G465" t="n">
-        <v>6.37258529663086</v>
+        <v>6.37258577346802</v>
       </c>
       <c r="H465" t="n">
         <v>4800</v>
@@ -13912,7 +13912,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G467" t="n">
-        <v>6.42123126983643</v>
+        <v>6.42123079299927</v>
       </c>
       <c r="H467" t="n">
         <v>6900</v>
@@ -14028,7 +14028,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G471" t="n">
-        <v>6.37258529663086</v>
+        <v>6.37258577346802</v>
       </c>
       <c r="H471" t="n">
         <v>600</v>
@@ -14057,7 +14057,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G472" t="n">
-        <v>6.22664833068848</v>
+        <v>6.22664880752563</v>
       </c>
       <c r="H472" t="n">
         <v>600</v>
@@ -14086,7 +14086,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G473" t="n">
-        <v>6.22664833068848</v>
+        <v>6.22664880752563</v>
       </c>
       <c r="H473" t="n">
         <v>0</v>
@@ -14115,7 +14115,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G474" t="n">
-        <v>6.22664833068848</v>
+        <v>6.22664880752563</v>
       </c>
       <c r="H474" t="n">
         <v>0</v>
@@ -14144,7 +14144,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G475" t="n">
-        <v>6.22664833068848</v>
+        <v>6.22664880752563</v>
       </c>
       <c r="H475" t="n">
         <v>0</v>
@@ -14173,7 +14173,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G476" t="n">
-        <v>6.22664833068848</v>
+        <v>6.22664880752563</v>
       </c>
       <c r="H476" t="n">
         <v>0</v>
@@ -14202,7 +14202,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G477" t="n">
-        <v>6.22664833068848</v>
+        <v>6.22664880752563</v>
       </c>
       <c r="H477" t="n">
         <v>0</v>
@@ -14231,7 +14231,7 @@
         <v>6.65000009536743</v>
       </c>
       <c r="G478" t="n">
-        <v>6.46987676620483</v>
+        <v>6.46987724304199</v>
       </c>
       <c r="H478" t="n">
         <v>2400</v>
@@ -14289,7 +14289,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G480" t="n">
-        <v>6.37258529663086</v>
+        <v>6.37258577346802</v>
       </c>
       <c r="H480" t="n">
         <v>1800</v>
@@ -14347,7 +14347,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G482" t="n">
-        <v>6.22664833068848</v>
+        <v>6.22664880752563</v>
       </c>
       <c r="H482" t="n">
         <v>3000</v>
@@ -14376,7 +14376,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G483" t="n">
-        <v>6.22664833068848</v>
+        <v>6.22664880752563</v>
       </c>
       <c r="H483" t="n">
         <v>0</v>
@@ -14405,7 +14405,7 @@
         <v>6.65000009536743</v>
       </c>
       <c r="G484" t="n">
-        <v>6.46987676620483</v>
+        <v>6.46987724304199</v>
       </c>
       <c r="H484" t="n">
         <v>2400</v>
@@ -14434,7 +14434,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G485" t="n">
-        <v>6.22664833068848</v>
+        <v>6.22664880752563</v>
       </c>
       <c r="H485" t="n">
         <v>1500</v>
@@ -14521,7 +14521,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G488" t="n">
-        <v>6.22664833068848</v>
+        <v>6.22664880752563</v>
       </c>
       <c r="H488" t="n">
         <v>4200</v>
@@ -14956,7 +14956,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G503" t="n">
-        <v>6.37258529663086</v>
+        <v>6.37258577346802</v>
       </c>
       <c r="H503" t="n">
         <v>1800</v>
@@ -14985,7 +14985,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G504" t="n">
-        <v>6.22664833068848</v>
+        <v>6.22664880752563</v>
       </c>
       <c r="H504" t="n">
         <v>2700</v>
@@ -15014,7 +15014,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G505" t="n">
-        <v>6.22664833068848</v>
+        <v>6.22664880752563</v>
       </c>
       <c r="H505" t="n">
         <v>0</v>
@@ -15043,7 +15043,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G506" t="n">
-        <v>6.22664833068848</v>
+        <v>6.22664880752563</v>
       </c>
       <c r="H506" t="n">
         <v>0</v>
@@ -15710,7 +15710,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G529" t="n">
-        <v>6.22664833068848</v>
+        <v>6.22664880752563</v>
       </c>
       <c r="H529" t="n">
         <v>3300</v>
@@ -15768,7 +15768,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G531" t="n">
-        <v>6.42123126983643</v>
+        <v>6.42123079299927</v>
       </c>
       <c r="H531" t="n">
         <v>1200</v>
@@ -15826,7 +15826,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G533" t="n">
-        <v>5.6915454864502</v>
+        <v>5.69154596328735</v>
       </c>
       <c r="H533" t="n">
         <v>8700</v>
@@ -15855,7 +15855,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G534" t="n">
-        <v>5.6915454864502</v>
+        <v>5.69154596328735</v>
       </c>
       <c r="H534" t="n">
         <v>300</v>
@@ -15884,7 +15884,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G535" t="n">
-        <v>5.6915454864502</v>
+        <v>5.69154596328735</v>
       </c>
       <c r="H535" t="n">
         <v>0</v>
@@ -15913,7 +15913,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G536" t="n">
-        <v>5.64290046691895</v>
+        <v>5.64289999008179</v>
       </c>
       <c r="H536" t="n">
         <v>2400</v>
@@ -16232,7 +16232,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G547" t="n">
-        <v>6.22664833068848</v>
+        <v>6.22664880752563</v>
       </c>
       <c r="H547" t="n">
         <v>1500</v>
@@ -16261,7 +16261,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G548" t="n">
-        <v>6.22664833068848</v>
+        <v>6.22664880752563</v>
       </c>
       <c r="H548" t="n">
         <v>1200</v>
@@ -16290,7 +16290,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G549" t="n">
-        <v>6.22664833068848</v>
+        <v>6.22664880752563</v>
       </c>
       <c r="H549" t="n">
         <v>1200</v>
@@ -16348,7 +16348,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G551" t="n">
-        <v>6.37258529663086</v>
+        <v>6.37258577346802</v>
       </c>
       <c r="H551" t="n">
         <v>60600</v>
@@ -16377,7 +16377,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G552" t="n">
-        <v>6.37258529663086</v>
+        <v>6.37258577346802</v>
       </c>
       <c r="H552" t="n">
         <v>0</v>
@@ -16406,7 +16406,7 @@
         <v>6.65000009536743</v>
       </c>
       <c r="G553" t="n">
-        <v>6.46987676620483</v>
+        <v>6.46987724304199</v>
       </c>
       <c r="H553" t="n">
         <v>300</v>
@@ -16435,7 +16435,7 @@
         <v>6.65000009536743</v>
       </c>
       <c r="G554" t="n">
-        <v>6.46987676620483</v>
+        <v>6.46987724304199</v>
       </c>
       <c r="H554" t="n">
         <v>0</v>

--- a/data/VLT.MI.xlsx
+++ b/data/VLT.MI.xlsx
@@ -543,7 +543,7 @@
         <v>5.69799995422363</v>
       </c>
       <c r="G6" t="n">
-        <v>5.54366302490234</v>
+        <v>5.54366254806519</v>
       </c>
       <c r="H6" t="n">
         <v>18900</v>
@@ -717,7 +717,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G12" t="n">
-        <v>5.02023553848267</v>
+        <v>5.02023506164551</v>
       </c>
       <c r="H12" t="n">
         <v>3300</v>
@@ -804,7 +804,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G15" t="n">
-        <v>5.15644311904907</v>
+        <v>5.15644359588623</v>
       </c>
       <c r="H15" t="n">
         <v>1500</v>
@@ -1094,7 +1094,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G25" t="n">
-        <v>5.19536018371582</v>
+        <v>5.19535970687866</v>
       </c>
       <c r="H25" t="n">
         <v>1800</v>
@@ -1123,7 +1123,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G26" t="n">
-        <v>5.19536018371582</v>
+        <v>5.19535970687866</v>
       </c>
       <c r="H26" t="n">
         <v>0</v>
@@ -1152,7 +1152,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G27" t="n">
-        <v>5.19536018371582</v>
+        <v>5.19535970687866</v>
       </c>
       <c r="H27" t="n">
         <v>0</v>
@@ -1384,7 +1384,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G35" t="n">
-        <v>5.38994264602661</v>
+        <v>5.38994216918945</v>
       </c>
       <c r="H35" t="n">
         <v>300</v>
@@ -1848,7 +1848,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G51" t="n">
-        <v>4.65052843093872</v>
+        <v>4.65052795410156</v>
       </c>
       <c r="H51" t="n">
         <v>1500</v>
@@ -1993,7 +1993,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G56" t="n">
-        <v>4.70890331268311</v>
+        <v>4.70890283584595</v>
       </c>
       <c r="H56" t="n">
         <v>300</v>
@@ -2399,7 +2399,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G70" t="n">
-        <v>4.70890331268311</v>
+        <v>4.70890283584595</v>
       </c>
       <c r="H70" t="n">
         <v>300</v>
@@ -2747,7 +2747,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G82" t="n">
-        <v>4.70890331268311</v>
+        <v>4.70890283584595</v>
       </c>
       <c r="H82" t="n">
         <v>900</v>
@@ -2776,7 +2776,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G83" t="n">
-        <v>4.70890331268311</v>
+        <v>4.70890283584595</v>
       </c>
       <c r="H83" t="n">
         <v>0</v>
@@ -2805,7 +2805,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G84" t="n">
-        <v>4.66025686264038</v>
+        <v>4.66025733947754</v>
       </c>
       <c r="H84" t="n">
         <v>1200</v>
@@ -3298,7 +3298,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G101" t="n">
-        <v>4.70890331268311</v>
+        <v>4.70890283584595</v>
       </c>
       <c r="H101" t="n">
         <v>1200</v>
@@ -3356,7 +3356,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G103" t="n">
-        <v>4.66025686264038</v>
+        <v>4.66025733947754</v>
       </c>
       <c r="H103" t="n">
         <v>300</v>
@@ -3385,7 +3385,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G104" t="n">
-        <v>4.66025686264038</v>
+        <v>4.66025733947754</v>
       </c>
       <c r="H104" t="n">
         <v>0</v>
@@ -3414,7 +3414,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G105" t="n">
-        <v>4.66025686264038</v>
+        <v>4.66025733947754</v>
       </c>
       <c r="H105" t="n">
         <v>0</v>
@@ -3443,7 +3443,7 @@
         <v>4.5</v>
       </c>
       <c r="G106" t="n">
-        <v>4.37811183929443</v>
+        <v>4.37811231613159</v>
       </c>
       <c r="H106" t="n">
         <v>4800</v>
@@ -3472,7 +3472,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G107" t="n">
-        <v>4.47540330886841</v>
+        <v>4.47540378570557</v>
       </c>
       <c r="H107" t="n">
         <v>3600</v>
@@ -3501,7 +3501,7 @@
         <v>4.5</v>
       </c>
       <c r="G108" t="n">
-        <v>4.37811183929443</v>
+        <v>4.37811231613159</v>
       </c>
       <c r="H108" t="n">
         <v>600</v>
@@ -3646,7 +3646,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G113" t="n">
-        <v>4.47540330886841</v>
+        <v>4.47540378570557</v>
       </c>
       <c r="H113" t="n">
         <v>300</v>
@@ -3675,7 +3675,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G114" t="n">
-        <v>4.47540330886841</v>
+        <v>4.47540378570557</v>
       </c>
       <c r="H114" t="n">
         <v>300</v>
@@ -3733,7 +3733,7 @@
         <v>4.53000020980835</v>
       </c>
       <c r="G116" t="n">
-        <v>4.40729951858521</v>
+        <v>4.40729999542236</v>
       </c>
       <c r="H116" t="n">
         <v>2700</v>
@@ -3762,7 +3762,7 @@
         <v>4.53000020980835</v>
       </c>
       <c r="G117" t="n">
-        <v>4.40729951858521</v>
+        <v>4.40729999542236</v>
       </c>
       <c r="H117" t="n">
         <v>0</v>
@@ -4255,7 +4255,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G134" t="n">
-        <v>4.3586540222168</v>
+        <v>4.35865354537964</v>
       </c>
       <c r="H134" t="n">
         <v>600</v>
@@ -4284,7 +4284,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G135" t="n">
-        <v>4.3586540222168</v>
+        <v>4.35865354537964</v>
       </c>
       <c r="H135" t="n">
         <v>0</v>
@@ -4313,7 +4313,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G136" t="n">
-        <v>4.3586540222168</v>
+        <v>4.35865354537964</v>
       </c>
       <c r="H136" t="n">
         <v>0</v>
@@ -4342,7 +4342,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G137" t="n">
-        <v>4.3586540222168</v>
+        <v>4.35865354537964</v>
       </c>
       <c r="H137" t="n">
         <v>0</v>
@@ -4371,7 +4371,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G138" t="n">
-        <v>4.3586540222168</v>
+        <v>4.35865354537964</v>
       </c>
       <c r="H138" t="n">
         <v>0</v>
@@ -4400,7 +4400,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G139" t="n">
-        <v>4.3586540222168</v>
+        <v>4.35865354537964</v>
       </c>
       <c r="H139" t="n">
         <v>0</v>
@@ -4429,7 +4429,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G140" t="n">
-        <v>4.3586540222168</v>
+        <v>4.35865354537964</v>
       </c>
       <c r="H140" t="n">
         <v>3000</v>
@@ -4458,7 +4458,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G141" t="n">
-        <v>4.3586540222168</v>
+        <v>4.35865354537964</v>
       </c>
       <c r="H141" t="n">
         <v>0</v>
@@ -4632,7 +4632,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G147" t="n">
-        <v>4.96186017990112</v>
+        <v>4.96186065673828</v>
       </c>
       <c r="H147" t="n">
         <v>1500</v>
@@ -4661,7 +4661,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G148" t="n">
-        <v>4.73809051513672</v>
+        <v>4.73809003829956</v>
       </c>
       <c r="H148" t="n">
         <v>4500</v>
@@ -4690,7 +4690,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G149" t="n">
-        <v>4.66025686264038</v>
+        <v>4.66025733947754</v>
       </c>
       <c r="H149" t="n">
         <v>2100</v>
@@ -4777,7 +4777,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G152" t="n">
-        <v>4.70890331268311</v>
+        <v>4.70890283584595</v>
       </c>
       <c r="H152" t="n">
         <v>600</v>
@@ -4980,7 +4980,7 @@
         <v>4.5</v>
       </c>
       <c r="G159" t="n">
-        <v>4.37811183929443</v>
+        <v>4.37811231613159</v>
       </c>
       <c r="H159" t="n">
         <v>3900</v>
@@ -5009,7 +5009,7 @@
         <v>4.5</v>
       </c>
       <c r="G160" t="n">
-        <v>4.37811183929443</v>
+        <v>4.37811231613159</v>
       </c>
       <c r="H160" t="n">
         <v>0</v>
@@ -5038,7 +5038,7 @@
         <v>4.5</v>
       </c>
       <c r="G161" t="n">
-        <v>4.37811183929443</v>
+        <v>4.37811231613159</v>
       </c>
       <c r="H161" t="n">
         <v>1800</v>
@@ -5067,7 +5067,7 @@
         <v>4.5</v>
       </c>
       <c r="G162" t="n">
-        <v>4.37811183929443</v>
+        <v>4.37811231613159</v>
       </c>
       <c r="H162" t="n">
         <v>1200</v>
@@ -5212,7 +5212,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G167" t="n">
-        <v>4.47540330886841</v>
+        <v>4.47540378570557</v>
       </c>
       <c r="H167" t="n">
         <v>900</v>
@@ -5241,7 +5241,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G168" t="n">
-        <v>4.47540330886841</v>
+        <v>4.47540378570557</v>
       </c>
       <c r="H168" t="n">
         <v>0</v>
@@ -5270,7 +5270,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G169" t="n">
-        <v>4.47540330886841</v>
+        <v>4.47540378570557</v>
       </c>
       <c r="H169" t="n">
         <v>0</v>
@@ -5299,7 +5299,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G170" t="n">
-        <v>4.47540330886841</v>
+        <v>4.47540378570557</v>
       </c>
       <c r="H170" t="n">
         <v>0</v>
@@ -5328,7 +5328,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G171" t="n">
-        <v>4.47540330886841</v>
+        <v>4.47540378570557</v>
       </c>
       <c r="H171" t="n">
         <v>0</v>
@@ -5357,7 +5357,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G172" t="n">
-        <v>4.47540330886841</v>
+        <v>4.47540378570557</v>
       </c>
       <c r="H172" t="n">
         <v>0</v>
@@ -5386,7 +5386,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G173" t="n">
-        <v>4.47540330886841</v>
+        <v>4.47540378570557</v>
       </c>
       <c r="H173" t="n">
         <v>0</v>
@@ -5415,7 +5415,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G174" t="n">
-        <v>4.47540330886841</v>
+        <v>4.47540378570557</v>
       </c>
       <c r="H174" t="n">
         <v>0</v>
@@ -5560,7 +5560,7 @@
         <v>4.76999998092651</v>
       </c>
       <c r="G179" t="n">
-        <v>4.64079904556274</v>
+        <v>4.64079856872559</v>
       </c>
       <c r="H179" t="n">
         <v>1200</v>
@@ -5618,7 +5618,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G181" t="n">
-        <v>4.68944454193115</v>
+        <v>4.68944501876831</v>
       </c>
       <c r="H181" t="n">
         <v>600</v>
@@ -5647,7 +5647,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G182" t="n">
-        <v>4.68944454193115</v>
+        <v>4.68944501876831</v>
       </c>
       <c r="H182" t="n">
         <v>300</v>
@@ -5676,7 +5676,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G183" t="n">
-        <v>4.68944454193115</v>
+        <v>4.68944501876831</v>
       </c>
       <c r="H183" t="n">
         <v>2400</v>
@@ -5705,7 +5705,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G184" t="n">
-        <v>4.68944454193115</v>
+        <v>4.68944501876831</v>
       </c>
       <c r="H184" t="n">
         <v>0</v>
@@ -5821,7 +5821,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G188" t="n">
-        <v>5.15644311904907</v>
+        <v>5.15644359588623</v>
       </c>
       <c r="H188" t="n">
         <v>600</v>
@@ -6198,7 +6198,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G201" t="n">
-        <v>4.96186017990112</v>
+        <v>4.96186065673828</v>
       </c>
       <c r="H201" t="n">
         <v>600</v>
@@ -6227,7 +6227,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G202" t="n">
-        <v>4.96186017990112</v>
+        <v>4.96186065673828</v>
       </c>
       <c r="H202" t="n">
         <v>300</v>
@@ -6256,7 +6256,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G203" t="n">
-        <v>4.96186017990112</v>
+        <v>4.96186065673828</v>
       </c>
       <c r="H203" t="n">
         <v>300</v>
@@ -6575,7 +6575,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G214" t="n">
-        <v>5.42885875701904</v>
+        <v>5.4288592338562</v>
       </c>
       <c r="H214" t="n">
         <v>3600</v>
@@ -6720,7 +6720,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G219" t="n">
-        <v>5.40940093994141</v>
+        <v>5.40940046310425</v>
       </c>
       <c r="H219" t="n">
         <v>1800</v>
@@ -7445,7 +7445,7 @@
         <v>6.03999996185303</v>
       </c>
       <c r="G244" t="n">
-        <v>5.87639951705933</v>
+        <v>5.87639904022217</v>
       </c>
       <c r="H244" t="n">
         <v>9300</v>
@@ -7909,7 +7909,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G260" t="n">
-        <v>5.64289999008179</v>
+        <v>5.64290046691895</v>
       </c>
       <c r="H260" t="n">
         <v>300</v>
@@ -7938,7 +7938,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G261" t="n">
-        <v>5.64289999008179</v>
+        <v>5.64290046691895</v>
       </c>
       <c r="H261" t="n">
         <v>0</v>
@@ -7967,7 +7967,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G262" t="n">
-        <v>5.64289999008179</v>
+        <v>5.64290046691895</v>
       </c>
       <c r="H262" t="n">
         <v>0</v>
@@ -7996,7 +7996,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G263" t="n">
-        <v>5.64289999008179</v>
+        <v>5.64290046691895</v>
       </c>
       <c r="H263" t="n">
         <v>0</v>
@@ -8025,7 +8025,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G264" t="n">
-        <v>5.64289999008179</v>
+        <v>5.64290046691895</v>
       </c>
       <c r="H264" t="n">
         <v>300</v>
@@ -8054,7 +8054,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G265" t="n">
-        <v>5.64289999008179</v>
+        <v>5.64290046691895</v>
       </c>
       <c r="H265" t="n">
         <v>0</v>
@@ -8112,7 +8112,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G267" t="n">
-        <v>5.64289999008179</v>
+        <v>5.64290046691895</v>
       </c>
       <c r="H267" t="n">
         <v>300</v>
@@ -8141,7 +8141,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G268" t="n">
-        <v>5.64289999008179</v>
+        <v>5.64290046691895</v>
       </c>
       <c r="H268" t="n">
         <v>0</v>
@@ -8315,7 +8315,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G274" t="n">
-        <v>5.72073316574097</v>
+        <v>5.72073364257812</v>
       </c>
       <c r="H274" t="n">
         <v>900</v>
@@ -8489,7 +8489,7 @@
         <v>6.05000019073486</v>
       </c>
       <c r="G280" t="n">
-        <v>5.8861289024353</v>
+        <v>5.88612842559814</v>
       </c>
       <c r="H280" t="n">
         <v>3900</v>
@@ -8576,7 +8576,7 @@
         <v>6.05000019073486</v>
       </c>
       <c r="G283" t="n">
-        <v>5.8861289024353</v>
+        <v>5.88612842559814</v>
       </c>
       <c r="H283" t="n">
         <v>4800</v>
@@ -8605,7 +8605,7 @@
         <v>6.05000019073486</v>
       </c>
       <c r="G284" t="n">
-        <v>5.8861289024353</v>
+        <v>5.88612842559814</v>
       </c>
       <c r="H284" t="n">
         <v>0</v>
@@ -9330,7 +9330,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G309" t="n">
-        <v>5.69154596328735</v>
+        <v>5.6915454864502</v>
       </c>
       <c r="H309" t="n">
         <v>5100</v>
@@ -9359,7 +9359,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G310" t="n">
-        <v>5.69154596328735</v>
+        <v>5.6915454864502</v>
       </c>
       <c r="H310" t="n">
         <v>4200</v>
@@ -9388,7 +9388,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G311" t="n">
-        <v>5.69154596328735</v>
+        <v>5.6915454864502</v>
       </c>
       <c r="H311" t="n">
         <v>3000</v>
@@ -9417,7 +9417,7 @@
         <v>5.75</v>
       </c>
       <c r="G312" t="n">
-        <v>5.59425449371338</v>
+        <v>5.59425401687622</v>
       </c>
       <c r="H312" t="n">
         <v>2400</v>
@@ -9446,7 +9446,7 @@
         <v>5.75</v>
       </c>
       <c r="G313" t="n">
-        <v>5.59425449371338</v>
+        <v>5.59425401687622</v>
       </c>
       <c r="H313" t="n">
         <v>5100</v>
@@ -9475,7 +9475,7 @@
         <v>5.75</v>
       </c>
       <c r="G314" t="n">
-        <v>5.59425449371338</v>
+        <v>5.59425401687622</v>
       </c>
       <c r="H314" t="n">
         <v>0</v>
@@ -9504,7 +9504,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G315" t="n">
-        <v>5.69154596328735</v>
+        <v>5.6915454864502</v>
       </c>
       <c r="H315" t="n">
         <v>2100</v>
@@ -9533,7 +9533,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G316" t="n">
-        <v>5.69154596328735</v>
+        <v>5.6915454864502</v>
       </c>
       <c r="H316" t="n">
         <v>300</v>
@@ -9562,7 +9562,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G317" t="n">
-        <v>5.69154596328735</v>
+        <v>5.6915454864502</v>
       </c>
       <c r="H317" t="n">
         <v>0</v>
@@ -9591,7 +9591,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G318" t="n">
-        <v>5.69154596328735</v>
+        <v>5.6915454864502</v>
       </c>
       <c r="H318" t="n">
         <v>0</v>
@@ -9620,7 +9620,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G319" t="n">
-        <v>5.69154596328735</v>
+        <v>5.6915454864502</v>
       </c>
       <c r="H319" t="n">
         <v>0</v>
@@ -9765,7 +9765,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G324" t="n">
-        <v>5.64289999008179</v>
+        <v>5.64290046691895</v>
       </c>
       <c r="H324" t="n">
         <v>600</v>
@@ -9794,7 +9794,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G325" t="n">
-        <v>5.64289999008179</v>
+        <v>5.64290046691895</v>
       </c>
       <c r="H325" t="n">
         <v>0</v>
@@ -9823,7 +9823,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G326" t="n">
-        <v>5.64289999008179</v>
+        <v>5.64290046691895</v>
       </c>
       <c r="H326" t="n">
         <v>0</v>
@@ -9852,7 +9852,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G327" t="n">
-        <v>5.64289999008179</v>
+        <v>5.64290046691895</v>
       </c>
       <c r="H327" t="n">
         <v>0</v>
@@ -9881,7 +9881,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G328" t="n">
-        <v>5.64289999008179</v>
+        <v>5.64290046691895</v>
       </c>
       <c r="H328" t="n">
         <v>0</v>
@@ -9910,7 +9910,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G329" t="n">
-        <v>5.64289999008179</v>
+        <v>5.64290046691895</v>
       </c>
       <c r="H329" t="n">
         <v>0</v>
@@ -9939,7 +9939,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G330" t="n">
-        <v>5.64289999008179</v>
+        <v>5.64290046691895</v>
       </c>
       <c r="H330" t="n">
         <v>0</v>
@@ -9968,7 +9968,7 @@
         <v>6.05000019073486</v>
       </c>
       <c r="G331" t="n">
-        <v>5.8861289024353</v>
+        <v>5.88612842559814</v>
       </c>
       <c r="H331" t="n">
         <v>1500</v>
@@ -9997,7 +9997,7 @@
         <v>6.05000019073486</v>
       </c>
       <c r="G332" t="n">
-        <v>5.8861289024353</v>
+        <v>5.88612842559814</v>
       </c>
       <c r="H332" t="n">
         <v>0</v>
@@ -10026,7 +10026,7 @@
         <v>6.05000019073486</v>
       </c>
       <c r="G333" t="n">
-        <v>5.8861289024353</v>
+        <v>5.88612842559814</v>
       </c>
       <c r="H333" t="n">
         <v>0</v>
@@ -10055,7 +10055,7 @@
         <v>6.05000019073486</v>
       </c>
       <c r="G334" t="n">
-        <v>5.8861289024353</v>
+        <v>5.88612842559814</v>
       </c>
       <c r="H334" t="n">
         <v>0</v>
@@ -10084,7 +10084,7 @@
         <v>6.05000019073486</v>
       </c>
       <c r="G335" t="n">
-        <v>5.8861289024353</v>
+        <v>5.88612842559814</v>
       </c>
       <c r="H335" t="n">
         <v>0</v>
@@ -10113,7 +10113,7 @@
         <v>6.05000019073486</v>
       </c>
       <c r="G336" t="n">
-        <v>5.8861289024353</v>
+        <v>5.88612842559814</v>
       </c>
       <c r="H336" t="n">
         <v>0</v>
@@ -10142,7 +10142,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G337" t="n">
-        <v>5.64289999008179</v>
+        <v>5.64290046691895</v>
       </c>
       <c r="H337" t="n">
         <v>300</v>
@@ -10316,7 +10316,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G343" t="n">
-        <v>5.64289999008179</v>
+        <v>5.64290046691895</v>
       </c>
       <c r="H343" t="n">
         <v>1200</v>
@@ -10345,7 +10345,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G344" t="n">
-        <v>5.64289999008179</v>
+        <v>5.64290046691895</v>
       </c>
       <c r="H344" t="n">
         <v>0</v>
@@ -10374,7 +10374,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G345" t="n">
-        <v>5.64289999008179</v>
+        <v>5.64290046691895</v>
       </c>
       <c r="H345" t="n">
         <v>300</v>
@@ -10403,7 +10403,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G346" t="n">
-        <v>5.64289999008179</v>
+        <v>5.64290046691895</v>
       </c>
       <c r="H346" t="n">
         <v>0</v>
@@ -11128,7 +11128,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G371" t="n">
-        <v>5.64289999008179</v>
+        <v>5.64290046691895</v>
       </c>
       <c r="H371" t="n">
         <v>300</v>
@@ -11157,7 +11157,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G372" t="n">
-        <v>5.64289999008179</v>
+        <v>5.64290046691895</v>
       </c>
       <c r="H372" t="n">
         <v>0</v>
@@ -11186,7 +11186,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G373" t="n">
-        <v>5.64289999008179</v>
+        <v>5.64290046691895</v>
       </c>
       <c r="H373" t="n">
         <v>0</v>
@@ -11215,7 +11215,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G374" t="n">
-        <v>5.64289999008179</v>
+        <v>5.64290046691895</v>
       </c>
       <c r="H374" t="n">
         <v>0</v>
@@ -11244,7 +11244,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G375" t="n">
-        <v>5.64289999008179</v>
+        <v>5.64290046691895</v>
       </c>
       <c r="H375" t="n">
         <v>600</v>
@@ -11273,7 +11273,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G376" t="n">
-        <v>5.64289999008179</v>
+        <v>5.64290046691895</v>
       </c>
       <c r="H376" t="n">
         <v>0</v>
@@ -11302,7 +11302,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G377" t="n">
-        <v>5.64289999008179</v>
+        <v>5.64290046691895</v>
       </c>
       <c r="H377" t="n">
         <v>0</v>
@@ -11331,7 +11331,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G378" t="n">
-        <v>5.64289999008179</v>
+        <v>5.64290046691895</v>
       </c>
       <c r="H378" t="n">
         <v>0</v>
@@ -11360,7 +11360,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G379" t="n">
-        <v>5.64289999008179</v>
+        <v>5.64290046691895</v>
       </c>
       <c r="H379" t="n">
         <v>0</v>
@@ -11389,7 +11389,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G380" t="n">
-        <v>5.64289999008179</v>
+        <v>5.64290046691895</v>
       </c>
       <c r="H380" t="n">
         <v>0</v>
@@ -11650,7 +11650,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G389" t="n">
-        <v>5.69154596328735</v>
+        <v>5.6915454864502</v>
       </c>
       <c r="H389" t="n">
         <v>300</v>
@@ -11679,7 +11679,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G390" t="n">
-        <v>5.69154596328735</v>
+        <v>5.6915454864502</v>
       </c>
       <c r="H390" t="n">
         <v>0</v>
@@ -11708,7 +11708,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G391" t="n">
-        <v>5.69154596328735</v>
+        <v>5.6915454864502</v>
       </c>
       <c r="H391" t="n">
         <v>0</v>
@@ -11940,7 +11940,7 @@
         <v>5.75</v>
       </c>
       <c r="G399" t="n">
-        <v>5.59425449371338</v>
+        <v>5.59425401687622</v>
       </c>
       <c r="H399" t="n">
         <v>1500</v>
@@ -11969,7 +11969,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G400" t="n">
-        <v>5.69154596328735</v>
+        <v>5.6915454864502</v>
       </c>
       <c r="H400" t="n">
         <v>1200</v>
@@ -11998,7 +11998,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G401" t="n">
-        <v>5.69154596328735</v>
+        <v>5.6915454864502</v>
       </c>
       <c r="H401" t="n">
         <v>4500</v>
@@ -12027,7 +12027,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G402" t="n">
-        <v>5.69154596328735</v>
+        <v>5.6915454864502</v>
       </c>
       <c r="H402" t="n">
         <v>0</v>
@@ -12056,7 +12056,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G403" t="n">
-        <v>5.69154596328735</v>
+        <v>5.6915454864502</v>
       </c>
       <c r="H403" t="n">
         <v>0</v>
@@ -12085,7 +12085,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G404" t="n">
-        <v>5.69154596328735</v>
+        <v>5.6915454864502</v>
       </c>
       <c r="H404" t="n">
         <v>1500</v>
@@ -12114,7 +12114,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G405" t="n">
-        <v>5.69154596328735</v>
+        <v>5.6915454864502</v>
       </c>
       <c r="H405" t="n">
         <v>600</v>
@@ -12143,7 +12143,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G406" t="n">
-        <v>5.69154596328735</v>
+        <v>5.6915454864502</v>
       </c>
       <c r="H406" t="n">
         <v>0</v>
@@ -12172,7 +12172,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G407" t="n">
-        <v>5.69154596328735</v>
+        <v>5.6915454864502</v>
       </c>
       <c r="H407" t="n">
         <v>600</v>
@@ -12201,7 +12201,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G408" t="n">
-        <v>5.69154596328735</v>
+        <v>5.6915454864502</v>
       </c>
       <c r="H408" t="n">
         <v>0</v>
@@ -12230,7 +12230,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G409" t="n">
-        <v>5.64289999008179</v>
+        <v>5.64290046691895</v>
       </c>
       <c r="H409" t="n">
         <v>1200</v>
@@ -12259,7 +12259,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G410" t="n">
-        <v>5.64289999008179</v>
+        <v>5.64290046691895</v>
       </c>
       <c r="H410" t="n">
         <v>0</v>
@@ -12288,7 +12288,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G411" t="n">
-        <v>5.64289999008179</v>
+        <v>5.64290046691895</v>
       </c>
       <c r="H411" t="n">
         <v>4800</v>
@@ -12317,7 +12317,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G412" t="n">
-        <v>5.64289999008179</v>
+        <v>5.64290046691895</v>
       </c>
       <c r="H412" t="n">
         <v>0</v>
@@ -12346,7 +12346,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G413" t="n">
-        <v>5.64289999008179</v>
+        <v>5.64290046691895</v>
       </c>
       <c r="H413" t="n">
         <v>0</v>
@@ -12375,7 +12375,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G414" t="n">
-        <v>5.64289999008179</v>
+        <v>5.64290046691895</v>
       </c>
       <c r="H414" t="n">
         <v>0</v>
@@ -12404,7 +12404,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G415" t="n">
-        <v>5.64289999008179</v>
+        <v>5.64290046691895</v>
       </c>
       <c r="H415" t="n">
         <v>0</v>
@@ -12462,7 +12462,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G417" t="n">
-        <v>5.69154596328735</v>
+        <v>5.6915454864502</v>
       </c>
       <c r="H417" t="n">
         <v>300</v>
@@ -12491,7 +12491,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G418" t="n">
-        <v>5.69154596328735</v>
+        <v>5.6915454864502</v>
       </c>
       <c r="H418" t="n">
         <v>0</v>
@@ -12520,7 +12520,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G419" t="n">
-        <v>5.69154596328735</v>
+        <v>5.6915454864502</v>
       </c>
       <c r="H419" t="n">
         <v>0</v>
@@ -12549,7 +12549,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G420" t="n">
-        <v>5.69154596328735</v>
+        <v>5.6915454864502</v>
       </c>
       <c r="H420" t="n">
         <v>0</v>
@@ -12578,7 +12578,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G421" t="n">
-        <v>5.69154596328735</v>
+        <v>5.6915454864502</v>
       </c>
       <c r="H421" t="n">
         <v>0</v>
@@ -12607,7 +12607,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G422" t="n">
-        <v>5.69154596328735</v>
+        <v>5.6915454864502</v>
       </c>
       <c r="H422" t="n">
         <v>0</v>
@@ -12665,7 +12665,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G424" t="n">
-        <v>5.69154596328735</v>
+        <v>5.6915454864502</v>
       </c>
       <c r="H424" t="n">
         <v>300</v>
@@ -12694,7 +12694,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G425" t="n">
-        <v>5.69154596328735</v>
+        <v>5.6915454864502</v>
       </c>
       <c r="H425" t="n">
         <v>0</v>
@@ -12723,7 +12723,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G426" t="n">
-        <v>5.64289999008179</v>
+        <v>5.64290046691895</v>
       </c>
       <c r="H426" t="n">
         <v>900</v>
@@ -12810,7 +12810,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G429" t="n">
-        <v>5.64289999008179</v>
+        <v>5.64290046691895</v>
       </c>
       <c r="H429" t="n">
         <v>1200</v>
@@ -12839,7 +12839,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G430" t="n">
-        <v>5.64289999008179</v>
+        <v>5.64290046691895</v>
       </c>
       <c r="H430" t="n">
         <v>300</v>
@@ -12868,7 +12868,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G431" t="n">
-        <v>5.64289999008179</v>
+        <v>5.64290046691895</v>
       </c>
       <c r="H431" t="n">
         <v>600</v>
@@ -12897,7 +12897,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G432" t="n">
-        <v>5.64289999008179</v>
+        <v>5.64290046691895</v>
       </c>
       <c r="H432" t="n">
         <v>0</v>
@@ -12926,7 +12926,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G433" t="n">
-        <v>5.64289999008179</v>
+        <v>5.64290046691895</v>
       </c>
       <c r="H433" t="n">
         <v>0</v>
@@ -12955,7 +12955,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G434" t="n">
-        <v>5.64289999008179</v>
+        <v>5.64290046691895</v>
       </c>
       <c r="H434" t="n">
         <v>0</v>
@@ -12984,7 +12984,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G435" t="n">
-        <v>5.64289999008179</v>
+        <v>5.64290046691895</v>
       </c>
       <c r="H435" t="n">
         <v>0</v>
@@ -13013,7 +13013,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G436" t="n">
-        <v>5.64289999008179</v>
+        <v>5.64290046691895</v>
       </c>
       <c r="H436" t="n">
         <v>0</v>
@@ -13042,7 +13042,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G437" t="n">
-        <v>5.64289999008179</v>
+        <v>5.64290046691895</v>
       </c>
       <c r="H437" t="n">
         <v>0</v>
@@ -13071,7 +13071,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G438" t="n">
-        <v>5.64289999008179</v>
+        <v>5.64290046691895</v>
       </c>
       <c r="H438" t="n">
         <v>0</v>
@@ -13100,7 +13100,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G439" t="n">
-        <v>5.64289999008179</v>
+        <v>5.64290046691895</v>
       </c>
       <c r="H439" t="n">
         <v>0</v>
@@ -13129,7 +13129,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G440" t="n">
-        <v>5.64289999008179</v>
+        <v>5.64290046691895</v>
       </c>
       <c r="H440" t="n">
         <v>0</v>
@@ -13158,7 +13158,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G441" t="n">
-        <v>5.64289999008179</v>
+        <v>5.64290046691895</v>
       </c>
       <c r="H441" t="n">
         <v>0</v>
@@ -13187,7 +13187,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G442" t="n">
-        <v>5.64289999008179</v>
+        <v>5.64290046691895</v>
       </c>
       <c r="H442" t="n">
         <v>0</v>
@@ -13216,7 +13216,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G443" t="n">
-        <v>5.64289999008179</v>
+        <v>5.64290046691895</v>
       </c>
       <c r="H443" t="n">
         <v>0</v>
@@ -13419,7 +13419,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G450" t="n">
-        <v>5.64289999008179</v>
+        <v>5.64290046691895</v>
       </c>
       <c r="H450" t="n">
         <v>4500</v>
@@ -13506,7 +13506,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G453" t="n">
-        <v>5.69154596328735</v>
+        <v>5.6915454864502</v>
       </c>
       <c r="H453" t="n">
         <v>900</v>
@@ -13535,7 +13535,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G454" t="n">
-        <v>5.69154596328735</v>
+        <v>5.6915454864502</v>
       </c>
       <c r="H454" t="n">
         <v>0</v>
@@ -13680,7 +13680,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G459" t="n">
-        <v>6.37258577346802</v>
+        <v>6.37258529663086</v>
       </c>
       <c r="H459" t="n">
         <v>1500</v>
@@ -13709,7 +13709,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G460" t="n">
-        <v>6.37258577346802</v>
+        <v>6.37258529663086</v>
       </c>
       <c r="H460" t="n">
         <v>0</v>
@@ -13738,7 +13738,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G461" t="n">
-        <v>6.37258577346802</v>
+        <v>6.37258529663086</v>
       </c>
       <c r="H461" t="n">
         <v>0</v>
@@ -13767,7 +13767,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G462" t="n">
-        <v>6.37258577346802</v>
+        <v>6.37258529663086</v>
       </c>
       <c r="H462" t="n">
         <v>0</v>
@@ -13796,7 +13796,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G463" t="n">
-        <v>6.37258577346802</v>
+        <v>6.37258529663086</v>
       </c>
       <c r="H463" t="n">
         <v>0</v>
@@ -13825,7 +13825,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G464" t="n">
-        <v>6.37258577346802</v>
+        <v>6.37258529663086</v>
       </c>
       <c r="H464" t="n">
         <v>300</v>
@@ -13854,7 +13854,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G465" t="n">
-        <v>6.37258577346802</v>
+        <v>6.37258529663086</v>
       </c>
       <c r="H465" t="n">
         <v>4800</v>
@@ -13912,7 +13912,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G467" t="n">
-        <v>6.42123079299927</v>
+        <v>6.42123126983643</v>
       </c>
       <c r="H467" t="n">
         <v>6900</v>
@@ -14028,7 +14028,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G471" t="n">
-        <v>6.37258577346802</v>
+        <v>6.37258529663086</v>
       </c>
       <c r="H471" t="n">
         <v>600</v>
@@ -14057,7 +14057,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G472" t="n">
-        <v>6.22664880752563</v>
+        <v>6.22664833068848</v>
       </c>
       <c r="H472" t="n">
         <v>600</v>
@@ -14086,7 +14086,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G473" t="n">
-        <v>6.22664880752563</v>
+        <v>6.22664833068848</v>
       </c>
       <c r="H473" t="n">
         <v>0</v>
@@ -14115,7 +14115,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G474" t="n">
-        <v>6.22664880752563</v>
+        <v>6.22664833068848</v>
       </c>
       <c r="H474" t="n">
         <v>0</v>
@@ -14144,7 +14144,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G475" t="n">
-        <v>6.22664880752563</v>
+        <v>6.22664833068848</v>
       </c>
       <c r="H475" t="n">
         <v>0</v>
@@ -14173,7 +14173,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G476" t="n">
-        <v>6.22664880752563</v>
+        <v>6.22664833068848</v>
       </c>
       <c r="H476" t="n">
         <v>0</v>
@@ -14202,7 +14202,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G477" t="n">
-        <v>6.22664880752563</v>
+        <v>6.22664833068848</v>
       </c>
       <c r="H477" t="n">
         <v>0</v>
@@ -14231,7 +14231,7 @@
         <v>6.65000009536743</v>
       </c>
       <c r="G478" t="n">
-        <v>6.46987724304199</v>
+        <v>6.46987676620483</v>
       </c>
       <c r="H478" t="n">
         <v>2400</v>
@@ -14289,7 +14289,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G480" t="n">
-        <v>6.37258577346802</v>
+        <v>6.37258529663086</v>
       </c>
       <c r="H480" t="n">
         <v>1800</v>
@@ -14347,7 +14347,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G482" t="n">
-        <v>6.22664880752563</v>
+        <v>6.22664833068848</v>
       </c>
       <c r="H482" t="n">
         <v>3000</v>
@@ -14376,7 +14376,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G483" t="n">
-        <v>6.22664880752563</v>
+        <v>6.22664833068848</v>
       </c>
       <c r="H483" t="n">
         <v>0</v>
@@ -14405,7 +14405,7 @@
         <v>6.65000009536743</v>
       </c>
       <c r="G484" t="n">
-        <v>6.46987724304199</v>
+        <v>6.46987676620483</v>
       </c>
       <c r="H484" t="n">
         <v>2400</v>
@@ -14434,7 +14434,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G485" t="n">
-        <v>6.22664880752563</v>
+        <v>6.22664833068848</v>
       </c>
       <c r="H485" t="n">
         <v>1500</v>
@@ -14521,7 +14521,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G488" t="n">
-        <v>6.22664880752563</v>
+        <v>6.22664833068848</v>
       </c>
       <c r="H488" t="n">
         <v>4200</v>
@@ -14956,7 +14956,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G503" t="n">
-        <v>6.37258577346802</v>
+        <v>6.37258529663086</v>
       </c>
       <c r="H503" t="n">
         <v>1800</v>
@@ -14985,7 +14985,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G504" t="n">
-        <v>6.22664880752563</v>
+        <v>6.22664833068848</v>
       </c>
       <c r="H504" t="n">
         <v>2700</v>
@@ -15014,7 +15014,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G505" t="n">
-        <v>6.22664880752563</v>
+        <v>6.22664833068848</v>
       </c>
       <c r="H505" t="n">
         <v>0</v>
@@ -15043,7 +15043,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G506" t="n">
-        <v>6.22664880752563</v>
+        <v>6.22664833068848</v>
       </c>
       <c r="H506" t="n">
         <v>0</v>
@@ -15710,7 +15710,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G529" t="n">
-        <v>6.22664880752563</v>
+        <v>6.22664833068848</v>
       </c>
       <c r="H529" t="n">
         <v>3300</v>
@@ -15768,7 +15768,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G531" t="n">
-        <v>6.42123079299927</v>
+        <v>6.42123126983643</v>
       </c>
       <c r="H531" t="n">
         <v>1200</v>
@@ -15826,7 +15826,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G533" t="n">
-        <v>5.69154596328735</v>
+        <v>5.6915454864502</v>
       </c>
       <c r="H533" t="n">
         <v>8700</v>
@@ -15855,7 +15855,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G534" t="n">
-        <v>5.69154596328735</v>
+        <v>5.6915454864502</v>
       </c>
       <c r="H534" t="n">
         <v>300</v>
@@ -15884,7 +15884,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G535" t="n">
-        <v>5.69154596328735</v>
+        <v>5.6915454864502</v>
       </c>
       <c r="H535" t="n">
         <v>0</v>
@@ -15913,7 +15913,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G536" t="n">
-        <v>5.64289999008179</v>
+        <v>5.64290046691895</v>
       </c>
       <c r="H536" t="n">
         <v>2400</v>
@@ -16232,7 +16232,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G547" t="n">
-        <v>6.22664880752563</v>
+        <v>6.22664833068848</v>
       </c>
       <c r="H547" t="n">
         <v>1500</v>
@@ -16261,7 +16261,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G548" t="n">
-        <v>6.22664880752563</v>
+        <v>6.22664833068848</v>
       </c>
       <c r="H548" t="n">
         <v>1200</v>
@@ -16290,7 +16290,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G549" t="n">
-        <v>6.22664880752563</v>
+        <v>6.22664833068848</v>
       </c>
       <c r="H549" t="n">
         <v>1200</v>
@@ -16348,7 +16348,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G551" t="n">
-        <v>6.37258577346802</v>
+        <v>6.37258529663086</v>
       </c>
       <c r="H551" t="n">
         <v>60600</v>
@@ -16377,7 +16377,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G552" t="n">
-        <v>6.37258577346802</v>
+        <v>6.37258529663086</v>
       </c>
       <c r="H552" t="n">
         <v>0</v>
@@ -16406,7 +16406,7 @@
         <v>6.65000009536743</v>
       </c>
       <c r="G553" t="n">
-        <v>6.46987724304199</v>
+        <v>6.46987676620483</v>
       </c>
       <c r="H553" t="n">
         <v>300</v>
@@ -16435,7 +16435,7 @@
         <v>6.65000009536743</v>
       </c>
       <c r="G554" t="n">
-        <v>6.46987724304199</v>
+        <v>6.46987676620483</v>
       </c>
       <c r="H554" t="n">
         <v>0</v>
@@ -27171,6 +27171,35 @@
         <v>300</v>
       </c>
       <c r="I924" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="925">
+      <c r="A925" t="s">
+        <v>9</v>
+      </c>
+      <c r="B925" s="1" t="n">
+        <v>46317.2916666667</v>
+      </c>
+      <c r="C925" t="n">
+        <v>11.8999996185303</v>
+      </c>
+      <c r="D925" t="n">
+        <v>11.8999996185303</v>
+      </c>
+      <c r="E925" t="n">
+        <v>11.8999996185303</v>
+      </c>
+      <c r="F925" t="n">
+        <v>11.8999996185303</v>
+      </c>
+      <c r="G925" t="n">
+        <v>11.8999996185303</v>
+      </c>
+      <c r="H925" t="n">
+        <v>0</v>
+      </c>
+      <c r="I925" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/VLT.MI.xlsx
+++ b/data/VLT.MI.xlsx
@@ -543,7 +543,7 @@
         <v>5.69799995422363</v>
       </c>
       <c r="G6" t="n">
-        <v>5.54366254806519</v>
+        <v>5.54366302490234</v>
       </c>
       <c r="H6" t="n">
         <v>18900</v>
@@ -717,7 +717,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G12" t="n">
-        <v>5.02023506164551</v>
+        <v>5.02023553848267</v>
       </c>
       <c r="H12" t="n">
         <v>3300</v>
@@ -804,7 +804,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G15" t="n">
-        <v>5.15644359588623</v>
+        <v>5.15644311904907</v>
       </c>
       <c r="H15" t="n">
         <v>1500</v>
@@ -1094,7 +1094,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G25" t="n">
-        <v>5.19535970687866</v>
+        <v>5.19536018371582</v>
       </c>
       <c r="H25" t="n">
         <v>1800</v>
@@ -1123,7 +1123,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G26" t="n">
-        <v>5.19535970687866</v>
+        <v>5.19536018371582</v>
       </c>
       <c r="H26" t="n">
         <v>0</v>
@@ -1152,7 +1152,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G27" t="n">
-        <v>5.19535970687866</v>
+        <v>5.19536018371582</v>
       </c>
       <c r="H27" t="n">
         <v>0</v>
@@ -1384,7 +1384,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G35" t="n">
-        <v>5.38994216918945</v>
+        <v>5.38994264602661</v>
       </c>
       <c r="H35" t="n">
         <v>300</v>
@@ -1848,7 +1848,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G51" t="n">
-        <v>4.65052795410156</v>
+        <v>4.65052843093872</v>
       </c>
       <c r="H51" t="n">
         <v>1500</v>
@@ -1993,7 +1993,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G56" t="n">
-        <v>4.70890283584595</v>
+        <v>4.70890331268311</v>
       </c>
       <c r="H56" t="n">
         <v>300</v>
@@ -2399,7 +2399,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G70" t="n">
-        <v>4.70890283584595</v>
+        <v>4.70890331268311</v>
       </c>
       <c r="H70" t="n">
         <v>300</v>
@@ -2747,7 +2747,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G82" t="n">
-        <v>4.70890283584595</v>
+        <v>4.70890331268311</v>
       </c>
       <c r="H82" t="n">
         <v>900</v>
@@ -2776,7 +2776,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G83" t="n">
-        <v>4.70890283584595</v>
+        <v>4.70890331268311</v>
       </c>
       <c r="H83" t="n">
         <v>0</v>
@@ -2805,7 +2805,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G84" t="n">
-        <v>4.66025733947754</v>
+        <v>4.66025686264038</v>
       </c>
       <c r="H84" t="n">
         <v>1200</v>
@@ -3298,7 +3298,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G101" t="n">
-        <v>4.70890283584595</v>
+        <v>4.70890331268311</v>
       </c>
       <c r="H101" t="n">
         <v>1200</v>
@@ -3356,7 +3356,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G103" t="n">
-        <v>4.66025733947754</v>
+        <v>4.66025686264038</v>
       </c>
       <c r="H103" t="n">
         <v>300</v>
@@ -3385,7 +3385,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G104" t="n">
-        <v>4.66025733947754</v>
+        <v>4.66025686264038</v>
       </c>
       <c r="H104" t="n">
         <v>0</v>
@@ -3414,7 +3414,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G105" t="n">
-        <v>4.66025733947754</v>
+        <v>4.66025686264038</v>
       </c>
       <c r="H105" t="n">
         <v>0</v>
@@ -3443,7 +3443,7 @@
         <v>4.5</v>
       </c>
       <c r="G106" t="n">
-        <v>4.37811231613159</v>
+        <v>4.37811183929443</v>
       </c>
       <c r="H106" t="n">
         <v>4800</v>
@@ -3472,7 +3472,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G107" t="n">
-        <v>4.47540378570557</v>
+        <v>4.47540330886841</v>
       </c>
       <c r="H107" t="n">
         <v>3600</v>
@@ -3501,7 +3501,7 @@
         <v>4.5</v>
       </c>
       <c r="G108" t="n">
-        <v>4.37811231613159</v>
+        <v>4.37811183929443</v>
       </c>
       <c r="H108" t="n">
         <v>600</v>
@@ -3646,7 +3646,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G113" t="n">
-        <v>4.47540378570557</v>
+        <v>4.47540330886841</v>
       </c>
       <c r="H113" t="n">
         <v>300</v>
@@ -3675,7 +3675,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G114" t="n">
-        <v>4.47540378570557</v>
+        <v>4.47540330886841</v>
       </c>
       <c r="H114" t="n">
         <v>300</v>
@@ -3733,7 +3733,7 @@
         <v>4.53000020980835</v>
       </c>
       <c r="G116" t="n">
-        <v>4.40729999542236</v>
+        <v>4.40729951858521</v>
       </c>
       <c r="H116" t="n">
         <v>2700</v>
@@ -3762,7 +3762,7 @@
         <v>4.53000020980835</v>
       </c>
       <c r="G117" t="n">
-        <v>4.40729999542236</v>
+        <v>4.40729951858521</v>
       </c>
       <c r="H117" t="n">
         <v>0</v>
@@ -4255,7 +4255,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G134" t="n">
-        <v>4.35865354537964</v>
+        <v>4.3586540222168</v>
       </c>
       <c r="H134" t="n">
         <v>600</v>
@@ -4284,7 +4284,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G135" t="n">
-        <v>4.35865354537964</v>
+        <v>4.3586540222168</v>
       </c>
       <c r="H135" t="n">
         <v>0</v>
@@ -4313,7 +4313,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G136" t="n">
-        <v>4.35865354537964</v>
+        <v>4.3586540222168</v>
       </c>
       <c r="H136" t="n">
         <v>0</v>
@@ -4342,7 +4342,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G137" t="n">
-        <v>4.35865354537964</v>
+        <v>4.3586540222168</v>
       </c>
       <c r="H137" t="n">
         <v>0</v>
@@ -4371,7 +4371,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G138" t="n">
-        <v>4.35865354537964</v>
+        <v>4.3586540222168</v>
       </c>
       <c r="H138" t="n">
         <v>0</v>
@@ -4400,7 +4400,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G139" t="n">
-        <v>4.35865354537964</v>
+        <v>4.3586540222168</v>
       </c>
       <c r="H139" t="n">
         <v>0</v>
@@ -4429,7 +4429,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G140" t="n">
-        <v>4.35865354537964</v>
+        <v>4.3586540222168</v>
       </c>
       <c r="H140" t="n">
         <v>3000</v>
@@ -4458,7 +4458,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G141" t="n">
-        <v>4.35865354537964</v>
+        <v>4.3586540222168</v>
       </c>
       <c r="H141" t="n">
         <v>0</v>
@@ -4632,7 +4632,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G147" t="n">
-        <v>4.96186065673828</v>
+        <v>4.96186017990112</v>
       </c>
       <c r="H147" t="n">
         <v>1500</v>
@@ -4661,7 +4661,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G148" t="n">
-        <v>4.73809003829956</v>
+        <v>4.73809051513672</v>
       </c>
       <c r="H148" t="n">
         <v>4500</v>
@@ -4690,7 +4690,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G149" t="n">
-        <v>4.66025733947754</v>
+        <v>4.66025686264038</v>
       </c>
       <c r="H149" t="n">
         <v>2100</v>
@@ -4777,7 +4777,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G152" t="n">
-        <v>4.70890283584595</v>
+        <v>4.70890331268311</v>
       </c>
       <c r="H152" t="n">
         <v>600</v>
@@ -4980,7 +4980,7 @@
         <v>4.5</v>
       </c>
       <c r="G159" t="n">
-        <v>4.37811231613159</v>
+        <v>4.37811183929443</v>
       </c>
       <c r="H159" t="n">
         <v>3900</v>
@@ -5009,7 +5009,7 @@
         <v>4.5</v>
       </c>
       <c r="G160" t="n">
-        <v>4.37811231613159</v>
+        <v>4.37811183929443</v>
       </c>
       <c r="H160" t="n">
         <v>0</v>
@@ -5038,7 +5038,7 @@
         <v>4.5</v>
       </c>
       <c r="G161" t="n">
-        <v>4.37811231613159</v>
+        <v>4.37811183929443</v>
       </c>
       <c r="H161" t="n">
         <v>1800</v>
@@ -5067,7 +5067,7 @@
         <v>4.5</v>
       </c>
       <c r="G162" t="n">
-        <v>4.37811231613159</v>
+        <v>4.37811183929443</v>
       </c>
       <c r="H162" t="n">
         <v>1200</v>
@@ -5212,7 +5212,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G167" t="n">
-        <v>4.47540378570557</v>
+        <v>4.47540330886841</v>
       </c>
       <c r="H167" t="n">
         <v>900</v>
@@ -5241,7 +5241,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G168" t="n">
-        <v>4.47540378570557</v>
+        <v>4.47540330886841</v>
       </c>
       <c r="H168" t="n">
         <v>0</v>
@@ -5270,7 +5270,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G169" t="n">
-        <v>4.47540378570557</v>
+        <v>4.47540330886841</v>
       </c>
       <c r="H169" t="n">
         <v>0</v>
@@ -5299,7 +5299,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G170" t="n">
-        <v>4.47540378570557</v>
+        <v>4.47540330886841</v>
       </c>
       <c r="H170" t="n">
         <v>0</v>
@@ -5328,7 +5328,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G171" t="n">
-        <v>4.47540378570557</v>
+        <v>4.47540330886841</v>
       </c>
       <c r="H171" t="n">
         <v>0</v>
@@ -5357,7 +5357,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G172" t="n">
-        <v>4.47540378570557</v>
+        <v>4.47540330886841</v>
       </c>
       <c r="H172" t="n">
         <v>0</v>
@@ -5386,7 +5386,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G173" t="n">
-        <v>4.47540378570557</v>
+        <v>4.47540330886841</v>
       </c>
       <c r="H173" t="n">
         <v>0</v>
@@ -5415,7 +5415,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G174" t="n">
-        <v>4.47540378570557</v>
+        <v>4.47540330886841</v>
       </c>
       <c r="H174" t="n">
         <v>0</v>
@@ -5560,7 +5560,7 @@
         <v>4.76999998092651</v>
       </c>
       <c r="G179" t="n">
-        <v>4.64079856872559</v>
+        <v>4.64079904556274</v>
       </c>
       <c r="H179" t="n">
         <v>1200</v>
@@ -5618,7 +5618,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G181" t="n">
-        <v>4.68944501876831</v>
+        <v>4.68944454193115</v>
       </c>
       <c r="H181" t="n">
         <v>600</v>
@@ -5647,7 +5647,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G182" t="n">
-        <v>4.68944501876831</v>
+        <v>4.68944454193115</v>
       </c>
       <c r="H182" t="n">
         <v>300</v>
@@ -5676,7 +5676,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G183" t="n">
-        <v>4.68944501876831</v>
+        <v>4.68944454193115</v>
       </c>
       <c r="H183" t="n">
         <v>2400</v>
@@ -5705,7 +5705,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G184" t="n">
-        <v>4.68944501876831</v>
+        <v>4.68944454193115</v>
       </c>
       <c r="H184" t="n">
         <v>0</v>
@@ -5821,7 +5821,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G188" t="n">
-        <v>5.15644359588623</v>
+        <v>5.15644311904907</v>
       </c>
       <c r="H188" t="n">
         <v>600</v>
@@ -6198,7 +6198,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G201" t="n">
-        <v>4.96186065673828</v>
+        <v>4.96186017990112</v>
       </c>
       <c r="H201" t="n">
         <v>600</v>
@@ -6227,7 +6227,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G202" t="n">
-        <v>4.96186065673828</v>
+        <v>4.96186017990112</v>
       </c>
       <c r="H202" t="n">
         <v>300</v>
@@ -6256,7 +6256,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G203" t="n">
-        <v>4.96186065673828</v>
+        <v>4.96186017990112</v>
       </c>
       <c r="H203" t="n">
         <v>300</v>
@@ -6575,7 +6575,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G214" t="n">
-        <v>5.4288592338562</v>
+        <v>5.42885875701904</v>
       </c>
       <c r="H214" t="n">
         <v>3600</v>
@@ -6720,7 +6720,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G219" t="n">
-        <v>5.40940046310425</v>
+        <v>5.40940093994141</v>
       </c>
       <c r="H219" t="n">
         <v>1800</v>
@@ -7445,7 +7445,7 @@
         <v>6.03999996185303</v>
       </c>
       <c r="G244" t="n">
-        <v>5.87639904022217</v>
+        <v>5.87639951705933</v>
       </c>
       <c r="H244" t="n">
         <v>9300</v>
@@ -7909,7 +7909,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G260" t="n">
-        <v>5.64290046691895</v>
+        <v>5.64289999008179</v>
       </c>
       <c r="H260" t="n">
         <v>300</v>
@@ -7938,7 +7938,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G261" t="n">
-        <v>5.64290046691895</v>
+        <v>5.64289999008179</v>
       </c>
       <c r="H261" t="n">
         <v>0</v>
@@ -7967,7 +7967,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G262" t="n">
-        <v>5.64290046691895</v>
+        <v>5.64289999008179</v>
       </c>
       <c r="H262" t="n">
         <v>0</v>
@@ -7996,7 +7996,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G263" t="n">
-        <v>5.64290046691895</v>
+        <v>5.64289999008179</v>
       </c>
       <c r="H263" t="n">
         <v>0</v>
@@ -8025,7 +8025,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G264" t="n">
-        <v>5.64290046691895</v>
+        <v>5.64289999008179</v>
       </c>
       <c r="H264" t="n">
         <v>300</v>
@@ -8054,7 +8054,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G265" t="n">
-        <v>5.64290046691895</v>
+        <v>5.64289999008179</v>
       </c>
       <c r="H265" t="n">
         <v>0</v>
@@ -8112,7 +8112,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G267" t="n">
-        <v>5.64290046691895</v>
+        <v>5.64289999008179</v>
       </c>
       <c r="H267" t="n">
         <v>300</v>
@@ -8141,7 +8141,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G268" t="n">
-        <v>5.64290046691895</v>
+        <v>5.64289999008179</v>
       </c>
       <c r="H268" t="n">
         <v>0</v>
@@ -8315,7 +8315,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G274" t="n">
-        <v>5.72073364257812</v>
+        <v>5.72073316574097</v>
       </c>
       <c r="H274" t="n">
         <v>900</v>
@@ -8489,7 +8489,7 @@
         <v>6.05000019073486</v>
       </c>
       <c r="G280" t="n">
-        <v>5.88612842559814</v>
+        <v>5.8861289024353</v>
       </c>
       <c r="H280" t="n">
         <v>3900</v>
@@ -8576,7 +8576,7 @@
         <v>6.05000019073486</v>
       </c>
       <c r="G283" t="n">
-        <v>5.88612842559814</v>
+        <v>5.8861289024353</v>
       </c>
       <c r="H283" t="n">
         <v>4800</v>
@@ -8605,7 +8605,7 @@
         <v>6.05000019073486</v>
       </c>
       <c r="G284" t="n">
-        <v>5.88612842559814</v>
+        <v>5.8861289024353</v>
       </c>
       <c r="H284" t="n">
         <v>0</v>
@@ -9330,7 +9330,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G309" t="n">
-        <v>5.6915454864502</v>
+        <v>5.69154596328735</v>
       </c>
       <c r="H309" t="n">
         <v>5100</v>
@@ -9359,7 +9359,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G310" t="n">
-        <v>5.6915454864502</v>
+        <v>5.69154596328735</v>
       </c>
       <c r="H310" t="n">
         <v>4200</v>
@@ -9388,7 +9388,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G311" t="n">
-        <v>5.6915454864502</v>
+        <v>5.69154596328735</v>
       </c>
       <c r="H311" t="n">
         <v>3000</v>
@@ -9417,7 +9417,7 @@
         <v>5.75</v>
       </c>
       <c r="G312" t="n">
-        <v>5.59425401687622</v>
+        <v>5.59425449371338</v>
       </c>
       <c r="H312" t="n">
         <v>2400</v>
@@ -9446,7 +9446,7 @@
         <v>5.75</v>
       </c>
       <c r="G313" t="n">
-        <v>5.59425401687622</v>
+        <v>5.59425449371338</v>
       </c>
       <c r="H313" t="n">
         <v>5100</v>
@@ -9475,7 +9475,7 @@
         <v>5.75</v>
       </c>
       <c r="G314" t="n">
-        <v>5.59425401687622</v>
+        <v>5.59425449371338</v>
       </c>
       <c r="H314" t="n">
         <v>0</v>
@@ -9504,7 +9504,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G315" t="n">
-        <v>5.6915454864502</v>
+        <v>5.69154596328735</v>
       </c>
       <c r="H315" t="n">
         <v>2100</v>
@@ -9533,7 +9533,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G316" t="n">
-        <v>5.6915454864502</v>
+        <v>5.69154596328735</v>
       </c>
       <c r="H316" t="n">
         <v>300</v>
@@ -9562,7 +9562,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G317" t="n">
-        <v>5.6915454864502</v>
+        <v>5.69154596328735</v>
       </c>
       <c r="H317" t="n">
         <v>0</v>
@@ -9591,7 +9591,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G318" t="n">
-        <v>5.6915454864502</v>
+        <v>5.69154596328735</v>
       </c>
       <c r="H318" t="n">
         <v>0</v>
@@ -9620,7 +9620,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G319" t="n">
-        <v>5.6915454864502</v>
+        <v>5.69154596328735</v>
       </c>
       <c r="H319" t="n">
         <v>0</v>
@@ -9765,7 +9765,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G324" t="n">
-        <v>5.64290046691895</v>
+        <v>5.64289999008179</v>
       </c>
       <c r="H324" t="n">
         <v>600</v>
@@ -9794,7 +9794,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G325" t="n">
-        <v>5.64290046691895</v>
+        <v>5.64289999008179</v>
       </c>
       <c r="H325" t="n">
         <v>0</v>
@@ -9823,7 +9823,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G326" t="n">
-        <v>5.64290046691895</v>
+        <v>5.64289999008179</v>
       </c>
       <c r="H326" t="n">
         <v>0</v>
@@ -9852,7 +9852,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G327" t="n">
-        <v>5.64290046691895</v>
+        <v>5.64289999008179</v>
       </c>
       <c r="H327" t="n">
         <v>0</v>
@@ -9881,7 +9881,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G328" t="n">
-        <v>5.64290046691895</v>
+        <v>5.64289999008179</v>
       </c>
       <c r="H328" t="n">
         <v>0</v>
@@ -9910,7 +9910,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G329" t="n">
-        <v>5.64290046691895</v>
+        <v>5.64289999008179</v>
       </c>
       <c r="H329" t="n">
         <v>0</v>
@@ -9939,7 +9939,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G330" t="n">
-        <v>5.64290046691895</v>
+        <v>5.64289999008179</v>
       </c>
       <c r="H330" t="n">
         <v>0</v>
@@ -9968,7 +9968,7 @@
         <v>6.05000019073486</v>
       </c>
       <c r="G331" t="n">
-        <v>5.88612842559814</v>
+        <v>5.8861289024353</v>
       </c>
       <c r="H331" t="n">
         <v>1500</v>
@@ -9997,7 +9997,7 @@
         <v>6.05000019073486</v>
       </c>
       <c r="G332" t="n">
-        <v>5.88612842559814</v>
+        <v>5.8861289024353</v>
       </c>
       <c r="H332" t="n">
         <v>0</v>
@@ -10026,7 +10026,7 @@
         <v>6.05000019073486</v>
       </c>
       <c r="G333" t="n">
-        <v>5.88612842559814</v>
+        <v>5.8861289024353</v>
       </c>
       <c r="H333" t="n">
         <v>0</v>
@@ -10055,7 +10055,7 @@
         <v>6.05000019073486</v>
       </c>
       <c r="G334" t="n">
-        <v>5.88612842559814</v>
+        <v>5.8861289024353</v>
       </c>
       <c r="H334" t="n">
         <v>0</v>
@@ -10084,7 +10084,7 @@
         <v>6.05000019073486</v>
       </c>
       <c r="G335" t="n">
-        <v>5.88612842559814</v>
+        <v>5.8861289024353</v>
       </c>
       <c r="H335" t="n">
         <v>0</v>
@@ -10113,7 +10113,7 @@
         <v>6.05000019073486</v>
       </c>
       <c r="G336" t="n">
-        <v>5.88612842559814</v>
+        <v>5.8861289024353</v>
       </c>
       <c r="H336" t="n">
         <v>0</v>
@@ -10142,7 +10142,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G337" t="n">
-        <v>5.64290046691895</v>
+        <v>5.64289999008179</v>
       </c>
       <c r="H337" t="n">
         <v>300</v>
@@ -10316,7 +10316,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G343" t="n">
-        <v>5.64290046691895</v>
+        <v>5.64289999008179</v>
       </c>
       <c r="H343" t="n">
         <v>1200</v>
@@ -10345,7 +10345,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G344" t="n">
-        <v>5.64290046691895</v>
+        <v>5.64289999008179</v>
       </c>
       <c r="H344" t="n">
         <v>0</v>
@@ -10374,7 +10374,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G345" t="n">
-        <v>5.64290046691895</v>
+        <v>5.64289999008179</v>
       </c>
       <c r="H345" t="n">
         <v>300</v>
@@ -10403,7 +10403,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G346" t="n">
-        <v>5.64290046691895</v>
+        <v>5.64289999008179</v>
       </c>
       <c r="H346" t="n">
         <v>0</v>
@@ -11128,7 +11128,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G371" t="n">
-        <v>5.64290046691895</v>
+        <v>5.64289999008179</v>
       </c>
       <c r="H371" t="n">
         <v>300</v>
@@ -11157,7 +11157,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G372" t="n">
-        <v>5.64290046691895</v>
+        <v>5.64289999008179</v>
       </c>
       <c r="H372" t="n">
         <v>0</v>
@@ -11186,7 +11186,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G373" t="n">
-        <v>5.64290046691895</v>
+        <v>5.64289999008179</v>
       </c>
       <c r="H373" t="n">
         <v>0</v>
@@ -11215,7 +11215,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G374" t="n">
-        <v>5.64290046691895</v>
+        <v>5.64289999008179</v>
       </c>
       <c r="H374" t="n">
         <v>0</v>
@@ -11244,7 +11244,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G375" t="n">
-        <v>5.64290046691895</v>
+        <v>5.64289999008179</v>
       </c>
       <c r="H375" t="n">
         <v>600</v>
@@ -11273,7 +11273,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G376" t="n">
-        <v>5.64290046691895</v>
+        <v>5.64289999008179</v>
       </c>
       <c r="H376" t="n">
         <v>0</v>
@@ -11302,7 +11302,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G377" t="n">
-        <v>5.64290046691895</v>
+        <v>5.64289999008179</v>
       </c>
       <c r="H377" t="n">
         <v>0</v>
@@ -11331,7 +11331,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G378" t="n">
-        <v>5.64290046691895</v>
+        <v>5.64289999008179</v>
       </c>
       <c r="H378" t="n">
         <v>0</v>
@@ -11360,7 +11360,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G379" t="n">
-        <v>5.64290046691895</v>
+        <v>5.64289999008179</v>
       </c>
       <c r="H379" t="n">
         <v>0</v>
@@ -11389,7 +11389,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G380" t="n">
-        <v>5.64290046691895</v>
+        <v>5.64289999008179</v>
       </c>
       <c r="H380" t="n">
         <v>0</v>
@@ -11650,7 +11650,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G389" t="n">
-        <v>5.6915454864502</v>
+        <v>5.69154596328735</v>
       </c>
       <c r="H389" t="n">
         <v>300</v>
@@ -11679,7 +11679,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G390" t="n">
-        <v>5.6915454864502</v>
+        <v>5.69154596328735</v>
       </c>
       <c r="H390" t="n">
         <v>0</v>
@@ -11708,7 +11708,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G391" t="n">
-        <v>5.6915454864502</v>
+        <v>5.69154596328735</v>
       </c>
       <c r="H391" t="n">
         <v>0</v>
@@ -11940,7 +11940,7 @@
         <v>5.75</v>
       </c>
       <c r="G399" t="n">
-        <v>5.59425401687622</v>
+        <v>5.59425449371338</v>
       </c>
       <c r="H399" t="n">
         <v>1500</v>
@@ -11969,7 +11969,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G400" t="n">
-        <v>5.6915454864502</v>
+        <v>5.69154596328735</v>
       </c>
       <c r="H400" t="n">
         <v>1200</v>
@@ -11998,7 +11998,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G401" t="n">
-        <v>5.6915454864502</v>
+        <v>5.69154596328735</v>
       </c>
       <c r="H401" t="n">
         <v>4500</v>
@@ -12027,7 +12027,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G402" t="n">
-        <v>5.6915454864502</v>
+        <v>5.69154596328735</v>
       </c>
       <c r="H402" t="n">
         <v>0</v>
@@ -12056,7 +12056,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G403" t="n">
-        <v>5.6915454864502</v>
+        <v>5.69154596328735</v>
       </c>
       <c r="H403" t="n">
         <v>0</v>
@@ -12085,7 +12085,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G404" t="n">
-        <v>5.6915454864502</v>
+        <v>5.69154596328735</v>
       </c>
       <c r="H404" t="n">
         <v>1500</v>
@@ -12114,7 +12114,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G405" t="n">
-        <v>5.6915454864502</v>
+        <v>5.69154596328735</v>
       </c>
       <c r="H405" t="n">
         <v>600</v>
@@ -12143,7 +12143,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G406" t="n">
-        <v>5.6915454864502</v>
+        <v>5.69154596328735</v>
       </c>
       <c r="H406" t="n">
         <v>0</v>
@@ -12172,7 +12172,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G407" t="n">
-        <v>5.6915454864502</v>
+        <v>5.69154596328735</v>
       </c>
       <c r="H407" t="n">
         <v>600</v>
@@ -12201,7 +12201,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G408" t="n">
-        <v>5.6915454864502</v>
+        <v>5.69154596328735</v>
       </c>
       <c r="H408" t="n">
         <v>0</v>
@@ -12230,7 +12230,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G409" t="n">
-        <v>5.64290046691895</v>
+        <v>5.64289999008179</v>
       </c>
       <c r="H409" t="n">
         <v>1200</v>
@@ -12259,7 +12259,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G410" t="n">
-        <v>5.64290046691895</v>
+        <v>5.64289999008179</v>
       </c>
       <c r="H410" t="n">
         <v>0</v>
@@ -12288,7 +12288,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G411" t="n">
-        <v>5.64290046691895</v>
+        <v>5.64289999008179</v>
       </c>
       <c r="H411" t="n">
         <v>4800</v>
@@ -12317,7 +12317,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G412" t="n">
-        <v>5.64290046691895</v>
+        <v>5.64289999008179</v>
       </c>
       <c r="H412" t="n">
         <v>0</v>
@@ -12346,7 +12346,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G413" t="n">
-        <v>5.64290046691895</v>
+        <v>5.64289999008179</v>
       </c>
       <c r="H413" t="n">
         <v>0</v>
@@ -12375,7 +12375,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G414" t="n">
-        <v>5.64290046691895</v>
+        <v>5.64289999008179</v>
       </c>
       <c r="H414" t="n">
         <v>0</v>
@@ -12404,7 +12404,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G415" t="n">
-        <v>5.64290046691895</v>
+        <v>5.64289999008179</v>
       </c>
       <c r="H415" t="n">
         <v>0</v>
@@ -12462,7 +12462,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G417" t="n">
-        <v>5.6915454864502</v>
+        <v>5.69154596328735</v>
       </c>
       <c r="H417" t="n">
         <v>300</v>
@@ -12491,7 +12491,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G418" t="n">
-        <v>5.6915454864502</v>
+        <v>5.69154596328735</v>
       </c>
       <c r="H418" t="n">
         <v>0</v>
@@ -12520,7 +12520,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G419" t="n">
-        <v>5.6915454864502</v>
+        <v>5.69154596328735</v>
       </c>
       <c r="H419" t="n">
         <v>0</v>
@@ -12549,7 +12549,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G420" t="n">
-        <v>5.6915454864502</v>
+        <v>5.69154596328735</v>
       </c>
       <c r="H420" t="n">
         <v>0</v>
@@ -12578,7 +12578,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G421" t="n">
-        <v>5.6915454864502</v>
+        <v>5.69154596328735</v>
       </c>
       <c r="H421" t="n">
         <v>0</v>
@@ -12607,7 +12607,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G422" t="n">
-        <v>5.6915454864502</v>
+        <v>5.69154596328735</v>
       </c>
       <c r="H422" t="n">
         <v>0</v>
@@ -12665,7 +12665,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G424" t="n">
-        <v>5.6915454864502</v>
+        <v>5.69154596328735</v>
       </c>
       <c r="H424" t="n">
         <v>300</v>
@@ -12694,7 +12694,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G425" t="n">
-        <v>5.6915454864502</v>
+        <v>5.69154596328735</v>
       </c>
       <c r="H425" t="n">
         <v>0</v>
@@ -12723,7 +12723,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G426" t="n">
-        <v>5.64290046691895</v>
+        <v>5.64289999008179</v>
       </c>
       <c r="H426" t="n">
         <v>900</v>
@@ -12810,7 +12810,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G429" t="n">
-        <v>5.64290046691895</v>
+        <v>5.64289999008179</v>
       </c>
       <c r="H429" t="n">
         <v>1200</v>
@@ -12839,7 +12839,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G430" t="n">
-        <v>5.64290046691895</v>
+        <v>5.64289999008179</v>
       </c>
       <c r="H430" t="n">
         <v>300</v>
@@ -12868,7 +12868,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G431" t="n">
-        <v>5.64290046691895</v>
+        <v>5.64289999008179</v>
       </c>
       <c r="H431" t="n">
         <v>600</v>
@@ -12897,7 +12897,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G432" t="n">
-        <v>5.64290046691895</v>
+        <v>5.64289999008179</v>
       </c>
       <c r="H432" t="n">
         <v>0</v>
@@ -12926,7 +12926,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G433" t="n">
-        <v>5.64290046691895</v>
+        <v>5.64289999008179</v>
       </c>
       <c r="H433" t="n">
         <v>0</v>
@@ -12955,7 +12955,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G434" t="n">
-        <v>5.64290046691895</v>
+        <v>5.64289999008179</v>
       </c>
       <c r="H434" t="n">
         <v>0</v>
@@ -12984,7 +12984,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G435" t="n">
-        <v>5.64290046691895</v>
+        <v>5.64289999008179</v>
       </c>
       <c r="H435" t="n">
         <v>0</v>
@@ -13013,7 +13013,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G436" t="n">
-        <v>5.64290046691895</v>
+        <v>5.64289999008179</v>
       </c>
       <c r="H436" t="n">
         <v>0</v>
@@ -13042,7 +13042,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G437" t="n">
-        <v>5.64290046691895</v>
+        <v>5.64289999008179</v>
       </c>
       <c r="H437" t="n">
         <v>0</v>
@@ -13071,7 +13071,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G438" t="n">
-        <v>5.64290046691895</v>
+        <v>5.64289999008179</v>
       </c>
       <c r="H438" t="n">
         <v>0</v>
@@ -13100,7 +13100,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G439" t="n">
-        <v>5.64290046691895</v>
+        <v>5.64289999008179</v>
       </c>
       <c r="H439" t="n">
         <v>0</v>
@@ -13129,7 +13129,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G440" t="n">
-        <v>5.64290046691895</v>
+        <v>5.64289999008179</v>
       </c>
       <c r="H440" t="n">
         <v>0</v>
@@ -13158,7 +13158,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G441" t="n">
-        <v>5.64290046691895</v>
+        <v>5.64289999008179</v>
       </c>
       <c r="H441" t="n">
         <v>0</v>
@@ -13187,7 +13187,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G442" t="n">
-        <v>5.64290046691895</v>
+        <v>5.64289999008179</v>
       </c>
       <c r="H442" t="n">
         <v>0</v>
@@ -13216,7 +13216,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G443" t="n">
-        <v>5.64290046691895</v>
+        <v>5.64289999008179</v>
       </c>
       <c r="H443" t="n">
         <v>0</v>
@@ -13419,7 +13419,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G450" t="n">
-        <v>5.64290046691895</v>
+        <v>5.64289999008179</v>
       </c>
       <c r="H450" t="n">
         <v>4500</v>
@@ -13506,7 +13506,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G453" t="n">
-        <v>5.6915454864502</v>
+        <v>5.69154596328735</v>
       </c>
       <c r="H453" t="n">
         <v>900</v>
@@ -13535,7 +13535,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G454" t="n">
-        <v>5.6915454864502</v>
+        <v>5.69154596328735</v>
       </c>
       <c r="H454" t="n">
         <v>0</v>
@@ -13680,7 +13680,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G459" t="n">
-        <v>6.37258529663086</v>
+        <v>6.37258577346802</v>
       </c>
       <c r="H459" t="n">
         <v>1500</v>
@@ -13709,7 +13709,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G460" t="n">
-        <v>6.37258529663086</v>
+        <v>6.37258577346802</v>
       </c>
       <c r="H460" t="n">
         <v>0</v>
@@ -13738,7 +13738,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G461" t="n">
-        <v>6.37258529663086</v>
+        <v>6.37258577346802</v>
       </c>
       <c r="H461" t="n">
         <v>0</v>
@@ -13767,7 +13767,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G462" t="n">
-        <v>6.37258529663086</v>
+        <v>6.37258577346802</v>
       </c>
       <c r="H462" t="n">
         <v>0</v>
@@ -13796,7 +13796,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G463" t="n">
-        <v>6.37258529663086</v>
+        <v>6.37258577346802</v>
       </c>
       <c r="H463" t="n">
         <v>0</v>
@@ -13825,7 +13825,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G464" t="n">
-        <v>6.37258529663086</v>
+        <v>6.37258577346802</v>
       </c>
       <c r="H464" t="n">
         <v>300</v>
@@ -13854,7 +13854,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G465" t="n">
-        <v>6.37258529663086</v>
+        <v>6.37258577346802</v>
       </c>
       <c r="H465" t="n">
         <v>4800</v>
@@ -13912,7 +13912,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G467" t="n">
-        <v>6.42123126983643</v>
+        <v>6.42123079299927</v>
       </c>
       <c r="H467" t="n">
         <v>6900</v>
@@ -14028,7 +14028,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G471" t="n">
-        <v>6.37258529663086</v>
+        <v>6.37258577346802</v>
       </c>
       <c r="H471" t="n">
         <v>600</v>
@@ -14057,7 +14057,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G472" t="n">
-        <v>6.22664833068848</v>
+        <v>6.22664880752563</v>
       </c>
       <c r="H472" t="n">
         <v>600</v>
@@ -14086,7 +14086,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G473" t="n">
-        <v>6.22664833068848</v>
+        <v>6.22664880752563</v>
       </c>
       <c r="H473" t="n">
         <v>0</v>
@@ -14115,7 +14115,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G474" t="n">
-        <v>6.22664833068848</v>
+        <v>6.22664880752563</v>
       </c>
       <c r="H474" t="n">
         <v>0</v>
@@ -14144,7 +14144,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G475" t="n">
-        <v>6.22664833068848</v>
+        <v>6.22664880752563</v>
       </c>
       <c r="H475" t="n">
         <v>0</v>
@@ -14173,7 +14173,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G476" t="n">
-        <v>6.22664833068848</v>
+        <v>6.22664880752563</v>
       </c>
       <c r="H476" t="n">
         <v>0</v>
@@ -14202,7 +14202,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G477" t="n">
-        <v>6.22664833068848</v>
+        <v>6.22664880752563</v>
       </c>
       <c r="H477" t="n">
         <v>0</v>
@@ -14231,7 +14231,7 @@
         <v>6.65000009536743</v>
       </c>
       <c r="G478" t="n">
-        <v>6.46987676620483</v>
+        <v>6.46987724304199</v>
       </c>
       <c r="H478" t="n">
         <v>2400</v>
@@ -14289,7 +14289,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G480" t="n">
-        <v>6.37258529663086</v>
+        <v>6.37258577346802</v>
       </c>
       <c r="H480" t="n">
         <v>1800</v>
@@ -14347,7 +14347,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G482" t="n">
-        <v>6.22664833068848</v>
+        <v>6.22664880752563</v>
       </c>
       <c r="H482" t="n">
         <v>3000</v>
@@ -14376,7 +14376,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G483" t="n">
-        <v>6.22664833068848</v>
+        <v>6.22664880752563</v>
       </c>
       <c r="H483" t="n">
         <v>0</v>
@@ -14405,7 +14405,7 @@
         <v>6.65000009536743</v>
       </c>
       <c r="G484" t="n">
-        <v>6.46987676620483</v>
+        <v>6.46987724304199</v>
       </c>
       <c r="H484" t="n">
         <v>2400</v>
@@ -14434,7 +14434,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G485" t="n">
-        <v>6.22664833068848</v>
+        <v>6.22664880752563</v>
       </c>
       <c r="H485" t="n">
         <v>1500</v>
@@ -14521,7 +14521,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G488" t="n">
-        <v>6.22664833068848</v>
+        <v>6.22664880752563</v>
       </c>
       <c r="H488" t="n">
         <v>4200</v>
@@ -14956,7 +14956,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G503" t="n">
-        <v>6.37258529663086</v>
+        <v>6.37258577346802</v>
       </c>
       <c r="H503" t="n">
         <v>1800</v>
@@ -14985,7 +14985,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G504" t="n">
-        <v>6.22664833068848</v>
+        <v>6.22664880752563</v>
       </c>
       <c r="H504" t="n">
         <v>2700</v>
@@ -15014,7 +15014,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G505" t="n">
-        <v>6.22664833068848</v>
+        <v>6.22664880752563</v>
       </c>
       <c r="H505" t="n">
         <v>0</v>
@@ -15043,7 +15043,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G506" t="n">
-        <v>6.22664833068848</v>
+        <v>6.22664880752563</v>
       </c>
       <c r="H506" t="n">
         <v>0</v>
@@ -15710,7 +15710,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G529" t="n">
-        <v>6.22664833068848</v>
+        <v>6.22664880752563</v>
       </c>
       <c r="H529" t="n">
         <v>3300</v>
@@ -15768,7 +15768,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G531" t="n">
-        <v>6.42123126983643</v>
+        <v>6.42123079299927</v>
       </c>
       <c r="H531" t="n">
         <v>1200</v>
@@ -15826,7 +15826,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G533" t="n">
-        <v>5.6915454864502</v>
+        <v>5.69154596328735</v>
       </c>
       <c r="H533" t="n">
         <v>8700</v>
@@ -15855,7 +15855,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G534" t="n">
-        <v>5.6915454864502</v>
+        <v>5.69154596328735</v>
       </c>
       <c r="H534" t="n">
         <v>300</v>
@@ -15884,7 +15884,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G535" t="n">
-        <v>5.6915454864502</v>
+        <v>5.69154596328735</v>
       </c>
       <c r="H535" t="n">
         <v>0</v>
@@ -15913,7 +15913,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G536" t="n">
-        <v>5.64290046691895</v>
+        <v>5.64289999008179</v>
       </c>
       <c r="H536" t="n">
         <v>2400</v>
@@ -16232,7 +16232,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G547" t="n">
-        <v>6.22664833068848</v>
+        <v>6.22664880752563</v>
       </c>
       <c r="H547" t="n">
         <v>1500</v>
@@ -16261,7 +16261,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G548" t="n">
-        <v>6.22664833068848</v>
+        <v>6.22664880752563</v>
       </c>
       <c r="H548" t="n">
         <v>1200</v>
@@ -16290,7 +16290,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G549" t="n">
-        <v>6.22664833068848</v>
+        <v>6.22664880752563</v>
       </c>
       <c r="H549" t="n">
         <v>1200</v>
@@ -16348,7 +16348,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G551" t="n">
-        <v>6.37258529663086</v>
+        <v>6.37258577346802</v>
       </c>
       <c r="H551" t="n">
         <v>60600</v>
@@ -16377,7 +16377,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G552" t="n">
-        <v>6.37258529663086</v>
+        <v>6.37258577346802</v>
       </c>
       <c r="H552" t="n">
         <v>0</v>
@@ -16406,7 +16406,7 @@
         <v>6.65000009536743</v>
       </c>
       <c r="G553" t="n">
-        <v>6.46987676620483</v>
+        <v>6.46987724304199</v>
       </c>
       <c r="H553" t="n">
         <v>300</v>
@@ -16435,7 +16435,7 @@
         <v>6.65000009536743</v>
       </c>
       <c r="G554" t="n">
-        <v>6.46987676620483</v>
+        <v>6.46987724304199</v>
       </c>
       <c r="H554" t="n">
         <v>0</v>
@@ -27200,6 +27200,35 @@
         <v>0</v>
       </c>
       <c r="I925" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="926">
+      <c r="A926" t="s">
+        <v>9</v>
+      </c>
+      <c r="B926" s="1" t="n">
+        <v>46318.2916666667</v>
+      </c>
+      <c r="C926" t="n">
+        <v>11.8999996185303</v>
+      </c>
+      <c r="D926" t="n">
+        <v>11.8999996185303</v>
+      </c>
+      <c r="E926" t="n">
+        <v>11.8999996185303</v>
+      </c>
+      <c r="F926" t="n">
+        <v>11.8999996185303</v>
+      </c>
+      <c r="G926" t="n">
+        <v>11.8999996185303</v>
+      </c>
+      <c r="H926" t="n">
+        <v>0</v>
+      </c>
+      <c r="I926" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/VLT.MI.xlsx
+++ b/data/VLT.MI.xlsx
@@ -543,7 +543,7 @@
         <v>5.69799995422363</v>
       </c>
       <c r="G6" t="n">
-        <v>5.54366302490234</v>
+        <v>5.54366254806519</v>
       </c>
       <c r="H6" t="n">
         <v>18900</v>
@@ -717,7 +717,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G12" t="n">
-        <v>5.02023553848267</v>
+        <v>5.02023506164551</v>
       </c>
       <c r="H12" t="n">
         <v>3300</v>
@@ -804,7 +804,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G15" t="n">
-        <v>5.15644311904907</v>
+        <v>5.15644359588623</v>
       </c>
       <c r="H15" t="n">
         <v>1500</v>
@@ -1094,7 +1094,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G25" t="n">
-        <v>5.19536018371582</v>
+        <v>5.19535970687866</v>
       </c>
       <c r="H25" t="n">
         <v>1800</v>
@@ -1123,7 +1123,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G26" t="n">
-        <v>5.19536018371582</v>
+        <v>5.19535970687866</v>
       </c>
       <c r="H26" t="n">
         <v>0</v>
@@ -1152,7 +1152,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G27" t="n">
-        <v>5.19536018371582</v>
+        <v>5.19535970687866</v>
       </c>
       <c r="H27" t="n">
         <v>0</v>
@@ -1384,7 +1384,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G35" t="n">
-        <v>5.38994264602661</v>
+        <v>5.38994216918945</v>
       </c>
       <c r="H35" t="n">
         <v>300</v>
@@ -1848,7 +1848,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G51" t="n">
-        <v>4.65052843093872</v>
+        <v>4.65052795410156</v>
       </c>
       <c r="H51" t="n">
         <v>1500</v>
@@ -1993,7 +1993,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G56" t="n">
-        <v>4.70890331268311</v>
+        <v>4.70890283584595</v>
       </c>
       <c r="H56" t="n">
         <v>300</v>
@@ -2399,7 +2399,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G70" t="n">
-        <v>4.70890331268311</v>
+        <v>4.70890283584595</v>
       </c>
       <c r="H70" t="n">
         <v>300</v>
@@ -2747,7 +2747,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G82" t="n">
-        <v>4.70890331268311</v>
+        <v>4.70890283584595</v>
       </c>
       <c r="H82" t="n">
         <v>900</v>
@@ -2776,7 +2776,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G83" t="n">
-        <v>4.70890331268311</v>
+        <v>4.70890283584595</v>
       </c>
       <c r="H83" t="n">
         <v>0</v>
@@ -2805,7 +2805,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G84" t="n">
-        <v>4.66025686264038</v>
+        <v>4.66025733947754</v>
       </c>
       <c r="H84" t="n">
         <v>1200</v>
@@ -3298,7 +3298,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G101" t="n">
-        <v>4.70890331268311</v>
+        <v>4.70890283584595</v>
       </c>
       <c r="H101" t="n">
         <v>1200</v>
@@ -3356,7 +3356,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G103" t="n">
-        <v>4.66025686264038</v>
+        <v>4.66025733947754</v>
       </c>
       <c r="H103" t="n">
         <v>300</v>
@@ -3385,7 +3385,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G104" t="n">
-        <v>4.66025686264038</v>
+        <v>4.66025733947754</v>
       </c>
       <c r="H104" t="n">
         <v>0</v>
@@ -3414,7 +3414,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G105" t="n">
-        <v>4.66025686264038</v>
+        <v>4.66025733947754</v>
       </c>
       <c r="H105" t="n">
         <v>0</v>
@@ -3443,7 +3443,7 @@
         <v>4.5</v>
       </c>
       <c r="G106" t="n">
-        <v>4.37811183929443</v>
+        <v>4.37811231613159</v>
       </c>
       <c r="H106" t="n">
         <v>4800</v>
@@ -3472,7 +3472,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G107" t="n">
-        <v>4.47540330886841</v>
+        <v>4.47540378570557</v>
       </c>
       <c r="H107" t="n">
         <v>3600</v>
@@ -3501,7 +3501,7 @@
         <v>4.5</v>
       </c>
       <c r="G108" t="n">
-        <v>4.37811183929443</v>
+        <v>4.37811231613159</v>
       </c>
       <c r="H108" t="n">
         <v>600</v>
@@ -3646,7 +3646,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G113" t="n">
-        <v>4.47540330886841</v>
+        <v>4.47540378570557</v>
       </c>
       <c r="H113" t="n">
         <v>300</v>
@@ -3675,7 +3675,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G114" t="n">
-        <v>4.47540330886841</v>
+        <v>4.47540378570557</v>
       </c>
       <c r="H114" t="n">
         <v>300</v>
@@ -3733,7 +3733,7 @@
         <v>4.53000020980835</v>
       </c>
       <c r="G116" t="n">
-        <v>4.40729951858521</v>
+        <v>4.40729999542236</v>
       </c>
       <c r="H116" t="n">
         <v>2700</v>
@@ -3762,7 +3762,7 @@
         <v>4.53000020980835</v>
       </c>
       <c r="G117" t="n">
-        <v>4.40729951858521</v>
+        <v>4.40729999542236</v>
       </c>
       <c r="H117" t="n">
         <v>0</v>
@@ -4255,7 +4255,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G134" t="n">
-        <v>4.3586540222168</v>
+        <v>4.35865354537964</v>
       </c>
       <c r="H134" t="n">
         <v>600</v>
@@ -4284,7 +4284,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G135" t="n">
-        <v>4.3586540222168</v>
+        <v>4.35865354537964</v>
       </c>
       <c r="H135" t="n">
         <v>0</v>
@@ -4313,7 +4313,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G136" t="n">
-        <v>4.3586540222168</v>
+        <v>4.35865354537964</v>
       </c>
       <c r="H136" t="n">
         <v>0</v>
@@ -4342,7 +4342,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G137" t="n">
-        <v>4.3586540222168</v>
+        <v>4.35865354537964</v>
       </c>
       <c r="H137" t="n">
         <v>0</v>
@@ -4371,7 +4371,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G138" t="n">
-        <v>4.3586540222168</v>
+        <v>4.35865354537964</v>
       </c>
       <c r="H138" t="n">
         <v>0</v>
@@ -4400,7 +4400,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G139" t="n">
-        <v>4.3586540222168</v>
+        <v>4.35865354537964</v>
       </c>
       <c r="H139" t="n">
         <v>0</v>
@@ -4429,7 +4429,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G140" t="n">
-        <v>4.3586540222168</v>
+        <v>4.35865354537964</v>
       </c>
       <c r="H140" t="n">
         <v>3000</v>
@@ -4458,7 +4458,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G141" t="n">
-        <v>4.3586540222168</v>
+        <v>4.35865354537964</v>
       </c>
       <c r="H141" t="n">
         <v>0</v>
@@ -4632,7 +4632,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G147" t="n">
-        <v>4.96186017990112</v>
+        <v>4.96186065673828</v>
       </c>
       <c r="H147" t="n">
         <v>1500</v>
@@ -4661,7 +4661,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G148" t="n">
-        <v>4.73809051513672</v>
+        <v>4.73809003829956</v>
       </c>
       <c r="H148" t="n">
         <v>4500</v>
@@ -4690,7 +4690,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G149" t="n">
-        <v>4.66025686264038</v>
+        <v>4.66025733947754</v>
       </c>
       <c r="H149" t="n">
         <v>2100</v>
@@ -4777,7 +4777,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G152" t="n">
-        <v>4.70890331268311</v>
+        <v>4.70890283584595</v>
       </c>
       <c r="H152" t="n">
         <v>600</v>
@@ -4980,7 +4980,7 @@
         <v>4.5</v>
       </c>
       <c r="G159" t="n">
-        <v>4.37811183929443</v>
+        <v>4.37811231613159</v>
       </c>
       <c r="H159" t="n">
         <v>3900</v>
@@ -5009,7 +5009,7 @@
         <v>4.5</v>
       </c>
       <c r="G160" t="n">
-        <v>4.37811183929443</v>
+        <v>4.37811231613159</v>
       </c>
       <c r="H160" t="n">
         <v>0</v>
@@ -5038,7 +5038,7 @@
         <v>4.5</v>
       </c>
       <c r="G161" t="n">
-        <v>4.37811183929443</v>
+        <v>4.37811231613159</v>
       </c>
       <c r="H161" t="n">
         <v>1800</v>
@@ -5067,7 +5067,7 @@
         <v>4.5</v>
       </c>
       <c r="G162" t="n">
-        <v>4.37811183929443</v>
+        <v>4.37811231613159</v>
       </c>
       <c r="H162" t="n">
         <v>1200</v>
@@ -5212,7 +5212,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G167" t="n">
-        <v>4.47540330886841</v>
+        <v>4.47540378570557</v>
       </c>
       <c r="H167" t="n">
         <v>900</v>
@@ -5241,7 +5241,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G168" t="n">
-        <v>4.47540330886841</v>
+        <v>4.47540378570557</v>
       </c>
       <c r="H168" t="n">
         <v>0</v>
@@ -5270,7 +5270,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G169" t="n">
-        <v>4.47540330886841</v>
+        <v>4.47540378570557</v>
       </c>
       <c r="H169" t="n">
         <v>0</v>
@@ -5299,7 +5299,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G170" t="n">
-        <v>4.47540330886841</v>
+        <v>4.47540378570557</v>
       </c>
       <c r="H170" t="n">
         <v>0</v>
@@ -5328,7 +5328,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G171" t="n">
-        <v>4.47540330886841</v>
+        <v>4.47540378570557</v>
       </c>
       <c r="H171" t="n">
         <v>0</v>
@@ -5357,7 +5357,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G172" t="n">
-        <v>4.47540330886841</v>
+        <v>4.47540378570557</v>
       </c>
       <c r="H172" t="n">
         <v>0</v>
@@ -5386,7 +5386,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G173" t="n">
-        <v>4.47540330886841</v>
+        <v>4.47540378570557</v>
       </c>
       <c r="H173" t="n">
         <v>0</v>
@@ -5415,7 +5415,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G174" t="n">
-        <v>4.47540330886841</v>
+        <v>4.47540378570557</v>
       </c>
       <c r="H174" t="n">
         <v>0</v>
@@ -5560,7 +5560,7 @@
         <v>4.76999998092651</v>
       </c>
       <c r="G179" t="n">
-        <v>4.64079904556274</v>
+        <v>4.64079856872559</v>
       </c>
       <c r="H179" t="n">
         <v>1200</v>
@@ -5618,7 +5618,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G181" t="n">
-        <v>4.68944454193115</v>
+        <v>4.68944501876831</v>
       </c>
       <c r="H181" t="n">
         <v>600</v>
@@ -5647,7 +5647,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G182" t="n">
-        <v>4.68944454193115</v>
+        <v>4.68944501876831</v>
       </c>
       <c r="H182" t="n">
         <v>300</v>
@@ -5676,7 +5676,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G183" t="n">
-        <v>4.68944454193115</v>
+        <v>4.68944501876831</v>
       </c>
       <c r="H183" t="n">
         <v>2400</v>
@@ -5705,7 +5705,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G184" t="n">
-        <v>4.68944454193115</v>
+        <v>4.68944501876831</v>
       </c>
       <c r="H184" t="n">
         <v>0</v>
@@ -5821,7 +5821,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G188" t="n">
-        <v>5.15644311904907</v>
+        <v>5.15644359588623</v>
       </c>
       <c r="H188" t="n">
         <v>600</v>
@@ -6198,7 +6198,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G201" t="n">
-        <v>4.96186017990112</v>
+        <v>4.96186065673828</v>
       </c>
       <c r="H201" t="n">
         <v>600</v>
@@ -6227,7 +6227,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G202" t="n">
-        <v>4.96186017990112</v>
+        <v>4.96186065673828</v>
       </c>
       <c r="H202" t="n">
         <v>300</v>
@@ -6256,7 +6256,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G203" t="n">
-        <v>4.96186017990112</v>
+        <v>4.96186065673828</v>
       </c>
       <c r="H203" t="n">
         <v>300</v>
@@ -6575,7 +6575,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G214" t="n">
-        <v>5.42885875701904</v>
+        <v>5.4288592338562</v>
       </c>
       <c r="H214" t="n">
         <v>3600</v>
@@ -6720,7 +6720,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G219" t="n">
-        <v>5.40940093994141</v>
+        <v>5.40940046310425</v>
       </c>
       <c r="H219" t="n">
         <v>1800</v>
@@ -7445,7 +7445,7 @@
         <v>6.03999996185303</v>
       </c>
       <c r="G244" t="n">
-        <v>5.87639951705933</v>
+        <v>5.87639904022217</v>
       </c>
       <c r="H244" t="n">
         <v>9300</v>
@@ -7909,7 +7909,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G260" t="n">
-        <v>5.64289999008179</v>
+        <v>5.64290046691895</v>
       </c>
       <c r="H260" t="n">
         <v>300</v>
@@ -7938,7 +7938,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G261" t="n">
-        <v>5.64289999008179</v>
+        <v>5.64290046691895</v>
       </c>
       <c r="H261" t="n">
         <v>0</v>
@@ -7967,7 +7967,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G262" t="n">
-        <v>5.64289999008179</v>
+        <v>5.64290046691895</v>
       </c>
       <c r="H262" t="n">
         <v>0</v>
@@ -7996,7 +7996,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G263" t="n">
-        <v>5.64289999008179</v>
+        <v>5.64290046691895</v>
       </c>
       <c r="H263" t="n">
         <v>0</v>
@@ -8025,7 +8025,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G264" t="n">
-        <v>5.64289999008179</v>
+        <v>5.64290046691895</v>
       </c>
       <c r="H264" t="n">
         <v>300</v>
@@ -8054,7 +8054,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G265" t="n">
-        <v>5.64289999008179</v>
+        <v>5.64290046691895</v>
       </c>
       <c r="H265" t="n">
         <v>0</v>
@@ -8112,7 +8112,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G267" t="n">
-        <v>5.64289999008179</v>
+        <v>5.64290046691895</v>
       </c>
       <c r="H267" t="n">
         <v>300</v>
@@ -8141,7 +8141,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G268" t="n">
-        <v>5.64289999008179</v>
+        <v>5.64290046691895</v>
       </c>
       <c r="H268" t="n">
         <v>0</v>
@@ -8315,7 +8315,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G274" t="n">
-        <v>5.72073316574097</v>
+        <v>5.72073364257812</v>
       </c>
       <c r="H274" t="n">
         <v>900</v>
@@ -8489,7 +8489,7 @@
         <v>6.05000019073486</v>
       </c>
       <c r="G280" t="n">
-        <v>5.8861289024353</v>
+        <v>5.88612842559814</v>
       </c>
       <c r="H280" t="n">
         <v>3900</v>
@@ -8576,7 +8576,7 @@
         <v>6.05000019073486</v>
       </c>
       <c r="G283" t="n">
-        <v>5.8861289024353</v>
+        <v>5.88612842559814</v>
       </c>
       <c r="H283" t="n">
         <v>4800</v>
@@ -8605,7 +8605,7 @@
         <v>6.05000019073486</v>
       </c>
       <c r="G284" t="n">
-        <v>5.8861289024353</v>
+        <v>5.88612842559814</v>
       </c>
       <c r="H284" t="n">
         <v>0</v>
@@ -9330,7 +9330,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G309" t="n">
-        <v>5.69154596328735</v>
+        <v>5.6915454864502</v>
       </c>
       <c r="H309" t="n">
         <v>5100</v>
@@ -9359,7 +9359,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G310" t="n">
-        <v>5.69154596328735</v>
+        <v>5.6915454864502</v>
       </c>
       <c r="H310" t="n">
         <v>4200</v>
@@ -9388,7 +9388,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G311" t="n">
-        <v>5.69154596328735</v>
+        <v>5.6915454864502</v>
       </c>
       <c r="H311" t="n">
         <v>3000</v>
@@ -9417,7 +9417,7 @@
         <v>5.75</v>
       </c>
       <c r="G312" t="n">
-        <v>5.59425449371338</v>
+        <v>5.59425401687622</v>
       </c>
       <c r="H312" t="n">
         <v>2400</v>
@@ -9446,7 +9446,7 @@
         <v>5.75</v>
       </c>
       <c r="G313" t="n">
-        <v>5.59425449371338</v>
+        <v>5.59425401687622</v>
       </c>
       <c r="H313" t="n">
         <v>5100</v>
@@ -9475,7 +9475,7 @@
         <v>5.75</v>
       </c>
       <c r="G314" t="n">
-        <v>5.59425449371338</v>
+        <v>5.59425401687622</v>
       </c>
       <c r="H314" t="n">
         <v>0</v>
@@ -9504,7 +9504,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G315" t="n">
-        <v>5.69154596328735</v>
+        <v>5.6915454864502</v>
       </c>
       <c r="H315" t="n">
         <v>2100</v>
@@ -9533,7 +9533,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G316" t="n">
-        <v>5.69154596328735</v>
+        <v>5.6915454864502</v>
       </c>
       <c r="H316" t="n">
         <v>300</v>
@@ -9562,7 +9562,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G317" t="n">
-        <v>5.69154596328735</v>
+        <v>5.6915454864502</v>
       </c>
       <c r="H317" t="n">
         <v>0</v>
@@ -9591,7 +9591,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G318" t="n">
-        <v>5.69154596328735</v>
+        <v>5.6915454864502</v>
       </c>
       <c r="H318" t="n">
         <v>0</v>
@@ -9620,7 +9620,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G319" t="n">
-        <v>5.69154596328735</v>
+        <v>5.6915454864502</v>
       </c>
       <c r="H319" t="n">
         <v>0</v>
@@ -9765,7 +9765,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G324" t="n">
-        <v>5.64289999008179</v>
+        <v>5.64290046691895</v>
       </c>
       <c r="H324" t="n">
         <v>600</v>
@@ -9794,7 +9794,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G325" t="n">
-        <v>5.64289999008179</v>
+        <v>5.64290046691895</v>
       </c>
       <c r="H325" t="n">
         <v>0</v>
@@ -9823,7 +9823,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G326" t="n">
-        <v>5.64289999008179</v>
+        <v>5.64290046691895</v>
       </c>
       <c r="H326" t="n">
         <v>0</v>
@@ -9852,7 +9852,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G327" t="n">
-        <v>5.64289999008179</v>
+        <v>5.64290046691895</v>
       </c>
       <c r="H327" t="n">
         <v>0</v>
@@ -9881,7 +9881,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G328" t="n">
-        <v>5.64289999008179</v>
+        <v>5.64290046691895</v>
       </c>
       <c r="H328" t="n">
         <v>0</v>
@@ -9910,7 +9910,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G329" t="n">
-        <v>5.64289999008179</v>
+        <v>5.64290046691895</v>
       </c>
       <c r="H329" t="n">
         <v>0</v>
@@ -9939,7 +9939,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G330" t="n">
-        <v>5.64289999008179</v>
+        <v>5.64290046691895</v>
       </c>
       <c r="H330" t="n">
         <v>0</v>
@@ -9968,7 +9968,7 @@
         <v>6.05000019073486</v>
       </c>
       <c r="G331" t="n">
-        <v>5.8861289024353</v>
+        <v>5.88612842559814</v>
       </c>
       <c r="H331" t="n">
         <v>1500</v>
@@ -9997,7 +9997,7 @@
         <v>6.05000019073486</v>
       </c>
       <c r="G332" t="n">
-        <v>5.8861289024353</v>
+        <v>5.88612842559814</v>
       </c>
       <c r="H332" t="n">
         <v>0</v>
@@ -10026,7 +10026,7 @@
         <v>6.05000019073486</v>
       </c>
       <c r="G333" t="n">
-        <v>5.8861289024353</v>
+        <v>5.88612842559814</v>
       </c>
       <c r="H333" t="n">
         <v>0</v>
@@ -10055,7 +10055,7 @@
         <v>6.05000019073486</v>
       </c>
       <c r="G334" t="n">
-        <v>5.8861289024353</v>
+        <v>5.88612842559814</v>
       </c>
       <c r="H334" t="n">
         <v>0</v>
@@ -10084,7 +10084,7 @@
         <v>6.05000019073486</v>
       </c>
       <c r="G335" t="n">
-        <v>5.8861289024353</v>
+        <v>5.88612842559814</v>
       </c>
       <c r="H335" t="n">
         <v>0</v>
@@ -10113,7 +10113,7 @@
         <v>6.05000019073486</v>
       </c>
       <c r="G336" t="n">
-        <v>5.8861289024353</v>
+        <v>5.88612842559814</v>
       </c>
       <c r="H336" t="n">
         <v>0</v>
@@ -10142,7 +10142,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G337" t="n">
-        <v>5.64289999008179</v>
+        <v>5.64290046691895</v>
       </c>
       <c r="H337" t="n">
         <v>300</v>
@@ -10316,7 +10316,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G343" t="n">
-        <v>5.64289999008179</v>
+        <v>5.64290046691895</v>
       </c>
       <c r="H343" t="n">
         <v>1200</v>
@@ -10345,7 +10345,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G344" t="n">
-        <v>5.64289999008179</v>
+        <v>5.64290046691895</v>
       </c>
       <c r="H344" t="n">
         <v>0</v>
@@ -10374,7 +10374,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G345" t="n">
-        <v>5.64289999008179</v>
+        <v>5.64290046691895</v>
       </c>
       <c r="H345" t="n">
         <v>300</v>
@@ -10403,7 +10403,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G346" t="n">
-        <v>5.64289999008179</v>
+        <v>5.64290046691895</v>
       </c>
       <c r="H346" t="n">
         <v>0</v>
@@ -11128,7 +11128,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G371" t="n">
-        <v>5.64289999008179</v>
+        <v>5.64290046691895</v>
       </c>
       <c r="H371" t="n">
         <v>300</v>
@@ -11157,7 +11157,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G372" t="n">
-        <v>5.64289999008179</v>
+        <v>5.64290046691895</v>
       </c>
       <c r="H372" t="n">
         <v>0</v>
@@ -11186,7 +11186,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G373" t="n">
-        <v>5.64289999008179</v>
+        <v>5.64290046691895</v>
       </c>
       <c r="H373" t="n">
         <v>0</v>
@@ -11215,7 +11215,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G374" t="n">
-        <v>5.64289999008179</v>
+        <v>5.64290046691895</v>
       </c>
       <c r="H374" t="n">
         <v>0</v>
@@ -11244,7 +11244,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G375" t="n">
-        <v>5.64289999008179</v>
+        <v>5.64290046691895</v>
       </c>
       <c r="H375" t="n">
         <v>600</v>
@@ -11273,7 +11273,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G376" t="n">
-        <v>5.64289999008179</v>
+        <v>5.64290046691895</v>
       </c>
       <c r="H376" t="n">
         <v>0</v>
@@ -11302,7 +11302,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G377" t="n">
-        <v>5.64289999008179</v>
+        <v>5.64290046691895</v>
       </c>
       <c r="H377" t="n">
         <v>0</v>
@@ -11331,7 +11331,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G378" t="n">
-        <v>5.64289999008179</v>
+        <v>5.64290046691895</v>
       </c>
       <c r="H378" t="n">
         <v>0</v>
@@ -11360,7 +11360,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G379" t="n">
-        <v>5.64289999008179</v>
+        <v>5.64290046691895</v>
       </c>
       <c r="H379" t="n">
         <v>0</v>
@@ -11389,7 +11389,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G380" t="n">
-        <v>5.64289999008179</v>
+        <v>5.64290046691895</v>
       </c>
       <c r="H380" t="n">
         <v>0</v>
@@ -11650,7 +11650,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G389" t="n">
-        <v>5.69154596328735</v>
+        <v>5.6915454864502</v>
       </c>
       <c r="H389" t="n">
         <v>300</v>
@@ -11679,7 +11679,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G390" t="n">
-        <v>5.69154596328735</v>
+        <v>5.6915454864502</v>
       </c>
       <c r="H390" t="n">
         <v>0</v>
@@ -11708,7 +11708,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G391" t="n">
-        <v>5.69154596328735</v>
+        <v>5.6915454864502</v>
       </c>
       <c r="H391" t="n">
         <v>0</v>
@@ -11940,7 +11940,7 @@
         <v>5.75</v>
       </c>
       <c r="G399" t="n">
-        <v>5.59425449371338</v>
+        <v>5.59425401687622</v>
       </c>
       <c r="H399" t="n">
         <v>1500</v>
@@ -11969,7 +11969,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G400" t="n">
-        <v>5.69154596328735</v>
+        <v>5.6915454864502</v>
       </c>
       <c r="H400" t="n">
         <v>1200</v>
@@ -11998,7 +11998,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G401" t="n">
-        <v>5.69154596328735</v>
+        <v>5.6915454864502</v>
       </c>
       <c r="H401" t="n">
         <v>4500</v>
@@ -12027,7 +12027,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G402" t="n">
-        <v>5.69154596328735</v>
+        <v>5.6915454864502</v>
       </c>
       <c r="H402" t="n">
         <v>0</v>
@@ -12056,7 +12056,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G403" t="n">
-        <v>5.69154596328735</v>
+        <v>5.6915454864502</v>
       </c>
       <c r="H403" t="n">
         <v>0</v>
@@ -12085,7 +12085,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G404" t="n">
-        <v>5.69154596328735</v>
+        <v>5.6915454864502</v>
       </c>
       <c r="H404" t="n">
         <v>1500</v>
@@ -12114,7 +12114,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G405" t="n">
-        <v>5.69154596328735</v>
+        <v>5.6915454864502</v>
       </c>
       <c r="H405" t="n">
         <v>600</v>
@@ -12143,7 +12143,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G406" t="n">
-        <v>5.69154596328735</v>
+        <v>5.6915454864502</v>
       </c>
       <c r="H406" t="n">
         <v>0</v>
@@ -12172,7 +12172,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G407" t="n">
-        <v>5.69154596328735</v>
+        <v>5.6915454864502</v>
       </c>
       <c r="H407" t="n">
         <v>600</v>
@@ -12201,7 +12201,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G408" t="n">
-        <v>5.69154596328735</v>
+        <v>5.6915454864502</v>
       </c>
       <c r="H408" t="n">
         <v>0</v>
@@ -12230,7 +12230,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G409" t="n">
-        <v>5.64289999008179</v>
+        <v>5.64290046691895</v>
       </c>
       <c r="H409" t="n">
         <v>1200</v>
@@ -12259,7 +12259,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G410" t="n">
-        <v>5.64289999008179</v>
+        <v>5.64290046691895</v>
       </c>
       <c r="H410" t="n">
         <v>0</v>
@@ -12288,7 +12288,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G411" t="n">
-        <v>5.64289999008179</v>
+        <v>5.64290046691895</v>
       </c>
       <c r="H411" t="n">
         <v>4800</v>
@@ -12317,7 +12317,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G412" t="n">
-        <v>5.64289999008179</v>
+        <v>5.64290046691895</v>
       </c>
       <c r="H412" t="n">
         <v>0</v>
@@ -12346,7 +12346,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G413" t="n">
-        <v>5.64289999008179</v>
+        <v>5.64290046691895</v>
       </c>
       <c r="H413" t="n">
         <v>0</v>
@@ -12375,7 +12375,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G414" t="n">
-        <v>5.64289999008179</v>
+        <v>5.64290046691895</v>
       </c>
       <c r="H414" t="n">
         <v>0</v>
@@ -12404,7 +12404,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G415" t="n">
-        <v>5.64289999008179</v>
+        <v>5.64290046691895</v>
       </c>
       <c r="H415" t="n">
         <v>0</v>
@@ -12462,7 +12462,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G417" t="n">
-        <v>5.69154596328735</v>
+        <v>5.6915454864502</v>
       </c>
       <c r="H417" t="n">
         <v>300</v>
@@ -12491,7 +12491,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G418" t="n">
-        <v>5.69154596328735</v>
+        <v>5.6915454864502</v>
       </c>
       <c r="H418" t="n">
         <v>0</v>
@@ -12520,7 +12520,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G419" t="n">
-        <v>5.69154596328735</v>
+        <v>5.6915454864502</v>
       </c>
       <c r="H419" t="n">
         <v>0</v>
@@ -12549,7 +12549,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G420" t="n">
-        <v>5.69154596328735</v>
+        <v>5.6915454864502</v>
       </c>
       <c r="H420" t="n">
         <v>0</v>
@@ -12578,7 +12578,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G421" t="n">
-        <v>5.69154596328735</v>
+        <v>5.6915454864502</v>
       </c>
       <c r="H421" t="n">
         <v>0</v>
@@ -12607,7 +12607,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G422" t="n">
-        <v>5.69154596328735</v>
+        <v>5.6915454864502</v>
       </c>
       <c r="H422" t="n">
         <v>0</v>
@@ -12665,7 +12665,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G424" t="n">
-        <v>5.69154596328735</v>
+        <v>5.6915454864502</v>
       </c>
       <c r="H424" t="n">
         <v>300</v>
@@ -12694,7 +12694,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G425" t="n">
-        <v>5.69154596328735</v>
+        <v>5.6915454864502</v>
       </c>
       <c r="H425" t="n">
         <v>0</v>
@@ -12723,7 +12723,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G426" t="n">
-        <v>5.64289999008179</v>
+        <v>5.64290046691895</v>
       </c>
       <c r="H426" t="n">
         <v>900</v>
@@ -12810,7 +12810,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G429" t="n">
-        <v>5.64289999008179</v>
+        <v>5.64290046691895</v>
       </c>
       <c r="H429" t="n">
         <v>1200</v>
@@ -12839,7 +12839,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G430" t="n">
-        <v>5.64289999008179</v>
+        <v>5.64290046691895</v>
       </c>
       <c r="H430" t="n">
         <v>300</v>
@@ -12868,7 +12868,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G431" t="n">
-        <v>5.64289999008179</v>
+        <v>5.64290046691895</v>
       </c>
       <c r="H431" t="n">
         <v>600</v>
@@ -12897,7 +12897,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G432" t="n">
-        <v>5.64289999008179</v>
+        <v>5.64290046691895</v>
       </c>
       <c r="H432" t="n">
         <v>0</v>
@@ -12926,7 +12926,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G433" t="n">
-        <v>5.64289999008179</v>
+        <v>5.64290046691895</v>
       </c>
       <c r="H433" t="n">
         <v>0</v>
@@ -12955,7 +12955,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G434" t="n">
-        <v>5.64289999008179</v>
+        <v>5.64290046691895</v>
       </c>
       <c r="H434" t="n">
         <v>0</v>
@@ -12984,7 +12984,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G435" t="n">
-        <v>5.64289999008179</v>
+        <v>5.64290046691895</v>
       </c>
       <c r="H435" t="n">
         <v>0</v>
@@ -13013,7 +13013,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G436" t="n">
-        <v>5.64289999008179</v>
+        <v>5.64290046691895</v>
       </c>
       <c r="H436" t="n">
         <v>0</v>
@@ -13042,7 +13042,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G437" t="n">
-        <v>5.64289999008179</v>
+        <v>5.64290046691895</v>
       </c>
       <c r="H437" t="n">
         <v>0</v>
@@ -13071,7 +13071,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G438" t="n">
-        <v>5.64289999008179</v>
+        <v>5.64290046691895</v>
       </c>
       <c r="H438" t="n">
         <v>0</v>
@@ -13100,7 +13100,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G439" t="n">
-        <v>5.64289999008179</v>
+        <v>5.64290046691895</v>
       </c>
       <c r="H439" t="n">
         <v>0</v>
@@ -13129,7 +13129,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G440" t="n">
-        <v>5.64289999008179</v>
+        <v>5.64290046691895</v>
       </c>
       <c r="H440" t="n">
         <v>0</v>
@@ -13158,7 +13158,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G441" t="n">
-        <v>5.64289999008179</v>
+        <v>5.64290046691895</v>
       </c>
       <c r="H441" t="n">
         <v>0</v>
@@ -13187,7 +13187,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G442" t="n">
-        <v>5.64289999008179</v>
+        <v>5.64290046691895</v>
       </c>
       <c r="H442" t="n">
         <v>0</v>
@@ -13216,7 +13216,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G443" t="n">
-        <v>5.64289999008179</v>
+        <v>5.64290046691895</v>
       </c>
       <c r="H443" t="n">
         <v>0</v>
@@ -13419,7 +13419,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G450" t="n">
-        <v>5.64289999008179</v>
+        <v>5.64290046691895</v>
       </c>
       <c r="H450" t="n">
         <v>4500</v>
@@ -13506,7 +13506,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G453" t="n">
-        <v>5.69154596328735</v>
+        <v>5.6915454864502</v>
       </c>
       <c r="H453" t="n">
         <v>900</v>
@@ -13535,7 +13535,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G454" t="n">
-        <v>5.69154596328735</v>
+        <v>5.6915454864502</v>
       </c>
       <c r="H454" t="n">
         <v>0</v>
@@ -13680,7 +13680,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G459" t="n">
-        <v>6.37258577346802</v>
+        <v>6.37258529663086</v>
       </c>
       <c r="H459" t="n">
         <v>1500</v>
@@ -13709,7 +13709,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G460" t="n">
-        <v>6.37258577346802</v>
+        <v>6.37258529663086</v>
       </c>
       <c r="H460" t="n">
         <v>0</v>
@@ -13738,7 +13738,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G461" t="n">
-        <v>6.37258577346802</v>
+        <v>6.37258529663086</v>
       </c>
       <c r="H461" t="n">
         <v>0</v>
@@ -13767,7 +13767,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G462" t="n">
-        <v>6.37258577346802</v>
+        <v>6.37258529663086</v>
       </c>
       <c r="H462" t="n">
         <v>0</v>
@@ -13796,7 +13796,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G463" t="n">
-        <v>6.37258577346802</v>
+        <v>6.37258529663086</v>
       </c>
       <c r="H463" t="n">
         <v>0</v>
@@ -13825,7 +13825,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G464" t="n">
-        <v>6.37258577346802</v>
+        <v>6.37258529663086</v>
       </c>
       <c r="H464" t="n">
         <v>300</v>
@@ -13854,7 +13854,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G465" t="n">
-        <v>6.37258577346802</v>
+        <v>6.37258529663086</v>
       </c>
       <c r="H465" t="n">
         <v>4800</v>
@@ -13912,7 +13912,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G467" t="n">
-        <v>6.42123079299927</v>
+        <v>6.42123126983643</v>
       </c>
       <c r="H467" t="n">
         <v>6900</v>
@@ -14028,7 +14028,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G471" t="n">
-        <v>6.37258577346802</v>
+        <v>6.37258529663086</v>
       </c>
       <c r="H471" t="n">
         <v>600</v>
@@ -14057,7 +14057,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G472" t="n">
-        <v>6.22664880752563</v>
+        <v>6.22664833068848</v>
       </c>
       <c r="H472" t="n">
         <v>600</v>
@@ -14086,7 +14086,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G473" t="n">
-        <v>6.22664880752563</v>
+        <v>6.22664833068848</v>
       </c>
       <c r="H473" t="n">
         <v>0</v>
@@ -14115,7 +14115,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G474" t="n">
-        <v>6.22664880752563</v>
+        <v>6.22664833068848</v>
       </c>
       <c r="H474" t="n">
         <v>0</v>
@@ -14144,7 +14144,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G475" t="n">
-        <v>6.22664880752563</v>
+        <v>6.22664833068848</v>
       </c>
       <c r="H475" t="n">
         <v>0</v>
@@ -14173,7 +14173,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G476" t="n">
-        <v>6.22664880752563</v>
+        <v>6.22664833068848</v>
       </c>
       <c r="H476" t="n">
         <v>0</v>
@@ -14202,7 +14202,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G477" t="n">
-        <v>6.22664880752563</v>
+        <v>6.22664833068848</v>
       </c>
       <c r="H477" t="n">
         <v>0</v>
@@ -14231,7 +14231,7 @@
         <v>6.65000009536743</v>
       </c>
       <c r="G478" t="n">
-        <v>6.46987724304199</v>
+        <v>6.46987676620483</v>
       </c>
       <c r="H478" t="n">
         <v>2400</v>
@@ -14289,7 +14289,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G480" t="n">
-        <v>6.37258577346802</v>
+        <v>6.37258529663086</v>
       </c>
       <c r="H480" t="n">
         <v>1800</v>
@@ -14347,7 +14347,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G482" t="n">
-        <v>6.22664880752563</v>
+        <v>6.22664833068848</v>
       </c>
       <c r="H482" t="n">
         <v>3000</v>
@@ -14376,7 +14376,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G483" t="n">
-        <v>6.22664880752563</v>
+        <v>6.22664833068848</v>
       </c>
       <c r="H483" t="n">
         <v>0</v>
@@ -14405,7 +14405,7 @@
         <v>6.65000009536743</v>
       </c>
       <c r="G484" t="n">
-        <v>6.46987724304199</v>
+        <v>6.46987676620483</v>
       </c>
       <c r="H484" t="n">
         <v>2400</v>
@@ -14434,7 +14434,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G485" t="n">
-        <v>6.22664880752563</v>
+        <v>6.22664833068848</v>
       </c>
       <c r="H485" t="n">
         <v>1500</v>
@@ -14521,7 +14521,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G488" t="n">
-        <v>6.22664880752563</v>
+        <v>6.22664833068848</v>
       </c>
       <c r="H488" t="n">
         <v>4200</v>
@@ -14956,7 +14956,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G503" t="n">
-        <v>6.37258577346802</v>
+        <v>6.37258529663086</v>
       </c>
       <c r="H503" t="n">
         <v>1800</v>
@@ -14985,7 +14985,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G504" t="n">
-        <v>6.22664880752563</v>
+        <v>6.22664833068848</v>
       </c>
       <c r="H504" t="n">
         <v>2700</v>
@@ -15014,7 +15014,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G505" t="n">
-        <v>6.22664880752563</v>
+        <v>6.22664833068848</v>
       </c>
       <c r="H505" t="n">
         <v>0</v>
@@ -15043,7 +15043,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G506" t="n">
-        <v>6.22664880752563</v>
+        <v>6.22664833068848</v>
       </c>
       <c r="H506" t="n">
         <v>0</v>
@@ -15710,7 +15710,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G529" t="n">
-        <v>6.22664880752563</v>
+        <v>6.22664833068848</v>
       </c>
       <c r="H529" t="n">
         <v>3300</v>
@@ -15768,7 +15768,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G531" t="n">
-        <v>6.42123079299927</v>
+        <v>6.42123126983643</v>
       </c>
       <c r="H531" t="n">
         <v>1200</v>
@@ -15826,7 +15826,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G533" t="n">
-        <v>5.69154596328735</v>
+        <v>5.6915454864502</v>
       </c>
       <c r="H533" t="n">
         <v>8700</v>
@@ -15855,7 +15855,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G534" t="n">
-        <v>5.69154596328735</v>
+        <v>5.6915454864502</v>
       </c>
       <c r="H534" t="n">
         <v>300</v>
@@ -15884,7 +15884,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G535" t="n">
-        <v>5.69154596328735</v>
+        <v>5.6915454864502</v>
       </c>
       <c r="H535" t="n">
         <v>0</v>
@@ -15913,7 +15913,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G536" t="n">
-        <v>5.64289999008179</v>
+        <v>5.64290046691895</v>
       </c>
       <c r="H536" t="n">
         <v>2400</v>
@@ -16232,7 +16232,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G547" t="n">
-        <v>6.22664880752563</v>
+        <v>6.22664833068848</v>
       </c>
       <c r="H547" t="n">
         <v>1500</v>
@@ -16261,7 +16261,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G548" t="n">
-        <v>6.22664880752563</v>
+        <v>6.22664833068848</v>
       </c>
       <c r="H548" t="n">
         <v>1200</v>
@@ -16290,7 +16290,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G549" t="n">
-        <v>6.22664880752563</v>
+        <v>6.22664833068848</v>
       </c>
       <c r="H549" t="n">
         <v>1200</v>
@@ -16348,7 +16348,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G551" t="n">
-        <v>6.37258577346802</v>
+        <v>6.37258529663086</v>
       </c>
       <c r="H551" t="n">
         <v>60600</v>
@@ -16377,7 +16377,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G552" t="n">
-        <v>6.37258577346802</v>
+        <v>6.37258529663086</v>
       </c>
       <c r="H552" t="n">
         <v>0</v>
@@ -16406,7 +16406,7 @@
         <v>6.65000009536743</v>
       </c>
       <c r="G553" t="n">
-        <v>6.46987724304199</v>
+        <v>6.46987676620483</v>
       </c>
       <c r="H553" t="n">
         <v>300</v>
@@ -16435,7 +16435,7 @@
         <v>6.65000009536743</v>
       </c>
       <c r="G554" t="n">
-        <v>6.46987724304199</v>
+        <v>6.46987676620483</v>
       </c>
       <c r="H554" t="n">
         <v>0</v>
@@ -27229,6 +27229,35 @@
         <v>0</v>
       </c>
       <c r="I926" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="927">
+      <c r="A927" t="s">
+        <v>9</v>
+      </c>
+      <c r="B927" s="1" t="n">
+        <v>46321.3333333333</v>
+      </c>
+      <c r="C927" t="n">
+        <v>11.8999996185303</v>
+      </c>
+      <c r="D927" t="n">
+        <v>11.8999996185303</v>
+      </c>
+      <c r="E927" t="n">
+        <v>11.8999996185303</v>
+      </c>
+      <c r="F927" t="n">
+        <v>11.8999996185303</v>
+      </c>
+      <c r="G927" t="n">
+        <v>11.8999996185303</v>
+      </c>
+      <c r="H927" t="n">
+        <v>0</v>
+      </c>
+      <c r="I927" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/VLT.MI.xlsx
+++ b/data/VLT.MI.xlsx
@@ -27261,6 +27261,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="928">
+      <c r="A928" t="s">
+        <v>9</v>
+      </c>
+      <c r="B928" s="1" t="n">
+        <v>46322.3333333333</v>
+      </c>
+      <c r="C928" t="n">
+        <v>11.8999996185303</v>
+      </c>
+      <c r="D928" t="n">
+        <v>11.8999996185303</v>
+      </c>
+      <c r="E928" t="n">
+        <v>11.8999996185303</v>
+      </c>
+      <c r="F928" t="n">
+        <v>11.8999996185303</v>
+      </c>
+      <c r="G928" t="n">
+        <v>11.8999996185303</v>
+      </c>
+      <c r="H928" t="n">
+        <v>0</v>
+      </c>
+      <c r="I928" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/VLT.MI.xlsx
+++ b/data/VLT.MI.xlsx
@@ -27290,6 +27290,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="929">
+      <c r="A929" t="s">
+        <v>9</v>
+      </c>
+      <c r="B929" s="1" t="n">
+        <v>46323.3333333333</v>
+      </c>
+      <c r="C929" t="n">
+        <v>11.8999996185303</v>
+      </c>
+      <c r="D929" t="n">
+        <v>11.8999996185303</v>
+      </c>
+      <c r="E929" t="n">
+        <v>11.8999996185303</v>
+      </c>
+      <c r="F929" t="n">
+        <v>11.8999996185303</v>
+      </c>
+      <c r="G929" t="n">
+        <v>11.8999996185303</v>
+      </c>
+      <c r="H929" t="n">
+        <v>0</v>
+      </c>
+      <c r="I929" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/VLT.MI.xlsx
+++ b/data/VLT.MI.xlsx
@@ -543,7 +543,7 @@
         <v>5.69799995422363</v>
       </c>
       <c r="G6" t="n">
-        <v>5.54366254806519</v>
+        <v>5.54366302490234</v>
       </c>
       <c r="H6" t="n">
         <v>18900</v>
@@ -717,7 +717,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G12" t="n">
-        <v>5.02023506164551</v>
+        <v>5.02023553848267</v>
       </c>
       <c r="H12" t="n">
         <v>3300</v>
@@ -804,7 +804,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G15" t="n">
-        <v>5.15644359588623</v>
+        <v>5.15644311904907</v>
       </c>
       <c r="H15" t="n">
         <v>1500</v>
@@ -1094,7 +1094,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G25" t="n">
-        <v>5.19535970687866</v>
+        <v>5.19536018371582</v>
       </c>
       <c r="H25" t="n">
         <v>1800</v>
@@ -1123,7 +1123,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G26" t="n">
-        <v>5.19535970687866</v>
+        <v>5.19536018371582</v>
       </c>
       <c r="H26" t="n">
         <v>0</v>
@@ -1152,7 +1152,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G27" t="n">
-        <v>5.19535970687866</v>
+        <v>5.19536018371582</v>
       </c>
       <c r="H27" t="n">
         <v>0</v>
@@ -1384,7 +1384,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G35" t="n">
-        <v>5.38994216918945</v>
+        <v>5.38994264602661</v>
       </c>
       <c r="H35" t="n">
         <v>300</v>
@@ -1848,7 +1848,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G51" t="n">
-        <v>4.65052795410156</v>
+        <v>4.65052843093872</v>
       </c>
       <c r="H51" t="n">
         <v>1500</v>
@@ -1993,7 +1993,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G56" t="n">
-        <v>4.70890283584595</v>
+        <v>4.70890331268311</v>
       </c>
       <c r="H56" t="n">
         <v>300</v>
@@ -2399,7 +2399,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G70" t="n">
-        <v>4.70890283584595</v>
+        <v>4.70890331268311</v>
       </c>
       <c r="H70" t="n">
         <v>300</v>
@@ -2747,7 +2747,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G82" t="n">
-        <v>4.70890283584595</v>
+        <v>4.70890331268311</v>
       </c>
       <c r="H82" t="n">
         <v>900</v>
@@ -2776,7 +2776,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G83" t="n">
-        <v>4.70890283584595</v>
+        <v>4.70890331268311</v>
       </c>
       <c r="H83" t="n">
         <v>0</v>
@@ -2805,7 +2805,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G84" t="n">
-        <v>4.66025733947754</v>
+        <v>4.66025686264038</v>
       </c>
       <c r="H84" t="n">
         <v>1200</v>
@@ -3298,7 +3298,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G101" t="n">
-        <v>4.70890283584595</v>
+        <v>4.70890331268311</v>
       </c>
       <c r="H101" t="n">
         <v>1200</v>
@@ -3356,7 +3356,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G103" t="n">
-        <v>4.66025733947754</v>
+        <v>4.66025686264038</v>
       </c>
       <c r="H103" t="n">
         <v>300</v>
@@ -3385,7 +3385,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G104" t="n">
-        <v>4.66025733947754</v>
+        <v>4.66025686264038</v>
       </c>
       <c r="H104" t="n">
         <v>0</v>
@@ -3414,7 +3414,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G105" t="n">
-        <v>4.66025733947754</v>
+        <v>4.66025686264038</v>
       </c>
       <c r="H105" t="n">
         <v>0</v>
@@ -3443,7 +3443,7 @@
         <v>4.5</v>
       </c>
       <c r="G106" t="n">
-        <v>4.37811231613159</v>
+        <v>4.37811183929443</v>
       </c>
       <c r="H106" t="n">
         <v>4800</v>
@@ -3472,7 +3472,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G107" t="n">
-        <v>4.47540378570557</v>
+        <v>4.47540330886841</v>
       </c>
       <c r="H107" t="n">
         <v>3600</v>
@@ -3501,7 +3501,7 @@
         <v>4.5</v>
       </c>
       <c r="G108" t="n">
-        <v>4.37811231613159</v>
+        <v>4.37811183929443</v>
       </c>
       <c r="H108" t="n">
         <v>600</v>
@@ -3646,7 +3646,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G113" t="n">
-        <v>4.47540378570557</v>
+        <v>4.47540330886841</v>
       </c>
       <c r="H113" t="n">
         <v>300</v>
@@ -3675,7 +3675,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G114" t="n">
-        <v>4.47540378570557</v>
+        <v>4.47540330886841</v>
       </c>
       <c r="H114" t="n">
         <v>300</v>
@@ -3733,7 +3733,7 @@
         <v>4.53000020980835</v>
       </c>
       <c r="G116" t="n">
-        <v>4.40729999542236</v>
+        <v>4.40729951858521</v>
       </c>
       <c r="H116" t="n">
         <v>2700</v>
@@ -3762,7 +3762,7 @@
         <v>4.53000020980835</v>
       </c>
       <c r="G117" t="n">
-        <v>4.40729999542236</v>
+        <v>4.40729951858521</v>
       </c>
       <c r="H117" t="n">
         <v>0</v>
@@ -4255,7 +4255,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G134" t="n">
-        <v>4.35865354537964</v>
+        <v>4.3586540222168</v>
       </c>
       <c r="H134" t="n">
         <v>600</v>
@@ -4284,7 +4284,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G135" t="n">
-        <v>4.35865354537964</v>
+        <v>4.3586540222168</v>
       </c>
       <c r="H135" t="n">
         <v>0</v>
@@ -4313,7 +4313,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G136" t="n">
-        <v>4.35865354537964</v>
+        <v>4.3586540222168</v>
       </c>
       <c r="H136" t="n">
         <v>0</v>
@@ -4342,7 +4342,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G137" t="n">
-        <v>4.35865354537964</v>
+        <v>4.3586540222168</v>
       </c>
       <c r="H137" t="n">
         <v>0</v>
@@ -4371,7 +4371,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G138" t="n">
-        <v>4.35865354537964</v>
+        <v>4.3586540222168</v>
       </c>
       <c r="H138" t="n">
         <v>0</v>
@@ -4400,7 +4400,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G139" t="n">
-        <v>4.35865354537964</v>
+        <v>4.3586540222168</v>
       </c>
       <c r="H139" t="n">
         <v>0</v>
@@ -4429,7 +4429,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G140" t="n">
-        <v>4.35865354537964</v>
+        <v>4.3586540222168</v>
       </c>
       <c r="H140" t="n">
         <v>3000</v>
@@ -4458,7 +4458,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G141" t="n">
-        <v>4.35865354537964</v>
+        <v>4.3586540222168</v>
       </c>
       <c r="H141" t="n">
         <v>0</v>
@@ -4632,7 +4632,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G147" t="n">
-        <v>4.96186065673828</v>
+        <v>4.96186017990112</v>
       </c>
       <c r="H147" t="n">
         <v>1500</v>
@@ -4661,7 +4661,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G148" t="n">
-        <v>4.73809003829956</v>
+        <v>4.73809051513672</v>
       </c>
       <c r="H148" t="n">
         <v>4500</v>
@@ -4690,7 +4690,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G149" t="n">
-        <v>4.66025733947754</v>
+        <v>4.66025686264038</v>
       </c>
       <c r="H149" t="n">
         <v>2100</v>
@@ -4777,7 +4777,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G152" t="n">
-        <v>4.70890283584595</v>
+        <v>4.70890331268311</v>
       </c>
       <c r="H152" t="n">
         <v>600</v>
@@ -4980,7 +4980,7 @@
         <v>4.5</v>
       </c>
       <c r="G159" t="n">
-        <v>4.37811231613159</v>
+        <v>4.37811183929443</v>
       </c>
       <c r="H159" t="n">
         <v>3900</v>
@@ -5009,7 +5009,7 @@
         <v>4.5</v>
       </c>
       <c r="G160" t="n">
-        <v>4.37811231613159</v>
+        <v>4.37811183929443</v>
       </c>
       <c r="H160" t="n">
         <v>0</v>
@@ -5038,7 +5038,7 @@
         <v>4.5</v>
       </c>
       <c r="G161" t="n">
-        <v>4.37811231613159</v>
+        <v>4.37811183929443</v>
       </c>
       <c r="H161" t="n">
         <v>1800</v>
@@ -5067,7 +5067,7 @@
         <v>4.5</v>
       </c>
       <c r="G162" t="n">
-        <v>4.37811231613159</v>
+        <v>4.37811183929443</v>
       </c>
       <c r="H162" t="n">
         <v>1200</v>
@@ -5212,7 +5212,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G167" t="n">
-        <v>4.47540378570557</v>
+        <v>4.47540330886841</v>
       </c>
       <c r="H167" t="n">
         <v>900</v>
@@ -5241,7 +5241,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G168" t="n">
-        <v>4.47540378570557</v>
+        <v>4.47540330886841</v>
       </c>
       <c r="H168" t="n">
         <v>0</v>
@@ -5270,7 +5270,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G169" t="n">
-        <v>4.47540378570557</v>
+        <v>4.47540330886841</v>
       </c>
       <c r="H169" t="n">
         <v>0</v>
@@ -5299,7 +5299,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G170" t="n">
-        <v>4.47540378570557</v>
+        <v>4.47540330886841</v>
       </c>
       <c r="H170" t="n">
         <v>0</v>
@@ -5328,7 +5328,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G171" t="n">
-        <v>4.47540378570557</v>
+        <v>4.47540330886841</v>
       </c>
       <c r="H171" t="n">
         <v>0</v>
@@ -5357,7 +5357,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G172" t="n">
-        <v>4.47540378570557</v>
+        <v>4.47540330886841</v>
       </c>
       <c r="H172" t="n">
         <v>0</v>
@@ -5386,7 +5386,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G173" t="n">
-        <v>4.47540378570557</v>
+        <v>4.47540330886841</v>
       </c>
       <c r="H173" t="n">
         <v>0</v>
@@ -5415,7 +5415,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G174" t="n">
-        <v>4.47540378570557</v>
+        <v>4.47540330886841</v>
       </c>
       <c r="H174" t="n">
         <v>0</v>
@@ -5560,7 +5560,7 @@
         <v>4.76999998092651</v>
       </c>
       <c r="G179" t="n">
-        <v>4.64079856872559</v>
+        <v>4.64079904556274</v>
       </c>
       <c r="H179" t="n">
         <v>1200</v>
@@ -5618,7 +5618,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G181" t="n">
-        <v>4.68944501876831</v>
+        <v>4.68944454193115</v>
       </c>
       <c r="H181" t="n">
         <v>600</v>
@@ -5647,7 +5647,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G182" t="n">
-        <v>4.68944501876831</v>
+        <v>4.68944454193115</v>
       </c>
       <c r="H182" t="n">
         <v>300</v>
@@ -5676,7 +5676,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G183" t="n">
-        <v>4.68944501876831</v>
+        <v>4.68944454193115</v>
       </c>
       <c r="H183" t="n">
         <v>2400</v>
@@ -5705,7 +5705,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G184" t="n">
-        <v>4.68944501876831</v>
+        <v>4.68944454193115</v>
       </c>
       <c r="H184" t="n">
         <v>0</v>
@@ -5821,7 +5821,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G188" t="n">
-        <v>5.15644359588623</v>
+        <v>5.15644311904907</v>
       </c>
       <c r="H188" t="n">
         <v>600</v>
@@ -6198,7 +6198,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G201" t="n">
-        <v>4.96186065673828</v>
+        <v>4.96186017990112</v>
       </c>
       <c r="H201" t="n">
         <v>600</v>
@@ -6227,7 +6227,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G202" t="n">
-        <v>4.96186065673828</v>
+        <v>4.96186017990112</v>
       </c>
       <c r="H202" t="n">
         <v>300</v>
@@ -6256,7 +6256,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G203" t="n">
-        <v>4.96186065673828</v>
+        <v>4.96186017990112</v>
       </c>
       <c r="H203" t="n">
         <v>300</v>
@@ -6575,7 +6575,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G214" t="n">
-        <v>5.4288592338562</v>
+        <v>5.42885875701904</v>
       </c>
       <c r="H214" t="n">
         <v>3600</v>
@@ -6720,7 +6720,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G219" t="n">
-        <v>5.40940046310425</v>
+        <v>5.40940093994141</v>
       </c>
       <c r="H219" t="n">
         <v>1800</v>
@@ -7445,7 +7445,7 @@
         <v>6.03999996185303</v>
       </c>
       <c r="G244" t="n">
-        <v>5.87639904022217</v>
+        <v>5.87639951705933</v>
       </c>
       <c r="H244" t="n">
         <v>9300</v>
@@ -7909,7 +7909,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G260" t="n">
-        <v>5.64290046691895</v>
+        <v>5.64289999008179</v>
       </c>
       <c r="H260" t="n">
         <v>300</v>
@@ -7938,7 +7938,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G261" t="n">
-        <v>5.64290046691895</v>
+        <v>5.64289999008179</v>
       </c>
       <c r="H261" t="n">
         <v>0</v>
@@ -7967,7 +7967,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G262" t="n">
-        <v>5.64290046691895</v>
+        <v>5.64289999008179</v>
       </c>
       <c r="H262" t="n">
         <v>0</v>
@@ -7996,7 +7996,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G263" t="n">
-        <v>5.64290046691895</v>
+        <v>5.64289999008179</v>
       </c>
       <c r="H263" t="n">
         <v>0</v>
@@ -8025,7 +8025,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G264" t="n">
-        <v>5.64290046691895</v>
+        <v>5.64289999008179</v>
       </c>
       <c r="H264" t="n">
         <v>300</v>
@@ -8054,7 +8054,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G265" t="n">
-        <v>5.64290046691895</v>
+        <v>5.64289999008179</v>
       </c>
       <c r="H265" t="n">
         <v>0</v>
@@ -8112,7 +8112,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G267" t="n">
-        <v>5.64290046691895</v>
+        <v>5.64289999008179</v>
       </c>
       <c r="H267" t="n">
         <v>300</v>
@@ -8141,7 +8141,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G268" t="n">
-        <v>5.64290046691895</v>
+        <v>5.64289999008179</v>
       </c>
       <c r="H268" t="n">
         <v>0</v>
@@ -8315,7 +8315,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G274" t="n">
-        <v>5.72073364257812</v>
+        <v>5.72073316574097</v>
       </c>
       <c r="H274" t="n">
         <v>900</v>
@@ -8489,7 +8489,7 @@
         <v>6.05000019073486</v>
       </c>
       <c r="G280" t="n">
-        <v>5.88612842559814</v>
+        <v>5.8861289024353</v>
       </c>
       <c r="H280" t="n">
         <v>3900</v>
@@ -8576,7 +8576,7 @@
         <v>6.05000019073486</v>
       </c>
       <c r="G283" t="n">
-        <v>5.88612842559814</v>
+        <v>5.8861289024353</v>
       </c>
       <c r="H283" t="n">
         <v>4800</v>
@@ -8605,7 +8605,7 @@
         <v>6.05000019073486</v>
       </c>
       <c r="G284" t="n">
-        <v>5.88612842559814</v>
+        <v>5.8861289024353</v>
       </c>
       <c r="H284" t="n">
         <v>0</v>
@@ -9330,7 +9330,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G309" t="n">
-        <v>5.6915454864502</v>
+        <v>5.69154596328735</v>
       </c>
       <c r="H309" t="n">
         <v>5100</v>
@@ -9359,7 +9359,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G310" t="n">
-        <v>5.6915454864502</v>
+        <v>5.69154596328735</v>
       </c>
       <c r="H310" t="n">
         <v>4200</v>
@@ -9388,7 +9388,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G311" t="n">
-        <v>5.6915454864502</v>
+        <v>5.69154596328735</v>
       </c>
       <c r="H311" t="n">
         <v>3000</v>
@@ -9417,7 +9417,7 @@
         <v>5.75</v>
       </c>
       <c r="G312" t="n">
-        <v>5.59425401687622</v>
+        <v>5.59425449371338</v>
       </c>
       <c r="H312" t="n">
         <v>2400</v>
@@ -9446,7 +9446,7 @@
         <v>5.75</v>
       </c>
       <c r="G313" t="n">
-        <v>5.59425401687622</v>
+        <v>5.59425449371338</v>
       </c>
       <c r="H313" t="n">
         <v>5100</v>
@@ -9475,7 +9475,7 @@
         <v>5.75</v>
       </c>
       <c r="G314" t="n">
-        <v>5.59425401687622</v>
+        <v>5.59425449371338</v>
       </c>
       <c r="H314" t="n">
         <v>0</v>
@@ -9504,7 +9504,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G315" t="n">
-        <v>5.6915454864502</v>
+        <v>5.69154596328735</v>
       </c>
       <c r="H315" t="n">
         <v>2100</v>
@@ -9533,7 +9533,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G316" t="n">
-        <v>5.6915454864502</v>
+        <v>5.69154596328735</v>
       </c>
       <c r="H316" t="n">
         <v>300</v>
@@ -9562,7 +9562,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G317" t="n">
-        <v>5.6915454864502</v>
+        <v>5.69154596328735</v>
       </c>
       <c r="H317" t="n">
         <v>0</v>
@@ -9591,7 +9591,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G318" t="n">
-        <v>5.6915454864502</v>
+        <v>5.69154596328735</v>
       </c>
       <c r="H318" t="n">
         <v>0</v>
@@ -9620,7 +9620,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G319" t="n">
-        <v>5.6915454864502</v>
+        <v>5.69154596328735</v>
       </c>
       <c r="H319" t="n">
         <v>0</v>
@@ -9765,7 +9765,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G324" t="n">
-        <v>5.64290046691895</v>
+        <v>5.64289999008179</v>
       </c>
       <c r="H324" t="n">
         <v>600</v>
@@ -9794,7 +9794,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G325" t="n">
-        <v>5.64290046691895</v>
+        <v>5.64289999008179</v>
       </c>
       <c r="H325" t="n">
         <v>0</v>
@@ -9823,7 +9823,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G326" t="n">
-        <v>5.64290046691895</v>
+        <v>5.64289999008179</v>
       </c>
       <c r="H326" t="n">
         <v>0</v>
@@ -9852,7 +9852,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G327" t="n">
-        <v>5.64290046691895</v>
+        <v>5.64289999008179</v>
       </c>
       <c r="H327" t="n">
         <v>0</v>
@@ -9881,7 +9881,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G328" t="n">
-        <v>5.64290046691895</v>
+        <v>5.64289999008179</v>
       </c>
       <c r="H328" t="n">
         <v>0</v>
@@ -9910,7 +9910,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G329" t="n">
-        <v>5.64290046691895</v>
+        <v>5.64289999008179</v>
       </c>
       <c r="H329" t="n">
         <v>0</v>
@@ -9939,7 +9939,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G330" t="n">
-        <v>5.64290046691895</v>
+        <v>5.64289999008179</v>
       </c>
       <c r="H330" t="n">
         <v>0</v>
@@ -9968,7 +9968,7 @@
         <v>6.05000019073486</v>
       </c>
       <c r="G331" t="n">
-        <v>5.88612842559814</v>
+        <v>5.8861289024353</v>
       </c>
       <c r="H331" t="n">
         <v>1500</v>
@@ -9997,7 +9997,7 @@
         <v>6.05000019073486</v>
       </c>
       <c r="G332" t="n">
-        <v>5.88612842559814</v>
+        <v>5.8861289024353</v>
       </c>
       <c r="H332" t="n">
         <v>0</v>
@@ -10026,7 +10026,7 @@
         <v>6.05000019073486</v>
       </c>
       <c r="G333" t="n">
-        <v>5.88612842559814</v>
+        <v>5.8861289024353</v>
       </c>
       <c r="H333" t="n">
         <v>0</v>
@@ -10055,7 +10055,7 @@
         <v>6.05000019073486</v>
       </c>
       <c r="G334" t="n">
-        <v>5.88612842559814</v>
+        <v>5.8861289024353</v>
       </c>
       <c r="H334" t="n">
         <v>0</v>
@@ -10084,7 +10084,7 @@
         <v>6.05000019073486</v>
       </c>
       <c r="G335" t="n">
-        <v>5.88612842559814</v>
+        <v>5.8861289024353</v>
       </c>
       <c r="H335" t="n">
         <v>0</v>
@@ -10113,7 +10113,7 @@
         <v>6.05000019073486</v>
       </c>
       <c r="G336" t="n">
-        <v>5.88612842559814</v>
+        <v>5.8861289024353</v>
       </c>
       <c r="H336" t="n">
         <v>0</v>
@@ -10142,7 +10142,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G337" t="n">
-        <v>5.64290046691895</v>
+        <v>5.64289999008179</v>
       </c>
       <c r="H337" t="n">
         <v>300</v>
@@ -10316,7 +10316,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G343" t="n">
-        <v>5.64290046691895</v>
+        <v>5.64289999008179</v>
       </c>
       <c r="H343" t="n">
         <v>1200</v>
@@ -10345,7 +10345,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G344" t="n">
-        <v>5.64290046691895</v>
+        <v>5.64289999008179</v>
       </c>
       <c r="H344" t="n">
         <v>0</v>
@@ -10374,7 +10374,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G345" t="n">
-        <v>5.64290046691895</v>
+        <v>5.64289999008179</v>
       </c>
       <c r="H345" t="n">
         <v>300</v>
@@ -10403,7 +10403,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G346" t="n">
-        <v>5.64290046691895</v>
+        <v>5.64289999008179</v>
       </c>
       <c r="H346" t="n">
         <v>0</v>
@@ -11128,7 +11128,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G371" t="n">
-        <v>5.64290046691895</v>
+        <v>5.64289999008179</v>
       </c>
       <c r="H371" t="n">
         <v>300</v>
@@ -11157,7 +11157,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G372" t="n">
-        <v>5.64290046691895</v>
+        <v>5.64289999008179</v>
       </c>
       <c r="H372" t="n">
         <v>0</v>
@@ -11186,7 +11186,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G373" t="n">
-        <v>5.64290046691895</v>
+        <v>5.64289999008179</v>
       </c>
       <c r="H373" t="n">
         <v>0</v>
@@ -11215,7 +11215,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G374" t="n">
-        <v>5.64290046691895</v>
+        <v>5.64289999008179</v>
       </c>
       <c r="H374" t="n">
         <v>0</v>
@@ -11244,7 +11244,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G375" t="n">
-        <v>5.64290046691895</v>
+        <v>5.64289999008179</v>
       </c>
       <c r="H375" t="n">
         <v>600</v>
@@ -11273,7 +11273,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G376" t="n">
-        <v>5.64290046691895</v>
+        <v>5.64289999008179</v>
       </c>
       <c r="H376" t="n">
         <v>0</v>
@@ -11302,7 +11302,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G377" t="n">
-        <v>5.64290046691895</v>
+        <v>5.64289999008179</v>
       </c>
       <c r="H377" t="n">
         <v>0</v>
@@ -11331,7 +11331,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G378" t="n">
-        <v>5.64290046691895</v>
+        <v>5.64289999008179</v>
       </c>
       <c r="H378" t="n">
         <v>0</v>
@@ -11360,7 +11360,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G379" t="n">
-        <v>5.64290046691895</v>
+        <v>5.64289999008179</v>
       </c>
       <c r="H379" t="n">
         <v>0</v>
@@ -11389,7 +11389,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G380" t="n">
-        <v>5.64290046691895</v>
+        <v>5.64289999008179</v>
       </c>
       <c r="H380" t="n">
         <v>0</v>
@@ -11650,7 +11650,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G389" t="n">
-        <v>5.6915454864502</v>
+        <v>5.69154596328735</v>
       </c>
       <c r="H389" t="n">
         <v>300</v>
@@ -11679,7 +11679,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G390" t="n">
-        <v>5.6915454864502</v>
+        <v>5.69154596328735</v>
       </c>
       <c r="H390" t="n">
         <v>0</v>
@@ -11708,7 +11708,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G391" t="n">
-        <v>5.6915454864502</v>
+        <v>5.69154596328735</v>
       </c>
       <c r="H391" t="n">
         <v>0</v>
@@ -11940,7 +11940,7 @@
         <v>5.75</v>
       </c>
       <c r="G399" t="n">
-        <v>5.59425401687622</v>
+        <v>5.59425449371338</v>
       </c>
       <c r="H399" t="n">
         <v>1500</v>
@@ -11969,7 +11969,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G400" t="n">
-        <v>5.6915454864502</v>
+        <v>5.69154596328735</v>
       </c>
       <c r="H400" t="n">
         <v>1200</v>
@@ -11998,7 +11998,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G401" t="n">
-        <v>5.6915454864502</v>
+        <v>5.69154596328735</v>
       </c>
       <c r="H401" t="n">
         <v>4500</v>
@@ -12027,7 +12027,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G402" t="n">
-        <v>5.6915454864502</v>
+        <v>5.69154596328735</v>
       </c>
       <c r="H402" t="n">
         <v>0</v>
@@ -12056,7 +12056,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G403" t="n">
-        <v>5.6915454864502</v>
+        <v>5.69154596328735</v>
       </c>
       <c r="H403" t="n">
         <v>0</v>
@@ -12085,7 +12085,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G404" t="n">
-        <v>5.6915454864502</v>
+        <v>5.69154596328735</v>
       </c>
       <c r="H404" t="n">
         <v>1500</v>
@@ -12114,7 +12114,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G405" t="n">
-        <v>5.6915454864502</v>
+        <v>5.69154596328735</v>
       </c>
       <c r="H405" t="n">
         <v>600</v>
@@ -12143,7 +12143,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G406" t="n">
-        <v>5.6915454864502</v>
+        <v>5.69154596328735</v>
       </c>
       <c r="H406" t="n">
         <v>0</v>
@@ -12172,7 +12172,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G407" t="n">
-        <v>5.6915454864502</v>
+        <v>5.69154596328735</v>
       </c>
       <c r="H407" t="n">
         <v>600</v>
@@ -12201,7 +12201,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G408" t="n">
-        <v>5.6915454864502</v>
+        <v>5.69154596328735</v>
       </c>
       <c r="H408" t="n">
         <v>0</v>
@@ -12230,7 +12230,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G409" t="n">
-        <v>5.64290046691895</v>
+        <v>5.64289999008179</v>
       </c>
       <c r="H409" t="n">
         <v>1200</v>
@@ -12259,7 +12259,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G410" t="n">
-        <v>5.64290046691895</v>
+        <v>5.64289999008179</v>
       </c>
       <c r="H410" t="n">
         <v>0</v>
@@ -12288,7 +12288,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G411" t="n">
-        <v>5.64290046691895</v>
+        <v>5.64289999008179</v>
       </c>
       <c r="H411" t="n">
         <v>4800</v>
@@ -12317,7 +12317,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G412" t="n">
-        <v>5.64290046691895</v>
+        <v>5.64289999008179</v>
       </c>
       <c r="H412" t="n">
         <v>0</v>
@@ -12346,7 +12346,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G413" t="n">
-        <v>5.64290046691895</v>
+        <v>5.64289999008179</v>
       </c>
       <c r="H413" t="n">
         <v>0</v>
@@ -12375,7 +12375,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G414" t="n">
-        <v>5.64290046691895</v>
+        <v>5.64289999008179</v>
       </c>
       <c r="H414" t="n">
         <v>0</v>
@@ -12404,7 +12404,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G415" t="n">
-        <v>5.64290046691895</v>
+        <v>5.64289999008179</v>
       </c>
       <c r="H415" t="n">
         <v>0</v>
@@ -12462,7 +12462,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G417" t="n">
-        <v>5.6915454864502</v>
+        <v>5.69154596328735</v>
       </c>
       <c r="H417" t="n">
         <v>300</v>
@@ -12491,7 +12491,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G418" t="n">
-        <v>5.6915454864502</v>
+        <v>5.69154596328735</v>
       </c>
       <c r="H418" t="n">
         <v>0</v>
@@ -12520,7 +12520,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G419" t="n">
-        <v>5.6915454864502</v>
+        <v>5.69154596328735</v>
       </c>
       <c r="H419" t="n">
         <v>0</v>
@@ -12549,7 +12549,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G420" t="n">
-        <v>5.6915454864502</v>
+        <v>5.69154596328735</v>
       </c>
       <c r="H420" t="n">
         <v>0</v>
@@ -12578,7 +12578,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G421" t="n">
-        <v>5.6915454864502</v>
+        <v>5.69154596328735</v>
       </c>
       <c r="H421" t="n">
         <v>0</v>
@@ -12607,7 +12607,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G422" t="n">
-        <v>5.6915454864502</v>
+        <v>5.69154596328735</v>
       </c>
       <c r="H422" t="n">
         <v>0</v>
@@ -12665,7 +12665,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G424" t="n">
-        <v>5.6915454864502</v>
+        <v>5.69154596328735</v>
       </c>
       <c r="H424" t="n">
         <v>300</v>
@@ -12694,7 +12694,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G425" t="n">
-        <v>5.6915454864502</v>
+        <v>5.69154596328735</v>
       </c>
       <c r="H425" t="n">
         <v>0</v>
@@ -12723,7 +12723,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G426" t="n">
-        <v>5.64290046691895</v>
+        <v>5.64289999008179</v>
       </c>
       <c r="H426" t="n">
         <v>900</v>
@@ -12810,7 +12810,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G429" t="n">
-        <v>5.64290046691895</v>
+        <v>5.64289999008179</v>
       </c>
       <c r="H429" t="n">
         <v>1200</v>
@@ -12839,7 +12839,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G430" t="n">
-        <v>5.64290046691895</v>
+        <v>5.64289999008179</v>
       </c>
       <c r="H430" t="n">
         <v>300</v>
@@ -12868,7 +12868,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G431" t="n">
-        <v>5.64290046691895</v>
+        <v>5.64289999008179</v>
       </c>
       <c r="H431" t="n">
         <v>600</v>
@@ -12897,7 +12897,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G432" t="n">
-        <v>5.64290046691895</v>
+        <v>5.64289999008179</v>
       </c>
       <c r="H432" t="n">
         <v>0</v>
@@ -12926,7 +12926,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G433" t="n">
-        <v>5.64290046691895</v>
+        <v>5.64289999008179</v>
       </c>
       <c r="H433" t="n">
         <v>0</v>
@@ -12955,7 +12955,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G434" t="n">
-        <v>5.64290046691895</v>
+        <v>5.64289999008179</v>
       </c>
       <c r="H434" t="n">
         <v>0</v>
@@ -12984,7 +12984,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G435" t="n">
-        <v>5.64290046691895</v>
+        <v>5.64289999008179</v>
       </c>
       <c r="H435" t="n">
         <v>0</v>
@@ -13013,7 +13013,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G436" t="n">
-        <v>5.64290046691895</v>
+        <v>5.64289999008179</v>
       </c>
       <c r="H436" t="n">
         <v>0</v>
@@ -13042,7 +13042,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G437" t="n">
-        <v>5.64290046691895</v>
+        <v>5.64289999008179</v>
       </c>
       <c r="H437" t="n">
         <v>0</v>
@@ -13071,7 +13071,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G438" t="n">
-        <v>5.64290046691895</v>
+        <v>5.64289999008179</v>
       </c>
       <c r="H438" t="n">
         <v>0</v>
@@ -13100,7 +13100,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G439" t="n">
-        <v>5.64290046691895</v>
+        <v>5.64289999008179</v>
       </c>
       <c r="H439" t="n">
         <v>0</v>
@@ -13129,7 +13129,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G440" t="n">
-        <v>5.64290046691895</v>
+        <v>5.64289999008179</v>
       </c>
       <c r="H440" t="n">
         <v>0</v>
@@ -13158,7 +13158,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G441" t="n">
-        <v>5.64290046691895</v>
+        <v>5.64289999008179</v>
       </c>
       <c r="H441" t="n">
         <v>0</v>
@@ -13187,7 +13187,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G442" t="n">
-        <v>5.64290046691895</v>
+        <v>5.64289999008179</v>
       </c>
       <c r="H442" t="n">
         <v>0</v>
@@ -13216,7 +13216,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G443" t="n">
-        <v>5.64290046691895</v>
+        <v>5.64289999008179</v>
       </c>
       <c r="H443" t="n">
         <v>0</v>
@@ -13419,7 +13419,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G450" t="n">
-        <v>5.64290046691895</v>
+        <v>5.64289999008179</v>
       </c>
       <c r="H450" t="n">
         <v>4500</v>
@@ -13506,7 +13506,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G453" t="n">
-        <v>5.6915454864502</v>
+        <v>5.69154596328735</v>
       </c>
       <c r="H453" t="n">
         <v>900</v>
@@ -13535,7 +13535,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G454" t="n">
-        <v>5.6915454864502</v>
+        <v>5.69154596328735</v>
       </c>
       <c r="H454" t="n">
         <v>0</v>
@@ -13680,7 +13680,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G459" t="n">
-        <v>6.37258529663086</v>
+        <v>6.37258577346802</v>
       </c>
       <c r="H459" t="n">
         <v>1500</v>
@@ -13709,7 +13709,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G460" t="n">
-        <v>6.37258529663086</v>
+        <v>6.37258577346802</v>
       </c>
       <c r="H460" t="n">
         <v>0</v>
@@ -13738,7 +13738,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G461" t="n">
-        <v>6.37258529663086</v>
+        <v>6.37258577346802</v>
       </c>
       <c r="H461" t="n">
         <v>0</v>
@@ -13767,7 +13767,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G462" t="n">
-        <v>6.37258529663086</v>
+        <v>6.37258577346802</v>
       </c>
       <c r="H462" t="n">
         <v>0</v>
@@ -13796,7 +13796,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G463" t="n">
-        <v>6.37258529663086</v>
+        <v>6.37258577346802</v>
       </c>
       <c r="H463" t="n">
         <v>0</v>
@@ -13825,7 +13825,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G464" t="n">
-        <v>6.37258529663086</v>
+        <v>6.37258577346802</v>
       </c>
       <c r="H464" t="n">
         <v>300</v>
@@ -13854,7 +13854,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G465" t="n">
-        <v>6.37258529663086</v>
+        <v>6.37258577346802</v>
       </c>
       <c r="H465" t="n">
         <v>4800</v>
@@ -13912,7 +13912,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G467" t="n">
-        <v>6.42123126983643</v>
+        <v>6.42123079299927</v>
       </c>
       <c r="H467" t="n">
         <v>6900</v>
@@ -14028,7 +14028,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G471" t="n">
-        <v>6.37258529663086</v>
+        <v>6.37258577346802</v>
       </c>
       <c r="H471" t="n">
         <v>600</v>
@@ -14057,7 +14057,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G472" t="n">
-        <v>6.22664833068848</v>
+        <v>6.22664880752563</v>
       </c>
       <c r="H472" t="n">
         <v>600</v>
@@ -14086,7 +14086,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G473" t="n">
-        <v>6.22664833068848</v>
+        <v>6.22664880752563</v>
       </c>
       <c r="H473" t="n">
         <v>0</v>
@@ -14115,7 +14115,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G474" t="n">
-        <v>6.22664833068848</v>
+        <v>6.22664880752563</v>
       </c>
       <c r="H474" t="n">
         <v>0</v>
@@ -14144,7 +14144,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G475" t="n">
-        <v>6.22664833068848</v>
+        <v>6.22664880752563</v>
       </c>
       <c r="H475" t="n">
         <v>0</v>
@@ -14173,7 +14173,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G476" t="n">
-        <v>6.22664833068848</v>
+        <v>6.22664880752563</v>
       </c>
       <c r="H476" t="n">
         <v>0</v>
@@ -14202,7 +14202,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G477" t="n">
-        <v>6.22664833068848</v>
+        <v>6.22664880752563</v>
       </c>
       <c r="H477" t="n">
         <v>0</v>
@@ -14231,7 +14231,7 @@
         <v>6.65000009536743</v>
       </c>
       <c r="G478" t="n">
-        <v>6.46987676620483</v>
+        <v>6.46987724304199</v>
       </c>
       <c r="H478" t="n">
         <v>2400</v>
@@ -14289,7 +14289,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G480" t="n">
-        <v>6.37258529663086</v>
+        <v>6.37258577346802</v>
       </c>
       <c r="H480" t="n">
         <v>1800</v>
@@ -14347,7 +14347,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G482" t="n">
-        <v>6.22664833068848</v>
+        <v>6.22664880752563</v>
       </c>
       <c r="H482" t="n">
         <v>3000</v>
@@ -14376,7 +14376,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G483" t="n">
-        <v>6.22664833068848</v>
+        <v>6.22664880752563</v>
       </c>
       <c r="H483" t="n">
         <v>0</v>
@@ -14405,7 +14405,7 @@
         <v>6.65000009536743</v>
       </c>
       <c r="G484" t="n">
-        <v>6.46987676620483</v>
+        <v>6.46987724304199</v>
       </c>
       <c r="H484" t="n">
         <v>2400</v>
@@ -14434,7 +14434,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G485" t="n">
-        <v>6.22664833068848</v>
+        <v>6.22664880752563</v>
       </c>
       <c r="H485" t="n">
         <v>1500</v>
@@ -14521,7 +14521,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G488" t="n">
-        <v>6.22664833068848</v>
+        <v>6.22664880752563</v>
       </c>
       <c r="H488" t="n">
         <v>4200</v>
@@ -14956,7 +14956,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G503" t="n">
-        <v>6.37258529663086</v>
+        <v>6.37258577346802</v>
       </c>
       <c r="H503" t="n">
         <v>1800</v>
@@ -14985,7 +14985,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G504" t="n">
-        <v>6.22664833068848</v>
+        <v>6.22664880752563</v>
       </c>
       <c r="H504" t="n">
         <v>2700</v>
@@ -15014,7 +15014,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G505" t="n">
-        <v>6.22664833068848</v>
+        <v>6.22664880752563</v>
       </c>
       <c r="H505" t="n">
         <v>0</v>
@@ -15043,7 +15043,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G506" t="n">
-        <v>6.22664833068848</v>
+        <v>6.22664880752563</v>
       </c>
       <c r="H506" t="n">
         <v>0</v>
@@ -15710,7 +15710,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G529" t="n">
-        <v>6.22664833068848</v>
+        <v>6.22664880752563</v>
       </c>
       <c r="H529" t="n">
         <v>3300</v>
@@ -15768,7 +15768,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G531" t="n">
-        <v>6.42123126983643</v>
+        <v>6.42123079299927</v>
       </c>
       <c r="H531" t="n">
         <v>1200</v>
@@ -15826,7 +15826,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G533" t="n">
-        <v>5.6915454864502</v>
+        <v>5.69154596328735</v>
       </c>
       <c r="H533" t="n">
         <v>8700</v>
@@ -15855,7 +15855,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G534" t="n">
-        <v>5.6915454864502</v>
+        <v>5.69154596328735</v>
       </c>
       <c r="H534" t="n">
         <v>300</v>
@@ -15884,7 +15884,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G535" t="n">
-        <v>5.6915454864502</v>
+        <v>5.69154596328735</v>
       </c>
       <c r="H535" t="n">
         <v>0</v>
@@ -15913,7 +15913,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G536" t="n">
-        <v>5.64290046691895</v>
+        <v>5.64289999008179</v>
       </c>
       <c r="H536" t="n">
         <v>2400</v>
@@ -16232,7 +16232,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G547" t="n">
-        <v>6.22664833068848</v>
+        <v>6.22664880752563</v>
       </c>
       <c r="H547" t="n">
         <v>1500</v>
@@ -16261,7 +16261,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G548" t="n">
-        <v>6.22664833068848</v>
+        <v>6.22664880752563</v>
       </c>
       <c r="H548" t="n">
         <v>1200</v>
@@ -16290,7 +16290,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G549" t="n">
-        <v>6.22664833068848</v>
+        <v>6.22664880752563</v>
       </c>
       <c r="H549" t="n">
         <v>1200</v>
@@ -16348,7 +16348,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G551" t="n">
-        <v>6.37258529663086</v>
+        <v>6.37258577346802</v>
       </c>
       <c r="H551" t="n">
         <v>60600</v>
@@ -16377,7 +16377,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G552" t="n">
-        <v>6.37258529663086</v>
+        <v>6.37258577346802</v>
       </c>
       <c r="H552" t="n">
         <v>0</v>
@@ -16406,7 +16406,7 @@
         <v>6.65000009536743</v>
       </c>
       <c r="G553" t="n">
-        <v>6.46987676620483</v>
+        <v>6.46987724304199</v>
       </c>
       <c r="H553" t="n">
         <v>300</v>
@@ -16435,7 +16435,7 @@
         <v>6.65000009536743</v>
       </c>
       <c r="G554" t="n">
-        <v>6.46987676620483</v>
+        <v>6.46987724304199</v>
       </c>
       <c r="H554" t="n">
         <v>0</v>
@@ -27316,6 +27316,35 @@
         <v>0</v>
       </c>
       <c r="I929" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="930">
+      <c r="A930" t="s">
+        <v>9</v>
+      </c>
+      <c r="B930" s="1" t="n">
+        <v>46324.3333333333</v>
+      </c>
+      <c r="C930" t="n">
+        <v>11.8999996185303</v>
+      </c>
+      <c r="D930" t="n">
+        <v>11.8999996185303</v>
+      </c>
+      <c r="E930" t="n">
+        <v>11.8999996185303</v>
+      </c>
+      <c r="F930" t="n">
+        <v>11.8999996185303</v>
+      </c>
+      <c r="G930" t="n">
+        <v>11.8999996185303</v>
+      </c>
+      <c r="H930" t="n">
+        <v>0</v>
+      </c>
+      <c r="I930" t="s">
         <v>9</v>
       </c>
     </row>
